--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{280D3D1F-BDBB-4C1A-BD65-EC54B9041147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E8BB21-2884-4C1E-9357-C728AEC92BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -27,6 +27,8 @@
     <sheet name="12" sheetId="85" r:id="rId12"/>
     <sheet name="13" sheetId="86" r:id="rId13"/>
     <sheet name="14" sheetId="87" r:id="rId14"/>
+    <sheet name="15" sheetId="88" r:id="rId15"/>
+    <sheet name="16" sheetId="89" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -395,6 +397,132 @@
       </text>
     </comment>
     <comment ref="B57" authorId="0" shapeId="0" xr:uid="{F92CA02A-A2E4-4CDE-BE11-9E668A16D84D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{94600642-CF3A-43FA-A120-F6031FEE9C04}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{9767AF24-7B48-41F1-934E-6519F4D45047}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D4BF631E-4677-4071-9DCC-A07931960C33}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{EF80E771-233C-4B5B-8E1A-84647D961F56}">
       <text>
         <r>
           <rPr>
@@ -931,7 +1059,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4288" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4903" uniqueCount="333">
   <si>
     <t>№</t>
   </si>
@@ -1910,6 +2038,27 @@
   <si>
     <t>60-13-187AW12д/н</t>
   </si>
+  <si>
+    <t>60-13-014AU12н</t>
+  </si>
+  <si>
+    <t>60-13-192AL12н</t>
+  </si>
+  <si>
+    <t>60-13-453BD12н</t>
+  </si>
+  <si>
+    <t>60-13-043AZ12н</t>
+  </si>
+  <si>
+    <t>60-13-764BC12н</t>
+  </si>
+  <si>
+    <t>60-13-779ALC12н</t>
+  </si>
+  <si>
+    <t>60-13-896АR12н</t>
+  </si>
 </sst>
 </file>
 
@@ -2434,7 +2583,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="272">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3196,6 +3345,21 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3210,6 +3374,22 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="7" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -3677,10 +3857,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -3705,10 +3885,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5111,14 +5291,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5343,19 +5523,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5377,7 +5557,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -5919,10 +6099,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -5947,10 +6127,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7359,14 +7539,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -7596,19 +7776,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -7631,7 +7811,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8230,10 +8410,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8258,10 +8438,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -9663,14 +9843,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -9895,19 +10075,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -9929,7 +10109,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10476,10 +10656,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -10504,10 +10684,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -11909,14 +12089,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12141,19 +12321,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12175,7 +12355,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -12722,10 +12902,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -12750,10 +12930,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14155,14 +14335,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14387,19 +14567,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14421,7 +14601,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -14968,10 +15148,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -14996,10 +15176,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16401,14 +16581,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -16633,19 +16813,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -16667,7 +16847,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17103,6 +17283,4505 @@
       </c>
       <c r="H62" s="173">
         <v>8</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C856D3D-AC0A-4AC2-AA5A-929A455E8D63}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="265" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="265" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="270" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="270"/>
+      <c r="F2" s="265" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="265" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="266" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="265" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="265" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="266" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="266" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="266" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="271" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="271"/>
+      <c r="P2" s="265" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="265" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="265" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="265" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="200"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="200"/>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="193" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="191" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="191" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="200"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="200"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="256" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="247" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="200"/>
+      <c r="P5" s="200"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="200"/>
+      <c r="F6" s="191" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="200"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="191" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="200"/>
+      <c r="P6" s="200"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="200"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="191" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="200"/>
+      <c r="F7" s="247" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>237</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="200"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="247" t="s">
+        <v>261</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="200"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="200"/>
+      <c r="F8" s="191" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="191" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="200"/>
+      <c r="P8" s="200"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="179"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="200"/>
+      <c r="C9" s="191" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="247" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="200"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="200"/>
+      <c r="P9" s="200"/>
+      <c r="Q9" s="191" t="s">
+        <v>262</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="200"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="200"/>
+      <c r="C10" s="247" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="200"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="200"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="200"/>
+      <c r="P10" s="200"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="200"/>
+      <c r="C11" s="247" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="200"/>
+      <c r="F11" s="247" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="200"/>
+      <c r="M11" s="200"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="200"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="200"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="247" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="200"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="247" t="s">
+        <v>272</v>
+      </c>
+      <c r="O12" s="200"/>
+      <c r="P12" s="200"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="200"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="247" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="247" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="247" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="200"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="247" t="s">
+        <v>274</v>
+      </c>
+      <c r="O13" s="200"/>
+      <c r="P13" s="200"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="247" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="200"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="200"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="216" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="200"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="200"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="247" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="200"/>
+      <c r="N15" s="247" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="200"/>
+      <c r="Q15" s="200"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="191" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="216" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="248" t="s">
+        <v>278</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="200"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="200"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="200"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="247" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="200"/>
+      <c r="J17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="200"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="200"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="247" t="s">
+        <v>281</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="200"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="200"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="200"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="200"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="200"/>
+      <c r="N19" s="191" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="200"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="200"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="247" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="200"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="200"/>
+      <c r="L20" s="191" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="200"/>
+      <c r="N20" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O20" s="200"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="200"/>
+      <c r="S20" s="200"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="200"/>
+      <c r="L21" s="191" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="200"/>
+      <c r="O21" s="200"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="179"/>
+      <c r="R21" s="185">
+        <v>3</v>
+      </c>
+      <c r="S21" s="200"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="200"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="200"/>
+      <c r="L22" s="247" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="200"/>
+      <c r="N22" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="O22" s="200"/>
+      <c r="P22" s="200"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="200"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="200"/>
+      <c r="L23" s="247" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="200"/>
+      <c r="N23" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="O23" s="200"/>
+      <c r="P23" s="200"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="200"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="200"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="200"/>
+      <c r="N24" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="O24" s="200"/>
+      <c r="P24" s="200"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="200"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="200"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="200"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="200"/>
+      <c r="N25" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" s="200"/>
+      <c r="P25" s="200"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="200"/>
+      <c r="S25" s="200"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="200"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="200"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="M26" s="200"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="200"/>
+      <c r="P26" s="200"/>
+      <c r="Q26" s="191" t="s">
+        <v>245</v>
+      </c>
+      <c r="R26" s="200"/>
+      <c r="S26" s="200"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="200"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="200"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="200"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="200"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="200"/>
+      <c r="L28" s="185" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="200"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="200"/>
+      <c r="P28" s="200"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="200"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="200"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="200"/>
+      <c r="M29" s="200"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="200"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="200"/>
+      <c r="S29" s="200"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="200"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="200"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="200"/>
+      <c r="P30" s="200"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="200"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="200"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="200"/>
+      <c r="I31" s="200"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="200"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="200"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="200"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="200"/>
+      <c r="S31" s="200"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139">
+        <v>7</v>
+      </c>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="146">
+        <v>4</v>
+      </c>
+      <c r="B37" s="161" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="159" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="148"/>
+      <c r="E37" s="179"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="160"/>
+      <c r="H37" s="148"/>
+      <c r="I37" s="148"/>
+      <c r="J37" s="156"/>
+      <c r="K37" s="148"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="148"/>
+      <c r="N37" s="156"/>
+      <c r="O37" s="148"/>
+      <c r="P37" s="148"/>
+      <c r="Q37" s="171"/>
+      <c r="R37" s="150"/>
+      <c r="S37" s="190"/>
+      <c r="T37" s="144"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="272" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="274" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="275" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>30</v>
+      </c>
+      <c r="P49" s="151">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="274"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>9</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269" t="s">
+        <v>57</v>
+      </c>
+      <c r="O56" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <v>200</v>
+      </c>
+      <c r="H62" s="173">
+        <v>8</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2077F5E2-7FD1-48DF-B0B6-945646DA0758}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="267" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="267" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="270" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="270"/>
+      <c r="F2" s="267" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="267" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="268" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="267" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="267" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="268" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="268" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="268" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="271" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="271"/>
+      <c r="P2" s="267" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="267" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="267" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="267" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="200"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="200"/>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="193" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="191" t="s">
+        <v>332</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="191" t="s">
+        <v>326</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="200"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="200"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="247" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="200"/>
+      <c r="P5" s="200"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="200"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="200"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="191" t="s">
+        <v>327</v>
+      </c>
+      <c r="O6" s="200"/>
+      <c r="P6" s="200"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="200"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="191" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="200"/>
+      <c r="F7" s="247" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="200"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="247" t="s">
+        <v>261</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="200"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="200"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="191" t="s">
+        <v>328</v>
+      </c>
+      <c r="O8" s="200"/>
+      <c r="P8" s="200"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="179"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="200"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="247" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="200"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="200"/>
+      <c r="P9" s="200"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="200"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="200"/>
+      <c r="C10" s="247" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="200"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="200"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="200"/>
+      <c r="P10" s="200"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="200"/>
+      <c r="C11" s="247" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="200"/>
+      <c r="F11" s="247" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="200"/>
+      <c r="M11" s="200"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="200"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="200"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="247" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="200"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="247" t="s">
+        <v>272</v>
+      </c>
+      <c r="O12" s="200"/>
+      <c r="P12" s="200"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="200"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="247" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="247" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="247" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="200"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="247" t="s">
+        <v>274</v>
+      </c>
+      <c r="O13" s="200"/>
+      <c r="P13" s="200"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="247" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="200"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="200"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="216" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="200"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="200"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="247" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="200"/>
+      <c r="N15" s="247" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="200"/>
+      <c r="Q15" s="200"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="191" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="216" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="248" t="s">
+        <v>278</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="200"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="200"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="200"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="247" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="200"/>
+      <c r="J17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="200"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="200"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="247" t="s">
+        <v>281</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="200"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="200"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="200"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="200"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="200"/>
+      <c r="N19" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O19" s="200"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="200"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="247" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="200"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="200"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="200"/>
+      <c r="N20" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O20" s="200"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="200"/>
+      <c r="S20" s="200"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="200"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="200"/>
+      <c r="O21" s="200"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="179"/>
+      <c r="R21" s="185">
+        <v>3</v>
+      </c>
+      <c r="S21" s="200"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="200"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="200"/>
+      <c r="L22" s="247" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="200"/>
+      <c r="N22" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="O22" s="200"/>
+      <c r="P22" s="200"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="200"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="200"/>
+      <c r="L23" s="247" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="200"/>
+      <c r="N23" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="O23" s="200"/>
+      <c r="P23" s="200"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="200"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="200"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="200"/>
+      <c r="N24" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="O24" s="200"/>
+      <c r="P24" s="200"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="200"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="200"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="200"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="200"/>
+      <c r="N25" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" s="200"/>
+      <c r="P25" s="200"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="200"/>
+      <c r="S25" s="200"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="200"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="200"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="M26" s="200"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="200"/>
+      <c r="P26" s="200"/>
+      <c r="Q26" s="191" t="s">
+        <v>331</v>
+      </c>
+      <c r="R26" s="200"/>
+      <c r="S26" s="200"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="200"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="200"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="200"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="200"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="200"/>
+      <c r="L28" s="185" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="200"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="200"/>
+      <c r="P28" s="200"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="200"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="200"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="200"/>
+      <c r="M29" s="200"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="200"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="200"/>
+      <c r="S29" s="200"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="200"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="200"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="200"/>
+      <c r="P30" s="200"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="200"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="200"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="200"/>
+      <c r="I31" s="200"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="200"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="200"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="200"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="200"/>
+      <c r="S31" s="200"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139">
+        <v>7</v>
+      </c>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="277">
+        <v>4</v>
+      </c>
+      <c r="B37" s="278" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="279"/>
+      <c r="F37" s="280"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="281"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="282"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="272" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
+    </row>
+    <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="274" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="275" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="274"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
       </c>
       <c r="I62" s="175">
         <v>-1</v>
@@ -17214,10 +21893,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -17242,10 +21921,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -18651,14 +23330,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -18883,19 +23562,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -18917,7 +23596,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -19470,10 +24149,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -19498,10 +24177,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -20905,14 +25584,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -21137,19 +25816,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -21171,7 +25850,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -21725,10 +26404,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -21753,10 +26432,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -23160,14 +27839,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -23392,19 +28071,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -23426,7 +28105,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -23978,10 +28657,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -24006,10 +28685,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -25413,14 +30092,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -25645,19 +30324,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -25679,7 +30358,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -26232,10 +30911,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -26260,10 +30939,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -27667,14 +32346,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -27899,19 +32578,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -27933,7 +32612,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -28485,10 +33164,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -28513,10 +33192,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -29920,14 +34599,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30152,19 +34831,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30186,7 +34865,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -30736,10 +35415,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -30764,10 +35443,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -32171,14 +36850,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -32403,19 +37082,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -32437,7 +37116,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -32987,10 +37666,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="265" t="s">
+      <c r="D2" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="265"/>
+      <c r="E2" s="270"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -33015,10 +37694,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="266" t="s">
+      <c r="N2" s="271" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="266"/>
+      <c r="O2" s="271"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -34422,14 +39101,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="267" t="s">
+      <c r="L41" s="272" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="267"/>
-      <c r="N41" s="267"/>
-      <c r="O41" s="267"/>
-      <c r="P41" s="267"/>
-      <c r="Q41" s="268"/>
+      <c r="M41" s="272"/>
+      <c r="N41" s="272"/>
+      <c r="O41" s="272"/>
+      <c r="P41" s="272"/>
+      <c r="Q41" s="273"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -34654,19 +39333,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="269" t="s">
+      <c r="A49" s="274" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="270" t="s">
+      <c r="B49" s="275" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="270"/>
-      <c r="D49" s="270"/>
-      <c r="E49" s="270"/>
-      <c r="F49" s="271"/>
-      <c r="G49" s="271"/>
-      <c r="H49" s="271"/>
-      <c r="I49" s="271"/>
+      <c r="C49" s="275"/>
+      <c r="D49" s="275"/>
+      <c r="E49" s="275"/>
+      <c r="F49" s="276"/>
+      <c r="G49" s="276"/>
+      <c r="H49" s="276"/>
+      <c r="I49" s="276"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -34688,7 +39367,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="269"/>
+      <c r="A50" s="274"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E8BB21-2884-4C1E-9357-C728AEC92BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC18E5D-48F2-4B5F-B600-0DE4D38C5C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="14" sheetId="87" r:id="rId14"/>
     <sheet name="15" sheetId="88" r:id="rId15"/>
     <sheet name="16" sheetId="89" r:id="rId16"/>
+    <sheet name="17" sheetId="90" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -523,6 +524,69 @@
       </text>
     </comment>
     <comment ref="B57" authorId="0" shapeId="0" xr:uid="{EF80E771-233C-4B5B-8E1A-84647D961F56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{67B6D405-B8E3-41B3-94BB-7C70F0A5889D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{2BD75881-E0B3-43DE-B041-085A08B52664}">
       <text>
         <r>
           <rPr>
@@ -1059,7 +1123,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4903" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5210" uniqueCount="333">
   <si>
     <t>№</t>
   </si>
@@ -2583,7 +2647,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="285">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3360,21 +3424,6 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="45" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3390,6 +3439,27 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="45" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -3857,10 +3927,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -3885,10 +3955,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5291,14 +5361,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5523,19 +5593,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5557,7 +5627,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6099,10 +6169,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6127,10 +6197,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7539,14 +7609,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -7776,19 +7846,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -7811,7 +7881,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8410,10 +8480,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8438,10 +8508,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -9843,14 +9913,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10075,19 +10145,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10109,7 +10179,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10656,10 +10726,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -10684,10 +10754,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12089,14 +12159,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12321,19 +12391,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12355,7 +12425,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -12902,10 +12972,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -12930,10 +13000,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14335,14 +14405,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14567,19 +14637,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14601,7 +14671,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15148,10 +15218,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15176,10 +15246,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16581,14 +16651,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -16813,19 +16883,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -16847,7 +16917,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17394,10 +17464,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17422,10 +17492,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -18827,14 +18897,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19059,19 +19129,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19093,7 +19163,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -19644,10 +19714,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -19672,10 +19742,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -20986,18 +21056,18 @@
       <c r="T36" s="144"/>
     </row>
     <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A37" s="277">
+      <c r="A37" s="272">
         <v>4</v>
       </c>
-      <c r="B37" s="278" t="s">
+      <c r="B37" s="273" t="s">
         <v>173</v>
       </c>
       <c r="C37" s="177" t="s">
         <v>174</v>
       </c>
       <c r="D37" s="221"/>
-      <c r="E37" s="279"/>
-      <c r="F37" s="280"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
       <c r="G37" s="187"/>
       <c r="H37" s="221"/>
       <c r="I37" s="221"/>
@@ -21011,9 +21081,9 @@
       <c r="O37" s="221"/>
       <c r="P37" s="221"/>
       <c r="Q37" s="197"/>
-      <c r="R37" s="281"/>
+      <c r="R37" s="276"/>
       <c r="S37" s="194"/>
-      <c r="T37" s="282"/>
+      <c r="T37" s="277"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="146">
@@ -21077,16 +21147,16 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
-    </row>
-    <row r="42" spans="1:20" ht="27" x14ac:dyDescent="0.3">
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
       <c r="B42" s="152" t="s">
         <v>179</v>
@@ -21309,19 +21379,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21343,7 +21413,2256 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0060BF9E-50ED-4DD7-BE69-520877427C6A}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="270" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="270" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="278" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="278"/>
+      <c r="F2" s="270" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="270" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="271" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="270" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="270" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="271" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="271" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="271" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="279" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="279"/>
+      <c r="P2" s="270" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="270" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="270" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="270" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="193" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="200"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="200"/>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="193" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="191" t="s">
+        <v>332</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="191" t="s">
+        <v>326</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192" t="s">
+        <v>287</v>
+      </c>
+      <c r="I4" s="200"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="200"/>
+      <c r="P4" s="200"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="247" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="200"/>
+      <c r="J5" s="200"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="200"/>
+      <c r="P5" s="200"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="200"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="200"/>
+      <c r="J6" s="200"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="191" t="s">
+        <v>327</v>
+      </c>
+      <c r="O6" s="200"/>
+      <c r="P6" s="200"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="200"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="191" t="s">
+        <v>329</v>
+      </c>
+      <c r="E7" s="200"/>
+      <c r="F7" s="247" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="200"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="247" t="s">
+        <v>261</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="200"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="200"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="191" t="s">
+        <v>328</v>
+      </c>
+      <c r="O8" s="200"/>
+      <c r="P8" s="200"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="179"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="200"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="247" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="200"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="200"/>
+      <c r="P9" s="200"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="200"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="200"/>
+      <c r="C10" s="247" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="200"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="200"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="200"/>
+      <c r="P10" s="200"/>
+      <c r="R10" s="200"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="200"/>
+      <c r="C11" s="247" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="200"/>
+      <c r="F11" s="247" t="s">
+        <v>267</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="200"/>
+      <c r="M11" s="200"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="200"/>
+      <c r="P11" s="200"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="200"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="247" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="200"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="247" t="s">
+        <v>272</v>
+      </c>
+      <c r="O12" s="200"/>
+      <c r="P12" s="200"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="200"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="247" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="247" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="247" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="200"/>
+      <c r="J13" s="200"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="247" t="s">
+        <v>274</v>
+      </c>
+      <c r="O13" s="200"/>
+      <c r="P13" s="200"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="247" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="200"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="200"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="216" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="200"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="200"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="247" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="200"/>
+      <c r="I15" s="200"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="200"/>
+      <c r="N15" s="247" t="s">
+        <v>276</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="200"/>
+      <c r="Q15" s="200"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="200"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="191" t="s">
+        <v>330</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="216" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="248" t="s">
+        <v>278</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="200"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="200"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="200"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="247" t="s">
+        <v>279</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="200"/>
+      <c r="J17" s="200"/>
+      <c r="L17" s="200"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="200"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="200"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="200"/>
+      <c r="K18" s="200"/>
+      <c r="L18" s="200"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="247" t="s">
+        <v>281</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="200"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="200"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="200"/>
+      <c r="J19" s="200"/>
+      <c r="K19" s="200"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="200"/>
+      <c r="N19" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O19" s="200"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="200"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="200"/>
+      <c r="F20" s="247" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="200"/>
+      <c r="J20" s="200"/>
+      <c r="K20" s="200"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="200"/>
+      <c r="N20" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O20" s="200"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="200"/>
+      <c r="S20" s="200"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="200"/>
+      <c r="J21" s="200"/>
+      <c r="K21" s="200"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="200"/>
+      <c r="O21" s="200"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="179"/>
+      <c r="R21" s="185">
+        <v>3</v>
+      </c>
+      <c r="S21" s="200"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="200"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="200"/>
+      <c r="I22" s="200"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="200"/>
+      <c r="L22" s="247" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="200"/>
+      <c r="N22" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="O22" s="200"/>
+      <c r="P22" s="200"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="200"/>
+      <c r="J23" s="200"/>
+      <c r="K23" s="200"/>
+      <c r="L23" s="247" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="200"/>
+      <c r="N23" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="O23" s="200"/>
+      <c r="P23" s="200"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="200"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="200"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="200"/>
+      <c r="J24" s="200"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="200"/>
+      <c r="N24" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="O24" s="200"/>
+      <c r="P24" s="200"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="200"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="200"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="200"/>
+      <c r="J25" s="179"/>
+      <c r="K25" s="200"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="200"/>
+      <c r="N25" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="O25" s="200"/>
+      <c r="P25" s="200"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="200"/>
+      <c r="S25" s="200"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="200"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="200"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="200"/>
+      <c r="J26" s="200"/>
+      <c r="K26" s="200"/>
+      <c r="M26" s="200"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="200"/>
+      <c r="P26" s="200"/>
+      <c r="Q26" s="191" t="s">
+        <v>331</v>
+      </c>
+      <c r="R26" s="200"/>
+      <c r="S26" s="200"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="200"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="200"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="200"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="200"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="200"/>
+      <c r="P27" s="179"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="200"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="200"/>
+      <c r="F28" s="200"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="200"/>
+      <c r="I28" s="200"/>
+      <c r="J28" s="200"/>
+      <c r="K28" s="200"/>
+      <c r="L28" s="185" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="200"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="200"/>
+      <c r="P28" s="200"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="200"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="200"/>
+      <c r="C29" s="200"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="200"/>
+      <c r="F29" s="200"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="200"/>
+      <c r="I29" s="200"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="200"/>
+      <c r="M29" s="200"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="200"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="200"/>
+      <c r="S29" s="200"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="200"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="200"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="200"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="200"/>
+      <c r="M30" s="200"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="200"/>
+      <c r="P30" s="200"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="200"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="200"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="200"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="200"/>
+      <c r="I31" s="200"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="200"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="200"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="200"/>
+      <c r="P31" s="200"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="200"/>
+      <c r="S31" s="200"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139">
+        <v>7</v>
+      </c>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="280" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="282" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="283" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="282"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -21893,10 +24212,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -21921,10 +24240,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -23330,14 +25649,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -23562,19 +25881,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -23596,7 +25915,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -24149,10 +26468,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -24177,10 +26496,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -25584,14 +27903,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -25816,19 +28135,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -25850,7 +28169,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -26404,10 +28723,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -26432,10 +28751,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -27839,14 +30158,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -28071,19 +30390,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -28105,7 +30424,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -28657,10 +30976,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -28685,10 +31004,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -30092,14 +32411,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30324,19 +32643,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30358,7 +32677,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -30911,10 +33230,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -30939,10 +33258,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -32346,14 +34665,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -32578,19 +34897,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -32612,7 +34931,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -33164,10 +35483,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -33192,10 +35511,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -34599,14 +36918,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -34831,19 +37150,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -34865,7 +37184,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -35415,10 +37734,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -35443,10 +37762,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -36850,14 +39169,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37082,19 +39401,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37116,7 +39435,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -37666,10 +39985,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="D2" s="278" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="270"/>
+      <c r="E2" s="278"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -37694,10 +40013,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="271" t="s">
+      <c r="N2" s="279" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="271"/>
+      <c r="O2" s="279"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -39101,14 +41420,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="272" t="s">
+      <c r="L41" s="280" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="272"/>
-      <c r="N41" s="272"/>
-      <c r="O41" s="272"/>
-      <c r="P41" s="272"/>
-      <c r="Q41" s="273"/>
+      <c r="M41" s="280"/>
+      <c r="N41" s="280"/>
+      <c r="O41" s="280"/>
+      <c r="P41" s="280"/>
+      <c r="Q41" s="281"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39333,19 +41652,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="274" t="s">
+      <c r="A49" s="282" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="275" t="s">
+      <c r="B49" s="283" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="275"/>
-      <c r="D49" s="275"/>
-      <c r="E49" s="275"/>
-      <c r="F49" s="276"/>
-      <c r="G49" s="276"/>
-      <c r="H49" s="276"/>
-      <c r="I49" s="276"/>
+      <c r="C49" s="283"/>
+      <c r="D49" s="283"/>
+      <c r="E49" s="283"/>
+      <c r="F49" s="284"/>
+      <c r="G49" s="284"/>
+      <c r="H49" s="284"/>
+      <c r="I49" s="284"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39367,7 +41686,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="274"/>
+      <c r="A50" s="282"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC18E5D-48F2-4B5F-B600-0DE4D38C5C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C44F654-4D00-467A-88FA-592E322059AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="15" sheetId="88" r:id="rId15"/>
     <sheet name="16" sheetId="89" r:id="rId16"/>
     <sheet name="17" sheetId="90" r:id="rId17"/>
+    <sheet name="18" sheetId="91" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -617,6 +618,69 @@
 </comments>
 </file>
 
+<file path=xl/comments18.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{9E58FDB9-61B4-48D0-994B-1D491A12427B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{7406D024-8BC0-4F45-80E7-0E4EDF321B2C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1123,7 +1187,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5210" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5514" uniqueCount="351">
   <si>
     <t>№</t>
   </si>
@@ -2123,6 +2187,60 @@
   <si>
     <t>60-13-896АR12н</t>
   </si>
+  <si>
+    <t>60-13-932BC12н</t>
+  </si>
+  <si>
+    <t>60-13-941BC12н</t>
+  </si>
+  <si>
+    <t>60-13-729AP12н</t>
+  </si>
+  <si>
+    <t>60-13-209AT12н</t>
+  </si>
+  <si>
+    <t>60-13-763BC12н</t>
+  </si>
+  <si>
+    <t>60-13-096YS12н</t>
+  </si>
+  <si>
+    <t>60-13-021AU12н</t>
+  </si>
+  <si>
+    <t>60-13-545ВА12н</t>
+  </si>
+  <si>
+    <t>60-13-148AN12н</t>
+  </si>
+  <si>
+    <t>60-13-974АR12н</t>
+  </si>
+  <si>
+    <t>60-13-530BD12н</t>
+  </si>
+  <si>
+    <t>60-13-092MA12н</t>
+  </si>
+  <si>
+    <t>60-13-094YS12н</t>
+  </si>
+  <si>
+    <t>60-13-459BD12н</t>
+  </si>
+  <si>
+    <t>60-13-692BOн</t>
+  </si>
+  <si>
+    <t>60-27-635AV12н</t>
+  </si>
+  <si>
+    <t>60-13-736AY12н</t>
+  </si>
+  <si>
+    <t>60-13-907AS12н</t>
+  </si>
 </sst>
 </file>
 
@@ -2647,7 +2765,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="289">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3446,6 +3564,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3461,6 +3585,10 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="58">
     <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3927,10 +4055,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -3955,10 +4083,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5361,14 +5489,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5593,19 +5721,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5627,7 +5755,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6169,10 +6297,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6197,10 +6325,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7609,14 +7737,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -7846,19 +7974,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -7881,7 +8009,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8480,10 +8608,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8508,10 +8636,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -9913,14 +10041,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10145,19 +10273,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10179,7 +10307,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10726,10 +10854,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -10754,10 +10882,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12159,14 +12287,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12391,19 +12519,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12425,7 +12553,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -12972,10 +13100,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13000,10 +13128,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14405,14 +14533,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14637,19 +14765,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14671,7 +14799,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15218,10 +15346,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15246,10 +15374,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16651,14 +16779,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -16883,19 +17011,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -16917,7 +17045,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17464,10 +17592,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17492,10 +17620,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -18897,14 +19025,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19129,19 +19257,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19163,7 +19291,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -19714,10 +19842,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -19742,10 +19870,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21147,14 +21275,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21379,19 +21507,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21413,7 +21541,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -21963,10 +22091,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -21991,10 +22119,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23396,14 +23524,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -23628,19 +23756,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -23662,7 +23790,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -23928,6 +24056,2247 @@
       <c r="M56" s="193" t="s">
         <v>57</v>
       </c>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794C13C1-701E-42C8-A9C9-9575D79A0014}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="278" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="278" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="280" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="280"/>
+      <c r="F2" s="278" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="278" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="279" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="278" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="278" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="279" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="279" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="279" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="281" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="281"/>
+      <c r="P2" s="278" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="278" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="278" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="278" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="288"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="288"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="288"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="288"/>
+      <c r="J5" s="288"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="288"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="288"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="288"/>
+      <c r="J6" s="288"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="288"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="288"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="288"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="288"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="288"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="288"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="288"/>
+      <c r="P8" s="288"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="288"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>264</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="288"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="288"/>
+      <c r="P9" s="288"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="288"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="288"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="288"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="288"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="288"/>
+      <c r="P10" s="288"/>
+      <c r="R10" s="288"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="288"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="288"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="288"/>
+      <c r="M11" s="288"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="288"/>
+      <c r="P11" s="288"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="288"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="288"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="288"/>
+      <c r="P12" s="288"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="288"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="288"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="288"/>
+      <c r="J13" s="288"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="288"/>
+      <c r="P13" s="288"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="288"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="288"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="288"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="288"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="288"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="288"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="288"/>
+      <c r="H15" s="288"/>
+      <c r="I15" s="288"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="288"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="288"/>
+      <c r="Q15" s="288"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="288"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="288"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>244</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="288"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="288"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="288"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="288"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="288"/>
+      <c r="J17" s="288"/>
+      <c r="L17" s="288"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="288"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="288"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="288"/>
+      <c r="K18" s="288"/>
+      <c r="L18" s="288"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="288"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="288"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="288"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="288"/>
+      <c r="J19" s="288"/>
+      <c r="K19" s="288"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="288"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="288"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="288"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="288"/>
+      <c r="F20" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G20" s="288"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="288"/>
+      <c r="J20" s="288"/>
+      <c r="K20" s="288"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="288"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="288"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="288"/>
+      <c r="S20" s="288"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="288"/>
+      <c r="J21" s="288"/>
+      <c r="K21" s="288"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="288"/>
+      <c r="O21" s="288"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="287">
+        <v>3</v>
+      </c>
+      <c r="S21" s="288"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="288"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="288"/>
+      <c r="H22" s="288"/>
+      <c r="I22" s="288"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="288"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="288"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="288"/>
+      <c r="P22" s="288"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="288"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="288"/>
+      <c r="J23" s="288"/>
+      <c r="K23" s="288"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="288"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="288"/>
+      <c r="P23" s="288"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="288"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="288"/>
+      <c r="G24" s="288"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="288"/>
+      <c r="J24" s="288"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="288"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="288"/>
+      <c r="P24" s="288"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="288"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="288"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="288"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="288"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="288"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="288"/>
+      <c r="P25" s="288"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="288"/>
+      <c r="S25" s="288"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="288"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="288"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="288"/>
+      <c r="J26" s="288"/>
+      <c r="K26" s="288"/>
+      <c r="M26" s="288"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="288"/>
+      <c r="P26" s="288"/>
+      <c r="Q26" s="191" t="s">
+        <v>331</v>
+      </c>
+      <c r="R26" s="288"/>
+      <c r="S26" s="288"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="288"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="288"/>
+      <c r="G27" s="288"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="288"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="288"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="288"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="288"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="288"/>
+      <c r="F28" s="288"/>
+      <c r="G28" s="288"/>
+      <c r="H28" s="288"/>
+      <c r="I28" s="288"/>
+      <c r="J28" s="288"/>
+      <c r="K28" s="288"/>
+      <c r="L28" s="287" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="288"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="288"/>
+      <c r="P28" s="288"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="288"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="288"/>
+      <c r="C29" s="288"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="288"/>
+      <c r="F29" s="288"/>
+      <c r="G29" s="288"/>
+      <c r="H29" s="288"/>
+      <c r="I29" s="288"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="288"/>
+      <c r="M29" s="288"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="288"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="288"/>
+      <c r="S29" s="288"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="288"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="288"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="288"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="288"/>
+      <c r="M30" s="288"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="288"/>
+      <c r="P30" s="288"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="288"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="288"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="288"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="288"/>
+      <c r="I31" s="288"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="288"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="288"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="288"/>
+      <c r="P31" s="288"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="288"/>
+      <c r="S31" s="288"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="282" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="284" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="285" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="284"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
       <c r="N56" s="269"/>
       <c r="O56" s="253"/>
       <c r="P56" s="200"/>
@@ -24212,10 +26581,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -24240,10 +26609,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -25649,14 +28018,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -25881,19 +28250,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -25915,7 +28284,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -26468,10 +28837,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -26496,10 +28865,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -27903,14 +30272,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -28135,19 +30504,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -28169,7 +30538,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -28723,10 +31092,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -28751,10 +31120,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -30158,14 +32527,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30390,19 +32759,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30424,7 +32793,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -30976,10 +33345,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -31004,10 +33373,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -32411,14 +34780,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -32643,19 +35012,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -32677,7 +35046,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -33230,10 +35599,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -33258,10 +35627,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -34665,14 +37034,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -34897,19 +37266,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -34931,7 +37300,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -35483,10 +37852,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -35511,10 +37880,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -36918,14 +39287,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37150,19 +39519,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37184,7 +39553,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -37734,10 +40103,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -37762,10 +40131,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -39169,14 +41538,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39401,19 +41770,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39435,7 +41804,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -39985,10 +42354,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="278" t="s">
+      <c r="D2" s="280" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="278"/>
+      <c r="E2" s="280"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -40013,10 +42382,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="279" t="s">
+      <c r="N2" s="281" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="279"/>
+      <c r="O2" s="281"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -41420,14 +43789,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="280" t="s">
+      <c r="L41" s="282" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="280"/>
-      <c r="N41" s="280"/>
-      <c r="O41" s="280"/>
-      <c r="P41" s="280"/>
-      <c r="Q41" s="281"/>
+      <c r="M41" s="282"/>
+      <c r="N41" s="282"/>
+      <c r="O41" s="282"/>
+      <c r="P41" s="282"/>
+      <c r="Q41" s="283"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -41652,19 +44021,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="282" t="s">
+      <c r="A49" s="284" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="283" t="s">
+      <c r="B49" s="285" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="283"/>
-      <c r="D49" s="283"/>
-      <c r="E49" s="283"/>
-      <c r="F49" s="284"/>
-      <c r="G49" s="284"/>
-      <c r="H49" s="284"/>
-      <c r="I49" s="284"/>
+      <c r="C49" s="285"/>
+      <c r="D49" s="285"/>
+      <c r="E49" s="285"/>
+      <c r="F49" s="286"/>
+      <c r="G49" s="286"/>
+      <c r="H49" s="286"/>
+      <c r="I49" s="286"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -41686,7 +44055,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="282"/>
+      <c r="A50" s="284"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C44F654-4D00-467A-88FA-592E322059AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA93AB29-4AF2-4657-AC12-589F24B4CCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -31,6 +31,7 @@
     <sheet name="16" sheetId="89" r:id="rId16"/>
     <sheet name="17" sheetId="90" r:id="rId17"/>
     <sheet name="18" sheetId="91" r:id="rId18"/>
+    <sheet name="19" sheetId="92" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -681,6 +682,69 @@
 </comments>
 </file>
 
+<file path=xl/comments19.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{B548A010-6137-4069-8261-695B4184F918}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{74F66320-01AA-41F9-8A6B-910ABA673B91}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1187,7 +1251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5514" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5818" uniqueCount="352">
   <si>
     <t>№</t>
   </si>
@@ -2241,6 +2305,9 @@
   <si>
     <t>60-13-907AS12н</t>
   </si>
+  <si>
+    <t>60-13-452BD12н</t>
+  </si>
 </sst>
 </file>
 
@@ -2765,7 +2832,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="289">
+  <cellXfs count="291">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3570,6 +3637,16 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3585,10 +3662,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="58">
     <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4055,10 +4128,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4083,10 +4156,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5489,14 +5562,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5721,19 +5794,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5755,7 +5828,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6297,10 +6370,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6325,10 +6398,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7737,14 +7810,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -7974,19 +8047,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8009,7 +8082,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8608,10 +8681,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8636,10 +8709,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10041,14 +10114,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10273,19 +10346,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10307,7 +10380,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10854,10 +10927,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -10882,10 +10955,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12287,14 +12360,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12519,19 +12592,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12553,7 +12626,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13100,10 +13173,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13128,10 +13201,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14533,14 +14606,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14765,19 +14838,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14799,7 +14872,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15346,10 +15419,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15374,10 +15447,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16779,14 +16852,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17011,19 +17084,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17045,7 +17118,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17592,10 +17665,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17620,10 +17693,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19025,14 +19098,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19257,19 +19330,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19291,7 +19364,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -19842,10 +19915,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -19870,10 +19943,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21275,14 +21348,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21507,19 +21580,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21541,7 +21614,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22091,10 +22164,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22119,10 +22192,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23524,14 +23597,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -23756,19 +23829,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -23790,7 +23863,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24340,10 +24413,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24368,10 +24441,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -24413,7 +24486,7 @@
       <c r="H3" s="192" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="288"/>
+      <c r="I3" s="283"/>
       <c r="J3" s="192" t="s">
         <v>20</v>
       </c>
@@ -24469,7 +24542,7 @@
         <v>28</v>
       </c>
       <c r="H4" s="192"/>
-      <c r="I4" s="288"/>
+      <c r="I4" s="283"/>
       <c r="J4" s="139">
         <v>1</v>
       </c>
@@ -24488,7 +24561,7 @@
       <c r="O4" s="192" t="s">
         <v>144</v>
       </c>
-      <c r="P4" s="288"/>
+      <c r="P4" s="283"/>
       <c r="Q4" s="192" t="s">
         <v>258</v>
       </c>
@@ -24525,8 +24598,8 @@
       <c r="H5" s="139">
         <v>1</v>
       </c>
-      <c r="I5" s="288"/>
-      <c r="J5" s="288"/>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
       <c r="K5" s="192" t="s">
         <v>37</v>
       </c>
@@ -24542,7 +24615,7 @@
       <c r="O5" s="192" t="s">
         <v>220</v>
       </c>
-      <c r="P5" s="288"/>
+      <c r="P5" s="283"/>
       <c r="Q5" s="192" t="s">
         <v>40</v>
       </c>
@@ -24565,7 +24638,7 @@
       <c r="D6" s="193" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="288"/>
+      <c r="E6" s="283"/>
       <c r="F6" s="192" t="s">
         <v>236</v>
       </c>
@@ -24573,8 +24646,8 @@
         <v>45</v>
       </c>
       <c r="H6" s="196"/>
-      <c r="I6" s="288"/>
-      <c r="J6" s="288"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
       <c r="K6" s="192" t="s">
         <v>46</v>
       </c>
@@ -24590,14 +24663,14 @@
       <c r="O6" s="192" t="s">
         <v>152</v>
       </c>
-      <c r="P6" s="288"/>
+      <c r="P6" s="283"/>
       <c r="Q6" s="193" t="s">
         <v>49</v>
       </c>
       <c r="R6" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="288"/>
+      <c r="S6" s="283"/>
       <c r="T6" s="200"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -24613,7 +24686,7 @@
       <c r="D7" s="192" t="s">
         <v>238</v>
       </c>
-      <c r="E7" s="288"/>
+      <c r="E7" s="283"/>
       <c r="F7" s="191" t="s">
         <v>334</v>
       </c>
@@ -24641,7 +24714,7 @@
       <c r="N7" s="192" t="s">
         <v>239</v>
       </c>
-      <c r="O7" s="288"/>
+      <c r="O7" s="283"/>
       <c r="P7" s="139">
         <v>1</v>
       </c>
@@ -24660,14 +24733,14 @@
       <c r="A8" s="146">
         <v>6</v>
       </c>
-      <c r="B8" s="288"/>
+      <c r="B8" s="283"/>
       <c r="C8" s="193" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="192" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="288"/>
+      <c r="E8" s="283"/>
       <c r="F8" s="192" t="s">
         <v>240</v>
       </c>
@@ -24695,8 +24768,8 @@
       <c r="N8" s="192" t="s">
         <v>243</v>
       </c>
-      <c r="O8" s="288"/>
-      <c r="P8" s="288"/>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
       <c r="Q8" s="192" t="s">
         <v>254</v>
       </c>
@@ -24712,7 +24785,7 @@
       <c r="A9" s="146">
         <v>7</v>
       </c>
-      <c r="B9" s="288"/>
+      <c r="B9" s="283"/>
       <c r="C9" s="192" t="s">
         <v>242</v>
       </c>
@@ -24741,26 +24814,26 @@
       <c r="L9" s="192" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="288"/>
+      <c r="M9" s="283"/>
       <c r="N9" s="178" t="s">
         <v>83</v>
       </c>
-      <c r="O9" s="288"/>
-      <c r="P9" s="288"/>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
       <c r="Q9" s="191" t="s">
         <v>309</v>
       </c>
       <c r="R9" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="S9" s="288"/>
+      <c r="S9" s="283"/>
       <c r="T9" s="200"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="146">
         <v>8</v>
       </c>
-      <c r="B10" s="288"/>
+      <c r="B10" s="283"/>
       <c r="C10" s="191" t="s">
         <v>335</v>
       </c>
@@ -24777,7 +24850,7 @@
       <c r="H10" s="192" t="s">
         <v>80</v>
       </c>
-      <c r="I10" s="288"/>
+      <c r="I10" s="283"/>
       <c r="J10" s="191" t="s">
         <v>290</v>
       </c>
@@ -24787,13 +24860,13 @@
       <c r="L10" s="193" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="288"/>
+      <c r="M10" s="283"/>
       <c r="N10" s="193" t="s">
         <v>92</v>
       </c>
-      <c r="O10" s="288"/>
-      <c r="P10" s="288"/>
-      <c r="R10" s="288"/>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
       <c r="S10" s="154" t="s">
         <v>84</v>
       </c>
@@ -24803,14 +24876,14 @@
       <c r="A11" s="146">
         <v>9</v>
       </c>
-      <c r="B11" s="288"/>
+      <c r="B11" s="283"/>
       <c r="C11" s="191" t="s">
         <v>336</v>
       </c>
       <c r="D11" s="193" t="s">
         <v>77</v>
       </c>
-      <c r="E11" s="288"/>
+      <c r="E11" s="283"/>
       <c r="F11" s="191" t="s">
         <v>337</v>
       </c>
@@ -24827,17 +24900,17 @@
       <c r="K11" s="193" t="s">
         <v>113</v>
       </c>
-      <c r="L11" s="288"/>
-      <c r="M11" s="288"/>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
       <c r="N11" s="193" t="s">
         <v>99</v>
       </c>
-      <c r="O11" s="288"/>
-      <c r="P11" s="288"/>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
       <c r="Q11" s="139" t="s">
         <v>93</v>
       </c>
-      <c r="R11" s="288"/>
+      <c r="R11" s="283"/>
       <c r="S11" s="193" t="s">
         <v>94</v>
       </c>
@@ -24873,16 +24946,16 @@
       <c r="K12" s="193" t="s">
         <v>90</v>
       </c>
-      <c r="L12" s="288"/>
+      <c r="L12" s="283"/>
       <c r="M12" s="192"/>
       <c r="N12" s="191" t="s">
         <v>338</v>
       </c>
-      <c r="O12" s="288"/>
-      <c r="P12" s="288"/>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
       <c r="Q12" s="139"/>
       <c r="R12" s="139"/>
-      <c r="S12" s="288"/>
+      <c r="S12" s="283"/>
       <c r="T12" s="200"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -24892,7 +24965,7 @@
       <c r="B13" s="139">
         <v>5</v>
       </c>
-      <c r="C13" s="288"/>
+      <c r="C13" s="283"/>
       <c r="D13" s="191" t="s">
         <v>339</v>
       </c>
@@ -24906,8 +24979,8 @@
       <c r="H13" s="191" t="s">
         <v>341</v>
       </c>
-      <c r="I13" s="288"/>
-      <c r="J13" s="288"/>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
       <c r="K13" s="193" t="s">
         <v>97</v>
       </c>
@@ -24918,8 +24991,8 @@
       <c r="N13" s="191" t="s">
         <v>342</v>
       </c>
-      <c r="O13" s="288"/>
-      <c r="P13" s="288"/>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
       <c r="Q13" s="139"/>
       <c r="R13" s="139"/>
       <c r="S13" s="139">
@@ -24934,7 +25007,7 @@
       <c r="B14" s="181" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="288"/>
+      <c r="C14" s="283"/>
       <c r="D14" s="191" t="s">
         <v>343</v>
       </c>
@@ -24942,11 +25015,11 @@
       <c r="F14" s="192" t="s">
         <v>112</v>
       </c>
-      <c r="G14" s="288"/>
+      <c r="G14" s="283"/>
       <c r="H14" s="192" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="288"/>
+      <c r="I14" s="283"/>
       <c r="J14" s="139"/>
       <c r="K14" s="193" t="s">
         <v>102</v>
@@ -24961,14 +25034,14 @@
       <c r="O14" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="P14" s="288"/>
+      <c r="P14" s="283"/>
       <c r="Q14" s="139" t="s">
         <v>111</v>
       </c>
       <c r="R14" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="S14" s="288"/>
+      <c r="S14" s="283"/>
       <c r="T14" s="200"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -24978,14 +25051,14 @@
       <c r="B15" s="177" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="288"/>
+      <c r="D15" s="283"/>
       <c r="E15" s="193"/>
       <c r="F15" s="191" t="s">
         <v>345</v>
       </c>
-      <c r="G15" s="288"/>
-      <c r="H15" s="288"/>
-      <c r="I15" s="288"/>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
       <c r="J15" s="139"/>
       <c r="K15" s="193" t="s">
         <v>108</v>
@@ -24993,15 +25066,15 @@
       <c r="L15" s="177" t="s">
         <v>103</v>
       </c>
-      <c r="M15" s="288"/>
+      <c r="M15" s="283"/>
       <c r="N15" s="191" t="s">
         <v>346</v>
       </c>
       <c r="O15" s="193" t="s">
         <v>115</v>
       </c>
-      <c r="P15" s="288"/>
-      <c r="Q15" s="288"/>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
       <c r="R15" s="154" t="s">
         <v>116</v>
       </c>
@@ -25015,13 +25088,13 @@
         <v>14</v>
       </c>
       <c r="B16" s="139"/>
-      <c r="C16" s="288"/>
+      <c r="C16" s="283"/>
       <c r="D16" s="193"/>
       <c r="E16" s="193"/>
       <c r="F16" s="192" t="s">
         <v>277</v>
       </c>
-      <c r="G16" s="288"/>
+      <c r="G16" s="283"/>
       <c r="H16" s="139"/>
       <c r="I16" s="193"/>
       <c r="J16" s="139" t="s">
@@ -25042,12 +25115,12 @@
       <c r="O16" s="192" t="s">
         <v>118</v>
       </c>
-      <c r="P16" s="288"/>
+      <c r="P16" s="283"/>
       <c r="Q16" s="182"/>
       <c r="R16" s="192" t="s">
         <v>119</v>
       </c>
-      <c r="S16" s="288"/>
+      <c r="S16" s="283"/>
       <c r="T16" s="200"/>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -25057,19 +25130,19 @@
       <c r="B17" s="139">
         <v>1</v>
       </c>
-      <c r="C17" s="288"/>
+      <c r="C17" s="283"/>
       <c r="D17" s="193"/>
       <c r="E17" s="193"/>
       <c r="F17" s="191" t="s">
         <v>312</v>
       </c>
-      <c r="G17" s="288"/>
+      <c r="G17" s="283"/>
       <c r="H17" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="I17" s="288"/>
-      <c r="J17" s="288"/>
-      <c r="L17" s="288"/>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
       <c r="M17" s="183"/>
       <c r="N17" s="191" t="s">
         <v>325</v>
@@ -25077,14 +25150,14 @@
       <c r="O17" s="192" t="s">
         <v>247</v>
       </c>
-      <c r="P17" s="288"/>
+      <c r="P17" s="283"/>
       <c r="Q17" s="193" t="s">
         <v>122</v>
       </c>
       <c r="R17" s="193" t="s">
         <v>123</v>
       </c>
-      <c r="S17" s="288"/>
+      <c r="S17" s="283"/>
       <c r="T17" s="200"/>
     </row>
     <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
@@ -25107,9 +25180,9 @@
       <c r="I18" s="154" t="s">
         <v>121</v>
       </c>
-      <c r="J18" s="288"/>
-      <c r="K18" s="288"/>
-      <c r="L18" s="288"/>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
       <c r="M18" s="183"/>
       <c r="N18" s="191" t="s">
         <v>315</v>
@@ -25117,14 +25190,14 @@
       <c r="O18" s="191" t="s">
         <v>348</v>
       </c>
-      <c r="P18" s="288"/>
+      <c r="P18" s="283"/>
       <c r="Q18" s="193" t="s">
         <v>127</v>
       </c>
       <c r="R18" s="193" t="s">
         <v>128</v>
       </c>
-      <c r="S18" s="288"/>
+      <c r="S18" s="283"/>
       <c r="T18" s="200"/>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -25140,26 +25213,26 @@
       <c r="F19" s="192" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="288"/>
+      <c r="G19" s="283"/>
       <c r="H19" s="192" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="288"/>
-      <c r="J19" s="288"/>
-      <c r="K19" s="288"/>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
       <c r="L19" s="154" t="s">
         <v>126</v>
       </c>
-      <c r="M19" s="288"/>
+      <c r="M19" s="283"/>
       <c r="N19" s="192" t="s">
         <v>249</v>
       </c>
-      <c r="O19" s="288"/>
+      <c r="O19" s="283"/>
       <c r="P19" s="184"/>
       <c r="Q19" s="193" t="s">
         <v>132</v>
       </c>
-      <c r="R19" s="288"/>
+      <c r="R19" s="283"/>
       <c r="S19" s="192"/>
       <c r="T19" s="200"/>
     </row>
@@ -25172,29 +25245,29 @@
       </c>
       <c r="C20" s="193"/>
       <c r="D20" s="193"/>
-      <c r="E20" s="288"/>
+      <c r="E20" s="283"/>
       <c r="F20" s="192" t="s">
         <v>282</v>
       </c>
-      <c r="G20" s="288"/>
+      <c r="G20" s="283"/>
       <c r="H20" s="192" t="s">
         <v>134</v>
       </c>
-      <c r="I20" s="288"/>
-      <c r="J20" s="288"/>
-      <c r="K20" s="288"/>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
       <c r="L20" s="192" t="s">
         <v>248</v>
       </c>
-      <c r="M20" s="288"/>
+      <c r="M20" s="283"/>
       <c r="N20" s="194"/>
-      <c r="O20" s="288"/>
+      <c r="O20" s="283"/>
       <c r="P20" s="184"/>
       <c r="Q20" s="181" t="s">
         <v>135</v>
       </c>
-      <c r="R20" s="288"/>
-      <c r="S20" s="288"/>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
       <c r="T20" s="195"/>
     </row>
     <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
@@ -25211,43 +25284,43 @@
         <v>136</v>
       </c>
       <c r="H21" s="193"/>
-      <c r="I21" s="288"/>
-      <c r="J21" s="288"/>
-      <c r="K21" s="288"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
       <c r="L21" s="192" t="s">
         <v>250</v>
       </c>
-      <c r="M21" s="288"/>
-      <c r="O21" s="288"/>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
       <c r="P21" s="184"/>
       <c r="Q21" s="274"/>
-      <c r="R21" s="287">
+      <c r="R21" s="282">
         <v>3</v>
       </c>
-      <c r="S21" s="288"/>
+      <c r="S21" s="283"/>
       <c r="T21" s="195"/>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="146">
         <v>20</v>
       </c>
-      <c r="B22" s="288"/>
+      <c r="B22" s="283"/>
       <c r="C22" s="193"/>
       <c r="D22" s="192"/>
       <c r="E22" s="193"/>
       <c r="F22" s="192"/>
-      <c r="G22" s="288"/>
-      <c r="H22" s="288"/>
-      <c r="I22" s="288"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
       <c r="J22" s="246"/>
-      <c r="K22" s="288"/>
+      <c r="K22" s="283"/>
       <c r="L22" s="191" t="s">
         <v>349</v>
       </c>
-      <c r="M22" s="288"/>
+      <c r="M22" s="283"/>
       <c r="N22" s="192"/>
-      <c r="O22" s="288"/>
-      <c r="P22" s="288"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
       <c r="Q22" s="154" t="s">
         <v>139</v>
       </c>
@@ -25270,27 +25343,27 @@
       <c r="D23" s="192"/>
       <c r="E23" s="193"/>
       <c r="F23" s="193"/>
-      <c r="G23" s="288"/>
+      <c r="G23" s="283"/>
       <c r="H23" s="139">
         <v>2</v>
       </c>
-      <c r="I23" s="288"/>
-      <c r="J23" s="288"/>
-      <c r="K23" s="288"/>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
       <c r="L23" s="191" t="s">
         <v>350</v>
       </c>
-      <c r="M23" s="288"/>
+      <c r="M23" s="283"/>
       <c r="N23" s="192"/>
-      <c r="O23" s="288"/>
-      <c r="P23" s="288"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
       <c r="Q23" s="191" t="s">
         <v>145</v>
       </c>
       <c r="R23" s="193" t="s">
         <v>146</v>
       </c>
-      <c r="S23" s="288"/>
+      <c r="S23" s="283"/>
       <c r="T23" s="200"/>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -25303,28 +25376,28 @@
       <c r="C24" s="193"/>
       <c r="D24" s="192"/>
       <c r="E24" s="193"/>
-      <c r="F24" s="288"/>
-      <c r="G24" s="288"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
       <c r="H24" s="154" t="s">
         <v>147</v>
       </c>
-      <c r="I24" s="288"/>
-      <c r="J24" s="288"/>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
       <c r="K24" s="193"/>
       <c r="L24" s="193" t="s">
         <v>148</v>
       </c>
-      <c r="M24" s="288"/>
+      <c r="M24" s="283"/>
       <c r="N24" s="192"/>
-      <c r="O24" s="288"/>
-      <c r="P24" s="288"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
       <c r="Q24" s="191" t="s">
         <v>149</v>
       </c>
       <c r="R24" s="193" t="s">
         <v>256</v>
       </c>
-      <c r="S24" s="288"/>
+      <c r="S24" s="283"/>
       <c r="T24" s="200"/>
     </row>
     <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
@@ -25340,76 +25413,76 @@
       <c r="F25" s="193" t="s">
         <v>150</v>
       </c>
-      <c r="G25" s="288"/>
+      <c r="G25" s="283"/>
       <c r="H25" s="192" t="s">
         <v>151</v>
       </c>
-      <c r="I25" s="288"/>
+      <c r="I25" s="283"/>
       <c r="J25" s="274"/>
-      <c r="K25" s="288"/>
+      <c r="K25" s="283"/>
       <c r="L25" s="192" t="s">
         <v>143</v>
       </c>
-      <c r="M25" s="288"/>
+      <c r="M25" s="283"/>
       <c r="N25" s="192"/>
-      <c r="O25" s="288"/>
-      <c r="P25" s="288"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
       <c r="Q25" s="191" t="s">
         <v>153</v>
       </c>
-      <c r="R25" s="288"/>
-      <c r="S25" s="288"/>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
       <c r="T25" s="200"/>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="146">
         <v>24</v>
       </c>
-      <c r="B26" s="288"/>
+      <c r="B26" s="283"/>
       <c r="C26" s="192"/>
       <c r="D26" s="192"/>
       <c r="E26" s="193"/>
       <c r="F26" s="193" t="s">
         <v>154</v>
       </c>
-      <c r="G26" s="288"/>
+      <c r="G26" s="283"/>
       <c r="H26" s="192"/>
-      <c r="I26" s="288"/>
-      <c r="J26" s="288"/>
-      <c r="K26" s="288"/>
-      <c r="M26" s="288"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
       <c r="N26" s="192"/>
-      <c r="O26" s="288"/>
-      <c r="P26" s="288"/>
+      <c r="O26" s="283"/>
+      <c r="P26" s="283"/>
       <c r="Q26" s="191" t="s">
         <v>331</v>
       </c>
-      <c r="R26" s="288"/>
-      <c r="S26" s="288"/>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
       <c r="T26" s="200"/>
     </row>
     <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="146">
         <v>25</v>
       </c>
-      <c r="B27" s="288"/>
+      <c r="B27" s="283"/>
       <c r="C27" s="192"/>
       <c r="D27" s="192"/>
       <c r="E27" s="193"/>
-      <c r="F27" s="288"/>
-      <c r="G27" s="288"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
       <c r="H27" s="139">
         <v>1</v>
       </c>
-      <c r="I27" s="288"/>
+      <c r="I27" s="283"/>
       <c r="J27" s="192"/>
-      <c r="K27" s="288"/>
+      <c r="K27" s="283"/>
       <c r="L27" s="139"/>
       <c r="M27" s="183"/>
       <c r="N27" s="139" t="s">
         <v>155</v>
       </c>
-      <c r="O27" s="288"/>
+      <c r="O27" s="283"/>
       <c r="P27" s="274"/>
       <c r="Q27" s="193" t="s">
         <v>156</v>
@@ -25425,77 +25498,77 @@
         <v>26</v>
       </c>
       <c r="B28" s="139"/>
-      <c r="C28" s="288"/>
+      <c r="C28" s="283"/>
       <c r="D28" s="192"/>
-      <c r="E28" s="288"/>
-      <c r="F28" s="288"/>
-      <c r="G28" s="288"/>
-      <c r="H28" s="288"/>
-      <c r="I28" s="288"/>
-      <c r="J28" s="288"/>
-      <c r="K28" s="288"/>
-      <c r="L28" s="287" t="s">
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
         <v>225</v>
       </c>
-      <c r="M28" s="288"/>
+      <c r="M28" s="283"/>
       <c r="N28" s="181" t="s">
         <v>110</v>
       </c>
-      <c r="O28" s="288"/>
-      <c r="P28" s="288"/>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
       <c r="R28" s="196"/>
-      <c r="S28" s="288"/>
+      <c r="S28" s="283"/>
       <c r="T28" s="200"/>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="146">
         <v>27</v>
       </c>
-      <c r="B29" s="288"/>
-      <c r="C29" s="288"/>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
       <c r="D29" s="193"/>
-      <c r="E29" s="288"/>
-      <c r="F29" s="288"/>
-      <c r="G29" s="288"/>
-      <c r="H29" s="288"/>
-      <c r="I29" s="288"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
       <c r="J29" s="192"/>
       <c r="K29" s="139"/>
-      <c r="L29" s="288"/>
-      <c r="M29" s="288"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
       <c r="N29" s="193" t="s">
         <v>158</v>
       </c>
-      <c r="O29" s="288"/>
+      <c r="O29" s="283"/>
       <c r="P29" s="192"/>
       <c r="Q29" s="139"/>
-      <c r="R29" s="288"/>
-      <c r="S29" s="288"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
       <c r="T29" s="200"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="146">
         <v>28</v>
       </c>
-      <c r="B30" s="288"/>
+      <c r="B30" s="283"/>
       <c r="C30" s="139"/>
       <c r="D30" s="139"/>
-      <c r="E30" s="288"/>
+      <c r="E30" s="283"/>
       <c r="F30" s="139"/>
       <c r="G30" s="139"/>
       <c r="H30" s="193"/>
-      <c r="I30" s="288"/>
+      <c r="I30" s="283"/>
       <c r="J30" s="192"/>
       <c r="K30" s="139"/>
-      <c r="L30" s="288"/>
-      <c r="M30" s="288"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
       <c r="N30" s="193" t="s">
         <v>159</v>
       </c>
-      <c r="O30" s="288"/>
-      <c r="P30" s="288"/>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
       <c r="Q30" s="139"/>
-      <c r="R30" s="288"/>
+      <c r="R30" s="283"/>
       <c r="S30" s="192"/>
       <c r="T30" s="200"/>
     </row>
@@ -25503,28 +25576,28 @@
       <c r="A31" s="146">
         <v>29</v>
       </c>
-      <c r="B31" s="288"/>
+      <c r="B31" s="283"/>
       <c r="C31" s="139"/>
       <c r="D31" s="139"/>
-      <c r="E31" s="288"/>
+      <c r="E31" s="283"/>
       <c r="F31" s="139"/>
       <c r="G31" s="139"/>
-      <c r="H31" s="288"/>
-      <c r="I31" s="288"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
       <c r="J31" s="192"/>
-      <c r="K31" s="288"/>
+      <c r="K31" s="283"/>
       <c r="L31" s="193" t="s">
         <v>157</v>
       </c>
-      <c r="M31" s="288"/>
+      <c r="M31" s="283"/>
       <c r="N31" s="139"/>
-      <c r="O31" s="288"/>
-      <c r="P31" s="288"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
       <c r="Q31" s="139" t="s">
         <v>160</v>
       </c>
-      <c r="R31" s="288"/>
-      <c r="S31" s="288"/>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
       <c r="T31" s="200"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -25767,14 +25840,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -25999,19 +26072,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26033,7 +26106,2247 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D91EF2C-BFD5-4484-8751-A8A329463013}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="280" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="280" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="284" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="284"/>
+      <c r="F2" s="280" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="280" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="281" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="280" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="280" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="281" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="281" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="281" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="285" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="285"/>
+      <c r="P2" s="280" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="280" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="280" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="280" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="286" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="288" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="289" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="288"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26581,10 +28894,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -26609,10 +28922,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -28018,14 +30331,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -28250,19 +30563,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -28284,7 +30597,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -28837,10 +31150,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -28865,10 +31178,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -30272,14 +32585,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30504,19 +32817,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30538,7 +32851,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31092,10 +33405,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -31120,10 +33433,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -32527,14 +34840,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -32759,19 +35072,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -32793,7 +35106,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -33345,10 +35658,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -33373,10 +35686,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -34780,14 +37093,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -35012,19 +37325,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -35046,7 +37359,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -35599,10 +37912,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -35627,10 +37940,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -37034,14 +39347,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37266,19 +39579,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37300,7 +39613,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -37852,10 +40165,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -37880,10 +40193,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -39287,14 +41600,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39519,19 +41832,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39553,7 +41866,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -40103,10 +42416,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -40131,10 +42444,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -41538,14 +43851,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -41770,19 +44083,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -41804,7 +44117,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42354,10 +44667,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="280" t="s">
+      <c r="D2" s="284" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="280"/>
+      <c r="E2" s="284"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -42382,10 +44695,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="281" t="s">
+      <c r="N2" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="281"/>
+      <c r="O2" s="285"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -43789,14 +46102,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="282" t="s">
+      <c r="L41" s="286" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="282"/>
-      <c r="N41" s="282"/>
-      <c r="O41" s="282"/>
-      <c r="P41" s="282"/>
-      <c r="Q41" s="283"/>
+      <c r="M41" s="286"/>
+      <c r="N41" s="286"/>
+      <c r="O41" s="286"/>
+      <c r="P41" s="286"/>
+      <c r="Q41" s="287"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44021,19 +46334,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="284" t="s">
+      <c r="A49" s="288" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="285" t="s">
+      <c r="B49" s="289" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="285"/>
-      <c r="D49" s="285"/>
-      <c r="E49" s="285"/>
-      <c r="F49" s="286"/>
-      <c r="G49" s="286"/>
-      <c r="H49" s="286"/>
-      <c r="I49" s="286"/>
+      <c r="C49" s="289"/>
+      <c r="D49" s="289"/>
+      <c r="E49" s="289"/>
+      <c r="F49" s="290"/>
+      <c r="G49" s="290"/>
+      <c r="H49" s="290"/>
+      <c r="I49" s="290"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44055,7 +46368,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="284"/>
+      <c r="A50" s="288"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA93AB29-4AF2-4657-AC12-589F24B4CCBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7645E71F-4AE1-448E-BD6C-031EB59044CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -32,6 +32,7 @@
     <sheet name="17" sheetId="90" r:id="rId17"/>
     <sheet name="18" sheetId="91" r:id="rId18"/>
     <sheet name="19" sheetId="92" r:id="rId19"/>
+    <sheet name="20" sheetId="93" r:id="rId20"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -809,6 +810,69 @@
 </comments>
 </file>
 
+<file path=xl/comments20.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{ABC106DE-8665-4312-BFA0-994518E35A40}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{1273198A-1FED-4FF9-97D8-5C79CC352C45}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1251,7 +1315,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5818" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6122" uniqueCount="352">
   <si>
     <t>№</t>
   </si>
@@ -2832,7 +2896,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="291">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3647,6 +3711,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4128,10 +4198,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4156,10 +4226,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5562,14 +5632,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5794,19 +5864,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5828,7 +5898,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6370,10 +6440,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6398,10 +6468,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7810,14 +7880,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8047,19 +8117,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8082,7 +8152,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8681,10 +8751,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8709,10 +8779,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10114,14 +10184,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10346,19 +10416,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10380,7 +10450,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10927,10 +10997,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -10955,10 +11025,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12360,14 +12430,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12592,19 +12662,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12626,7 +12696,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13173,10 +13243,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13201,10 +13271,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14606,14 +14676,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14838,19 +14908,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14872,7 +14942,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15419,10 +15489,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15447,10 +15517,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16852,14 +16922,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17084,19 +17154,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17118,7 +17188,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17665,10 +17735,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17693,10 +17763,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19098,14 +19168,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19330,19 +19400,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19364,7 +19434,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -19915,10 +19985,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -19943,10 +20013,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21348,14 +21418,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21580,19 +21650,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21614,7 +21684,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22164,10 +22234,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22192,10 +22262,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23597,14 +23667,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -23829,19 +23899,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -23863,7 +23933,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24413,10 +24483,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24441,10 +24511,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -25840,14 +25910,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26072,19 +26142,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26106,7 +26176,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26654,10 +26724,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -26682,10 +26752,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28080,14 +28150,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28312,19 +28382,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28346,7 +28416,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -28894,10 +28964,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -28922,10 +28992,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30331,14 +30401,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30563,19 +30633,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30597,7 +30667,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31055,6 +31125,2246 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7800A18-1E39-4A30-A7E9-0922B0679383}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="284" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="284" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="286" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="286"/>
+      <c r="F2" s="284" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="284" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="285" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="284" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="284" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="285" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="285" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="285" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="287" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="287"/>
+      <c r="P2" s="284" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="284" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="284" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="284" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="288" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="290" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="291" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="290"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31150,10 +33460,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -31178,10 +33488,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -32585,14 +34895,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -32817,19 +35127,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -32851,7 +35161,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -33405,10 +35715,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -33433,10 +35743,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -34840,14 +37150,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -35072,19 +37382,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -35106,7 +37416,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -35658,10 +37968,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -35686,10 +37996,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -37093,14 +39403,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37325,19 +39635,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37359,7 +39669,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -37912,10 +40222,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -37940,10 +40250,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -39347,14 +41657,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39579,19 +41889,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39613,7 +41923,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -40165,10 +42475,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -40193,10 +42503,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -41600,14 +43910,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -41832,19 +44142,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -41866,7 +44176,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42416,10 +44726,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -42444,10 +44754,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -43851,14 +46161,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44083,19 +46393,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44117,7 +46427,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44667,10 +46977,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="284" t="s">
+      <c r="D2" s="286" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="284"/>
+      <c r="E2" s="286"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -44695,10 +47005,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="285" t="s">
+      <c r="N2" s="287" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="285"/>
+      <c r="O2" s="287"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -46102,14 +48412,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="286" t="s">
+      <c r="L41" s="288" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="286"/>
-      <c r="N41" s="286"/>
-      <c r="O41" s="286"/>
-      <c r="P41" s="286"/>
-      <c r="Q41" s="287"/>
+      <c r="M41" s="288"/>
+      <c r="N41" s="288"/>
+      <c r="O41" s="288"/>
+      <c r="P41" s="288"/>
+      <c r="Q41" s="289"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46334,19 +48644,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="288" t="s">
+      <c r="A49" s="290" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="289" t="s">
+      <c r="B49" s="291" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="289"/>
-      <c r="D49" s="289"/>
-      <c r="E49" s="289"/>
-      <c r="F49" s="290"/>
-      <c r="G49" s="290"/>
-      <c r="H49" s="290"/>
-      <c r="I49" s="290"/>
+      <c r="C49" s="291"/>
+      <c r="D49" s="291"/>
+      <c r="E49" s="291"/>
+      <c r="F49" s="292"/>
+      <c r="G49" s="292"/>
+      <c r="H49" s="292"/>
+      <c r="I49" s="292"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46368,7 +48678,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="288"/>
+      <c r="A50" s="290"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7645E71F-4AE1-448E-BD6C-031EB59044CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9F7F31-38F9-429C-9B9D-A7D0F8D19D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -33,6 +33,7 @@
     <sheet name="18" sheetId="91" r:id="rId18"/>
     <sheet name="19" sheetId="92" r:id="rId19"/>
     <sheet name="20" sheetId="93" r:id="rId20"/>
+    <sheet name="21" sheetId="94" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -873,6 +874,69 @@
 </comments>
 </file>
 
+<file path=xl/comments21.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{F26236F6-A3BA-4673-AF28-2932ECBA8549}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{51B92F4E-0830-4AE0-A780-842477A31FA3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1315,7 +1379,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6122" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6426" uniqueCount="352">
   <si>
     <t>№</t>
   </si>
@@ -2896,7 +2960,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="293">
+  <cellXfs count="295">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3717,6 +3781,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4198,10 +4268,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4226,10 +4296,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5632,14 +5702,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5864,19 +5934,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5898,7 +5968,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6440,10 +6510,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6468,10 +6538,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7880,14 +7950,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8117,19 +8187,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8152,7 +8222,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8751,10 +8821,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8779,10 +8849,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10184,14 +10254,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10416,19 +10486,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10450,7 +10520,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -10997,10 +11067,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11025,10 +11095,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12430,14 +12500,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12662,19 +12732,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12696,7 +12766,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13243,10 +13313,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13271,10 +13341,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14676,14 +14746,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14908,19 +14978,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -14942,7 +15012,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15489,10 +15559,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15517,10 +15587,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16922,14 +16992,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17154,19 +17224,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17188,7 +17258,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17735,10 +17805,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17763,10 +17833,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19168,14 +19238,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19400,19 +19470,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19434,7 +19504,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -19985,10 +20055,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20013,10 +20083,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21418,14 +21488,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21650,19 +21720,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21684,7 +21754,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22234,10 +22304,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22262,10 +22332,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23667,14 +23737,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -23899,19 +23969,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -23933,7 +24003,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24483,10 +24553,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24511,10 +24581,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -25910,14 +25980,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26142,19 +26212,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26176,7 +26246,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26724,10 +26794,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -26752,10 +26822,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28150,14 +28220,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28382,19 +28452,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28416,7 +28486,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -28964,10 +29034,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -28992,10 +29062,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30401,14 +30471,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30633,19 +30703,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30667,7 +30737,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31220,10 +31290,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31248,10 +31318,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -32646,14 +32716,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -32878,19 +32948,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -32912,7 +32982,2247 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA72948F-12F3-4979-BDB8-6392E09A3342}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="286" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="286" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="288" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="288"/>
+      <c r="F2" s="286" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="286" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="287" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="286" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="286" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="287" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="287" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="287" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="289" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="289"/>
+      <c r="P2" s="286" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="286" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="286" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="286" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="290" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="292" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="293" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="292"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33460,10 +35770,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -33488,10 +35798,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -34895,14 +37205,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -35127,19 +37437,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -35161,7 +37471,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -35715,10 +38025,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -35743,10 +38053,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -37150,14 +39460,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37382,19 +39692,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37416,7 +39726,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -37968,10 +40278,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -37996,10 +40306,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -39403,14 +41713,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39635,19 +41945,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39669,7 +41979,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -40222,10 +42532,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -40250,10 +42560,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -41657,14 +43967,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -41889,19 +44199,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -41923,7 +44233,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42475,10 +44785,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -42503,10 +44813,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -43910,14 +46220,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44142,19 +46452,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44176,7 +46486,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44726,10 +47036,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -44754,10 +47064,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -46161,14 +48471,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46393,19 +48703,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46427,7 +48737,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -46977,10 +49287,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="286" t="s">
+      <c r="D2" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="286"/>
+      <c r="E2" s="288"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -47005,10 +49315,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="287" t="s">
+      <c r="N2" s="289" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="287"/>
+      <c r="O2" s="289"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -48412,14 +50722,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="288" t="s">
+      <c r="L41" s="290" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="288"/>
-      <c r="N41" s="288"/>
-      <c r="O41" s="288"/>
-      <c r="P41" s="288"/>
-      <c r="Q41" s="289"/>
+      <c r="M41" s="290"/>
+      <c r="N41" s="290"/>
+      <c r="O41" s="290"/>
+      <c r="P41" s="290"/>
+      <c r="Q41" s="291"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48644,19 +50954,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="290" t="s">
+      <c r="A49" s="292" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="291" t="s">
+      <c r="B49" s="293" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="291"/>
-      <c r="D49" s="291"/>
-      <c r="E49" s="291"/>
-      <c r="F49" s="292"/>
-      <c r="G49" s="292"/>
-      <c r="H49" s="292"/>
-      <c r="I49" s="292"/>
+      <c r="C49" s="293"/>
+      <c r="D49" s="293"/>
+      <c r="E49" s="293"/>
+      <c r="F49" s="294"/>
+      <c r="G49" s="294"/>
+      <c r="H49" s="294"/>
+      <c r="I49" s="294"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -48678,7 +50988,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="290"/>
+      <c r="A50" s="292"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9F7F31-38F9-429C-9B9D-A7D0F8D19D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085C518-E38C-4765-B215-0F8EF4DF13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -34,6 +34,7 @@
     <sheet name="19" sheetId="92" r:id="rId19"/>
     <sheet name="20" sheetId="93" r:id="rId20"/>
     <sheet name="21" sheetId="94" r:id="rId21"/>
+    <sheet name="22" sheetId="95" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -937,6 +938,69 @@
 </comments>
 </file>
 
+<file path=xl/comments22.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{01068D76-C2D7-438D-BD3F-2F2C3011B0A0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{51735C04-7A0A-4558-8D5E-2DFE9CC13FC1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1379,7 +1443,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6426" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6730" uniqueCount="352">
   <si>
     <t>№</t>
   </si>
@@ -2960,7 +3024,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="295">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3787,6 +3851,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4268,10 +4338,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4296,10 +4366,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5702,14 +5772,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -5934,19 +6004,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -5968,7 +6038,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6510,10 +6580,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6538,10 +6608,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -7950,14 +8020,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8187,19 +8257,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8222,7 +8292,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8821,10 +8891,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8849,10 +8919,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10254,14 +10324,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10486,19 +10556,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10520,7 +10590,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11067,10 +11137,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11095,10 +11165,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12500,14 +12570,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12732,19 +12802,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12766,7 +12836,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13313,10 +13383,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13341,10 +13411,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14746,14 +14816,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -14978,19 +15048,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15012,7 +15082,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15559,10 +15629,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15587,10 +15657,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -16992,14 +17062,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17224,19 +17294,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17258,7 +17328,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17805,10 +17875,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17833,10 +17903,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19238,14 +19308,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19470,19 +19540,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19504,7 +19574,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20055,10 +20125,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20083,10 +20153,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21488,14 +21558,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21720,19 +21790,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21754,7 +21824,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22304,10 +22374,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22332,10 +22402,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23737,14 +23807,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -23969,19 +24039,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24003,7 +24073,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24553,10 +24623,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24581,10 +24651,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -25980,14 +26050,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26212,19 +26282,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26246,7 +26316,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26794,10 +26864,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -26822,10 +26892,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28220,14 +28290,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28452,19 +28522,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28486,7 +28556,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29034,10 +29104,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29062,10 +29132,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30471,14 +30541,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30703,19 +30773,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30737,7 +30807,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31290,10 +31360,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31318,10 +31388,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -32716,14 +32786,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -32948,19 +33018,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -32982,7 +33052,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33530,10 +33600,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33558,10 +33628,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -34956,14 +35026,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35188,19 +35258,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35222,7 +35292,2247 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13517E4-767D-472D-8205-3BE035067356}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="288" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="288" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="290" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="290"/>
+      <c r="F2" s="288" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="288" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="289" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="288" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="288" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="289" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="289" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="289" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="291" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="291"/>
+      <c r="P2" s="288" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="288" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="288" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="288" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="292" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="294" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="295" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="294"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -35770,10 +38080,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -35798,10 +38108,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -37205,14 +39515,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -37437,19 +39747,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -37471,7 +39781,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -38025,10 +40335,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -38053,10 +40363,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -39460,14 +41770,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39692,19 +42002,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39726,7 +42036,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -40278,10 +42588,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -40306,10 +42616,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -41713,14 +44023,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -41945,19 +44255,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -41979,7 +44289,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42532,10 +44842,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -42560,10 +44870,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -43967,14 +46277,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44199,19 +46509,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44233,7 +46543,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44785,10 +47095,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -44813,10 +47123,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -46220,14 +48530,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46452,19 +48762,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46486,7 +48796,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -47036,10 +49346,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -47064,10 +49374,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -48471,14 +50781,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48703,19 +51013,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -48737,7 +51047,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49287,10 +51597,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="290" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="288"/>
+      <c r="E2" s="290"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -49315,10 +51625,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="289" t="s">
+      <c r="N2" s="291" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="289"/>
+      <c r="O2" s="291"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -50722,14 +53032,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="290" t="s">
+      <c r="L41" s="292" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="290"/>
-      <c r="N41" s="290"/>
-      <c r="O41" s="290"/>
-      <c r="P41" s="290"/>
-      <c r="Q41" s="291"/>
+      <c r="M41" s="292"/>
+      <c r="N41" s="292"/>
+      <c r="O41" s="292"/>
+      <c r="P41" s="292"/>
+      <c r="Q41" s="293"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -50954,19 +53264,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="292" t="s">
+      <c r="A49" s="294" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="293" t="s">
+      <c r="B49" s="295" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="293"/>
-      <c r="D49" s="293"/>
-      <c r="E49" s="293"/>
-      <c r="F49" s="294"/>
-      <c r="G49" s="294"/>
-      <c r="H49" s="294"/>
-      <c r="I49" s="294"/>
+      <c r="C49" s="295"/>
+      <c r="D49" s="295"/>
+      <c r="E49" s="295"/>
+      <c r="F49" s="296"/>
+      <c r="G49" s="296"/>
+      <c r="H49" s="296"/>
+      <c r="I49" s="296"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -50988,7 +53298,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="292"/>
+      <c r="A50" s="294"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8085C518-E38C-4765-B215-0F8EF4DF13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A4C18-15BD-431A-B116-820DEAA24165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="20" sheetId="93" r:id="rId20"/>
     <sheet name="21" sheetId="94" r:id="rId21"/>
     <sheet name="22" sheetId="95" r:id="rId22"/>
+    <sheet name="23" sheetId="96" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1001,6 +1002,69 @@
 </comments>
 </file>
 
+<file path=xl/comments23.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{7BC7663E-41C3-4D5C-AEDC-3D7FFBBD12FD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{A1F5E7DE-5494-43F6-A109-848FC954EC22}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1443,7 +1507,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6730" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7034" uniqueCount="352">
   <si>
     <t>№</t>
   </si>
@@ -3024,7 +3088,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="297">
+  <cellXfs count="299">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3857,6 +3921,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4338,10 +4408,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4366,10 +4436,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5772,14 +5842,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6004,19 +6074,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6038,7 +6108,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6580,10 +6650,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6608,10 +6678,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8020,14 +8090,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8257,19 +8327,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8292,7 +8362,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8891,10 +8961,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8919,10 +8989,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10324,14 +10394,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10556,19 +10626,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10590,7 +10660,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11137,10 +11207,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11165,10 +11235,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12570,14 +12640,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12802,19 +12872,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12836,7 +12906,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13383,10 +13453,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13411,10 +13481,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14816,14 +14886,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15048,19 +15118,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15082,7 +15152,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15629,10 +15699,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15657,10 +15727,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17062,14 +17132,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17294,19 +17364,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17328,7 +17398,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17875,10 +17945,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17903,10 +17973,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19308,14 +19378,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19540,19 +19610,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19574,7 +19644,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20125,10 +20195,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20153,10 +20223,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21558,14 +21628,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21790,19 +21860,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21824,7 +21894,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22374,10 +22444,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22402,10 +22472,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23807,14 +23877,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24039,19 +24109,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24073,7 +24143,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24623,10 +24693,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24651,10 +24721,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26050,14 +26120,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26282,19 +26352,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26316,7 +26386,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26864,10 +26934,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -26892,10 +26962,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28290,14 +28360,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28522,19 +28592,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28556,7 +28626,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29104,10 +29174,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29132,10 +29202,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30541,14 +30611,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30773,19 +30843,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30807,7 +30877,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31360,10 +31430,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31388,10 +31458,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -32786,14 +32856,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33018,19 +33088,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33052,7 +33122,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33600,10 +33670,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33628,10 +33698,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35026,14 +35096,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35258,19 +35328,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35292,7 +35362,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -35840,10 +35910,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -35868,10 +35938,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37266,14 +37336,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37498,19 +37568,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37532,7 +37602,2247 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ABC156-14C1-4D92-B9E5-84603C681761}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="290" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="290" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="292" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="292"/>
+      <c r="F2" s="290" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="290" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="291" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="290" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="290" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="291" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="291" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="291" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="293" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="293"/>
+      <c r="P2" s="290" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="290" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="290" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="290" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>345</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>122</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>128</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>132</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>156</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="294" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="296" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="297" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="296"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38080,10 +40390,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -38108,10 +40418,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -39515,14 +41825,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -39747,19 +42057,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -39781,7 +42091,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -40335,10 +42645,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -40363,10 +42673,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -41770,14 +44080,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -42002,19 +44312,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -42036,7 +44346,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42588,10 +44898,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -42616,10 +44926,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -44023,14 +46333,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44255,19 +46565,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44289,7 +46599,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44842,10 +47152,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -44870,10 +47180,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -46277,14 +48587,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46509,19 +48819,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46543,7 +48853,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -47095,10 +49405,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -47123,10 +49433,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -48530,14 +50840,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48762,19 +51072,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -48796,7 +51106,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49346,10 +51656,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -49374,10 +51684,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -50781,14 +53091,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51013,19 +53323,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51047,7 +53357,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51597,10 +53907,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="292" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="290"/>
+      <c r="E2" s="292"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -51625,10 +53935,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="291" t="s">
+      <c r="N2" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="291"/>
+      <c r="O2" s="293"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -53032,14 +55342,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="292" t="s">
+      <c r="L41" s="294" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="292"/>
-      <c r="N41" s="292"/>
-      <c r="O41" s="292"/>
-      <c r="P41" s="292"/>
-      <c r="Q41" s="293"/>
+      <c r="M41" s="294"/>
+      <c r="N41" s="294"/>
+      <c r="O41" s="294"/>
+      <c r="P41" s="294"/>
+      <c r="Q41" s="295"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53264,19 +55574,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="294" t="s">
+      <c r="A49" s="296" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="295" t="s">
+      <c r="B49" s="297" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="295"/>
-      <c r="D49" s="295"/>
-      <c r="E49" s="295"/>
-      <c r="F49" s="296"/>
-      <c r="G49" s="296"/>
-      <c r="H49" s="296"/>
-      <c r="I49" s="296"/>
+      <c r="C49" s="297"/>
+      <c r="D49" s="297"/>
+      <c r="E49" s="297"/>
+      <c r="F49" s="298"/>
+      <c r="G49" s="298"/>
+      <c r="H49" s="298"/>
+      <c r="I49" s="298"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53298,7 +55608,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="294"/>
+      <c r="A50" s="296"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A4C18-15BD-431A-B116-820DEAA24165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF7C96A-1A30-4D9C-AE75-3B40A1B0813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -36,6 +36,7 @@
     <sheet name="21" sheetId="94" r:id="rId21"/>
     <sheet name="22" sheetId="95" r:id="rId22"/>
     <sheet name="23" sheetId="96" r:id="rId23"/>
+    <sheet name="24" sheetId="97" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1065,6 +1066,69 @@
 </comments>
 </file>
 
+<file path=xl/comments24.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{374D61BB-323C-48A2-AC80-39513A5D9760}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{ED0CC90D-2D9F-40C4-ADF5-6B73AEC151CD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1507,7 +1571,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7034" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7338" uniqueCount="359">
   <si>
     <t>№</t>
   </si>
@@ -2564,6 +2628,27 @@
   <si>
     <t>60-13-452BD12н</t>
   </si>
+  <si>
+    <t>60-13-944BI12</t>
+  </si>
+  <si>
+    <t>60-13-115BJ12н</t>
+  </si>
+  <si>
+    <t>60-13-830BI12</t>
+  </si>
+  <si>
+    <t>60-13-058BJ12</t>
+  </si>
+  <si>
+    <t>60-20-807BI12</t>
+  </si>
+  <si>
+    <t>60-20-884BI12</t>
+  </si>
+  <si>
+    <t>60-20-594BJ12</t>
+  </si>
 </sst>
 </file>
 
@@ -3088,7 +3173,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3927,6 +4012,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4408,10 +4499,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4436,10 +4527,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5842,14 +5933,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6074,19 +6165,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6108,7 +6199,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6650,10 +6741,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6678,10 +6769,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8090,14 +8181,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8327,19 +8418,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8362,7 +8453,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -8961,10 +9052,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -8989,10 +9080,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10394,14 +10485,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10626,19 +10717,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10660,7 +10751,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11207,10 +11298,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11235,10 +11326,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12640,14 +12731,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12872,19 +12963,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12906,7 +12997,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13453,10 +13544,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13481,10 +13572,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14886,14 +14977,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15118,19 +15209,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15152,7 +15243,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15699,10 +15790,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15727,10 +15818,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17132,14 +17223,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17364,19 +17455,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17398,7 +17489,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -17945,10 +18036,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -17973,10 +18064,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19378,14 +19469,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19610,19 +19701,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19644,7 +19735,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20195,10 +20286,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20223,10 +20314,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21628,14 +21719,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21860,19 +21951,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21894,7 +21985,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22444,10 +22535,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22472,10 +22563,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23877,14 +23968,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24109,19 +24200,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24143,7 +24234,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24693,10 +24784,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24721,10 +24812,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26120,14 +26211,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26352,19 +26443,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26386,7 +26477,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -26934,10 +27025,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -26962,10 +27053,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28360,14 +28451,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28592,19 +28683,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28626,7 +28717,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29174,10 +29265,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29202,10 +29293,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30611,14 +30702,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30843,19 +30934,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30877,7 +30968,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31430,10 +31521,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31458,10 +31549,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -32856,14 +32947,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33088,19 +33179,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33122,7 +33213,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33670,10 +33761,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33698,10 +33789,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35096,14 +35187,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35328,19 +35419,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35362,7 +35453,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -35910,10 +36001,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -35938,10 +36029,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37336,14 +37427,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37568,19 +37659,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37602,7 +37693,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38150,10 +38241,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38178,10 +38269,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39576,14 +39667,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -39808,19 +39899,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -39842,7 +39933,2247 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>4</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>0</v>
+      </c>
+      <c r="J53" s="190"/>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="269"/>
+      <c r="O56" s="253"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="249" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>199</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161832FD-6616-42F7-9BC3-0C24AF2A2D32}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="292" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="292" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="294" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="294"/>
+      <c r="F2" s="292" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="292" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="293" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="292" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="292" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="293" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="293" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="293" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="295" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="295"/>
+      <c r="P2" s="292" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="292" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="292" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="292" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="192" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="192" t="s">
+        <v>230</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="191" t="s">
+        <v>333</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="192" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="192" t="s">
+        <v>234</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="192" t="s">
+        <v>258</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="192" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="192" t="s">
+        <v>235</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="192" t="s">
+        <v>236</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="191" t="s">
+        <v>334</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="192" t="s">
+        <v>240</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="192" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="192" t="s">
+        <v>242</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>351</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="191" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="191" t="s">
+        <v>290</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="191" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="191" t="s">
+        <v>337</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="193" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>338</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="283"/>
+      <c r="D13" s="191" t="s">
+        <v>339</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="191" t="s">
+        <v>340</v>
+      </c>
+      <c r="H13" s="191" t="s">
+        <v>341</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="191" t="s">
+        <v>342</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="283"/>
+      <c r="D14" s="191" t="s">
+        <v>343</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="283"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="191" t="s">
+        <v>344</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="191" t="s">
+        <v>353</v>
+      </c>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="191" t="s">
+        <v>346</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G16" s="283"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="191" t="s">
+        <v>347</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G17" s="283"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="191" t="s">
+        <v>325</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G18" s="274"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="283"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="192" t="s">
+        <v>249</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>262</v>
+      </c>
+      <c r="G20" s="283"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="192" t="s">
+        <v>248</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="194"/>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="192" t="s">
+        <v>250</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="191" t="s">
+        <v>349</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="191" t="s">
+        <v>350</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="296" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="298" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="299" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>29</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-1</v>
+      </c>
+      <c r="Q49" s="212" t="s">
+        <v>195</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="298"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40390,10 +42721,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -40418,10 +42749,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -41825,14 +44156,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -42057,19 +44388,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -42091,7 +44422,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -42645,10 +44976,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -42673,10 +45004,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -44080,14 +46411,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44312,19 +46643,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44346,7 +46677,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44898,10 +47229,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -44926,10 +47257,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -46333,14 +48664,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46565,19 +48896,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46599,7 +48930,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -47152,10 +49483,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -47180,10 +49511,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -48587,14 +50918,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48819,19 +51150,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -48853,7 +51184,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49405,10 +51736,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -49433,10 +51764,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -50840,14 +53171,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51072,19 +53403,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51106,7 +53437,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51656,10 +53987,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -51684,10 +54015,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -53091,14 +55422,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53323,19 +55654,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53357,7 +55688,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -53907,10 +56238,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="292" t="s">
+      <c r="D2" s="294" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="292"/>
+      <c r="E2" s="294"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -53935,10 +56266,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="293" t="s">
+      <c r="N2" s="295" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="293"/>
+      <c r="O2" s="295"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -55342,14 +57673,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="294" t="s">
+      <c r="L41" s="296" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="294"/>
-      <c r="N41" s="294"/>
-      <c r="O41" s="294"/>
-      <c r="P41" s="294"/>
-      <c r="Q41" s="295"/>
+      <c r="M41" s="296"/>
+      <c r="N41" s="296"/>
+      <c r="O41" s="296"/>
+      <c r="P41" s="296"/>
+      <c r="Q41" s="297"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55574,19 +57905,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="296" t="s">
+      <c r="A49" s="298" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="297" t="s">
+      <c r="B49" s="299" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="297"/>
-      <c r="D49" s="297"/>
-      <c r="E49" s="297"/>
-      <c r="F49" s="298"/>
-      <c r="G49" s="298"/>
-      <c r="H49" s="298"/>
-      <c r="I49" s="298"/>
+      <c r="C49" s="299"/>
+      <c r="D49" s="299"/>
+      <c r="E49" s="299"/>
+      <c r="F49" s="300"/>
+      <c r="G49" s="300"/>
+      <c r="H49" s="300"/>
+      <c r="I49" s="300"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55608,7 +57939,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="296"/>
+      <c r="A50" s="298"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF7C96A-1A30-4D9C-AE75-3B40A1B0813E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136C7ACA-E578-4378-AD6B-F6AD06472546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -37,6 +37,7 @@
     <sheet name="22" sheetId="95" r:id="rId22"/>
     <sheet name="23" sheetId="96" r:id="rId23"/>
     <sheet name="24" sheetId="97" r:id="rId24"/>
+    <sheet name="25" sheetId="98" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1129,6 +1130,69 @@
 </comments>
 </file>
 
+<file path=xl/comments25.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{8BD8106C-92A6-4764-B60B-FF2345F8CAB1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{4AE8BB96-9B71-43EF-BEC6-68A2834A340E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1571,7 +1635,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7338" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -2649,6 +2713,18 @@
   <si>
     <t>60-20-594BJ12</t>
   </si>
+  <si>
+    <t>60-13-115BJ12</t>
+  </si>
+  <si>
+    <t>60-13-311AT12 д/н</t>
+  </si>
+  <si>
+    <t>60-13-593BJ12</t>
+  </si>
+  <si>
+    <t>Кран 100т жоспар 30 кун, 1 ед мусоровоз ремонт</t>
+  </si>
 </sst>
 </file>
 
@@ -3173,7 +3249,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="301">
+  <cellXfs count="305">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4018,6 +4094,15 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4033,6 +4118,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="58">
     <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4499,10 +4585,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4527,10 +4613,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -5933,14 +6019,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6165,19 +6251,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6199,7 +6285,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6741,10 +6827,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6769,10 +6855,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8181,14 +8267,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8418,19 +8504,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8453,7 +8539,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9052,10 +9138,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9080,10 +9166,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10485,14 +10571,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10717,19 +10803,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10751,7 +10837,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11298,10 +11384,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11326,10 +11412,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12731,14 +12817,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -12963,19 +13049,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -12997,7 +13083,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13544,10 +13630,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13572,10 +13658,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -14977,14 +15063,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15209,19 +15295,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15243,7 +15329,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15790,10 +15876,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15818,10 +15904,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17223,14 +17309,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17455,19 +17541,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17489,7 +17575,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18036,10 +18122,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18064,10 +18150,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19469,14 +19555,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19701,19 +19787,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19735,7 +19821,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20286,10 +20372,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20314,10 +20400,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21719,14 +21805,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -21951,19 +22037,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -21985,7 +22071,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22535,10 +22621,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22563,10 +22649,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -23968,14 +24054,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24200,19 +24286,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24234,7 +24320,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24784,10 +24870,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24812,10 +24898,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26211,14 +26297,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26443,19 +26529,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26477,7 +26563,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27025,10 +27111,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27053,10 +27139,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28451,14 +28537,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28683,19 +28769,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28717,7 +28803,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29265,10 +29351,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29293,10 +29379,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30702,14 +30788,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -30934,19 +31020,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -30968,7 +31054,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31521,10 +31607,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31549,10 +31635,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -32947,14 +33033,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33179,19 +33265,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33213,7 +33299,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33761,10 +33847,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33789,10 +33875,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35187,14 +35273,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35419,19 +35505,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35453,7 +35539,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36001,10 +36087,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36029,10 +36115,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37427,14 +37513,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37659,19 +37745,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37693,7 +37779,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38241,10 +38327,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38269,10 +38355,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39667,14 +39753,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -39899,19 +39985,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -39933,7 +40019,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40481,10 +40567,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40509,10 +40595,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -41907,14 +41993,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42139,19 +42225,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42173,7 +42259,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42626,6 +42712,2255 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3E2ED0-F427-4EF4-A819-09EA6253010F}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="294" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="294" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="297" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="297"/>
+      <c r="F2" s="294" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="294" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="295" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="294" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="294" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="295" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="295" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="295" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="298" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="298"/>
+      <c r="P2" s="294" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="294" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="294" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="294" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="192" t="s">
+        <v>247</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="194" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="191" t="s">
+        <v>348</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="299" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="301" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="302" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="301"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194" t="s">
+        <v>120</v>
+      </c>
+      <c r="O56" s="200" t="s">
+        <v>291</v>
+      </c>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="304" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -42721,10 +45056,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -42749,10 +45084,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -44156,14 +46491,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -44388,19 +46723,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -44422,7 +46757,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -44976,10 +47311,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -45004,10 +47339,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -46411,14 +48746,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46643,19 +48978,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46677,7 +49012,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -47229,10 +49564,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -47257,10 +49592,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -48664,14 +50999,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48896,19 +51231,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -48930,7 +51265,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49483,10 +51818,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -49511,10 +51846,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -50918,14 +53253,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51150,19 +53485,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51184,7 +53519,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51736,10 +54071,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -51764,10 +54099,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -53171,14 +55506,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53403,19 +55738,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53437,7 +55772,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -53987,10 +56322,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -54015,10 +56350,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -55422,14 +57757,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55654,19 +57989,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55688,7 +58023,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56238,10 +58573,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="294" t="s">
+      <c r="D2" s="297" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="294"/>
+      <c r="E2" s="297"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -56266,10 +58601,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="295" t="s">
+      <c r="N2" s="298" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="295"/>
+      <c r="O2" s="298"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -57673,14 +60008,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="296" t="s">
+      <c r="L41" s="299" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="296"/>
-      <c r="N41" s="296"/>
-      <c r="O41" s="296"/>
-      <c r="P41" s="296"/>
-      <c r="Q41" s="297"/>
+      <c r="M41" s="299"/>
+      <c r="N41" s="299"/>
+      <c r="O41" s="299"/>
+      <c r="P41" s="299"/>
+      <c r="Q41" s="300"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -57905,19 +60240,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="298" t="s">
+      <c r="A49" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="299" t="s">
+      <c r="B49" s="302" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="299"/>
-      <c r="D49" s="299"/>
-      <c r="E49" s="299"/>
-      <c r="F49" s="300"/>
-      <c r="G49" s="300"/>
-      <c r="H49" s="300"/>
-      <c r="I49" s="300"/>
+      <c r="C49" s="302"/>
+      <c r="D49" s="302"/>
+      <c r="E49" s="302"/>
+      <c r="F49" s="303"/>
+      <c r="G49" s="303"/>
+      <c r="H49" s="303"/>
+      <c r="I49" s="303"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -57939,7 +60274,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="298"/>
+      <c r="A50" s="301"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{136C7ACA-E578-4378-AD6B-F6AD06472546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D835FAFB-2E77-4392-9B72-3DBAB283CE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -38,6 +38,7 @@
     <sheet name="23" sheetId="96" r:id="rId23"/>
     <sheet name="24" sheetId="97" r:id="rId24"/>
     <sheet name="25" sheetId="98" r:id="rId25"/>
+    <sheet name="26" sheetId="99" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1193,6 +1194,69 @@
 </comments>
 </file>
 
+<file path=xl/comments26.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D90D1236-FC5E-4D50-96B3-BAB9EC78341A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{EF09AF5B-1B77-44D9-86E1-8C675C9620CC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1635,7 +1699,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7646" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7954" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -3249,7 +3313,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="305">
+  <cellXfs count="307">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4097,6 +4161,13 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4118,7 +4189,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="58">
     <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4585,10 +4655,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4613,10 +4683,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6019,14 +6089,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6251,19 +6321,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6285,7 +6355,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6827,10 +6897,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6855,10 +6925,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8267,14 +8337,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8504,19 +8574,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8539,7 +8609,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9138,10 +9208,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9166,10 +9236,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10571,14 +10641,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10803,19 +10873,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10837,7 +10907,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11384,10 +11454,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11412,10 +11482,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12817,14 +12887,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13049,19 +13119,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13083,7 +13153,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13630,10 +13700,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13658,10 +13728,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15063,14 +15133,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15295,19 +15365,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15329,7 +15399,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15876,10 +15946,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15904,10 +15974,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17309,14 +17379,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17541,19 +17611,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17575,7 +17645,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18122,10 +18192,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18150,10 +18220,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19555,14 +19625,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19787,19 +19857,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19821,7 +19891,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20372,10 +20442,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20400,10 +20470,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21805,14 +21875,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22037,19 +22107,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22071,7 +22141,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22621,10 +22691,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22649,10 +22719,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24054,14 +24124,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24286,19 +24356,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24320,7 +24390,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24870,10 +24940,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24898,10 +24968,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26297,14 +26367,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26529,19 +26599,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26563,7 +26633,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27111,10 +27181,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27139,10 +27209,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28537,14 +28607,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28769,19 +28839,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28803,7 +28873,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29351,10 +29421,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29379,10 +29449,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30788,14 +30858,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31020,19 +31090,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31054,7 +31124,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31607,10 +31677,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31635,10 +31705,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33033,14 +33103,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33265,19 +33335,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33299,7 +33369,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33847,10 +33917,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33875,10 +33945,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35273,14 +35343,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35505,19 +35575,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35539,7 +35609,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36087,10 +36157,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36115,10 +36185,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37513,14 +37583,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37745,19 +37815,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37779,7 +37849,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38327,10 +38397,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38355,10 +38425,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39753,14 +39823,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -39985,19 +40055,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40019,7 +40089,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40567,10 +40637,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40595,10 +40665,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -41993,14 +42063,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42225,19 +42295,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42259,7 +42329,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42807,10 +42877,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -42835,10 +42905,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -43541,8 +43611,8 @@
       <c r="N17" s="156" t="s">
         <v>278</v>
       </c>
-      <c r="O17" s="192" t="s">
-        <v>247</v>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
       </c>
       <c r="P17" s="283"/>
       <c r="Q17" s="193" t="s">
@@ -43581,8 +43651,8 @@
       <c r="N18" s="191" t="s">
         <v>313</v>
       </c>
-      <c r="O18" s="191" t="s">
-        <v>348</v>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
       </c>
       <c r="P18" s="283"/>
       <c r="Q18" s="193" t="s">
@@ -44235,14 +44305,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44467,19 +44537,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44501,7 +44571,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -44782,7 +44852,7 @@
       <c r="A57" s="200">
         <v>38</v>
       </c>
-      <c r="B57" s="304" t="s">
+      <c r="B57" s="297" t="s">
         <v>288</v>
       </c>
       <c r="C57" s="151">
@@ -44961,6 +45031,2254 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B7143B-7020-4399-88FF-E0A9BDFF5C07}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="298" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="298" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="300" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="300"/>
+      <c r="F2" s="298" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="298" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="299" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="298" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="298" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="299" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="299" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="299" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="301" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="301"/>
+      <c r="P2" s="298" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="298" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="298" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="298" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="302" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="304" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="305" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="304"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194" t="s">
+        <v>120</v>
+      </c>
+      <c r="O56" s="200" t="s">
+        <v>291</v>
+      </c>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -45056,10 +47374,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -45084,10 +47402,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -46491,14 +48809,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -46723,19 +49041,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -46757,7 +49075,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -47311,10 +49629,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -47339,10 +49657,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -48746,14 +51064,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -48978,19 +51296,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -49012,7 +51330,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49564,10 +51882,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -49592,10 +51910,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -50999,14 +53317,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51231,19 +53549,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51265,7 +53583,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51818,10 +54136,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -51846,10 +54164,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -53253,14 +55571,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53485,19 +55803,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53519,7 +55837,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -54071,10 +56389,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -54099,10 +56417,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -55506,14 +57824,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55738,19 +58056,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55772,7 +58090,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56322,10 +58640,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -56350,10 +58668,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -57757,14 +60075,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -57989,19 +60307,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -58023,7 +60341,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -58573,10 +60891,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="297" t="s">
+      <c r="D2" s="300" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="297"/>
+      <c r="E2" s="300"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -58601,10 +60919,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="298" t="s">
+      <c r="N2" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="298"/>
+      <c r="O2" s="301"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -60008,14 +62326,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="299" t="s">
+      <c r="L41" s="302" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="299"/>
-      <c r="N41" s="299"/>
-      <c r="O41" s="299"/>
-      <c r="P41" s="299"/>
-      <c r="Q41" s="300"/>
+      <c r="M41" s="302"/>
+      <c r="N41" s="302"/>
+      <c r="O41" s="302"/>
+      <c r="P41" s="302"/>
+      <c r="Q41" s="303"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -60240,19 +62558,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="301" t="s">
+      <c r="A49" s="304" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="302" t="s">
+      <c r="B49" s="305" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="302"/>
-      <c r="D49" s="302"/>
-      <c r="E49" s="302"/>
-      <c r="F49" s="303"/>
-      <c r="G49" s="303"/>
-      <c r="H49" s="303"/>
-      <c r="I49" s="303"/>
+      <c r="C49" s="305"/>
+      <c r="D49" s="305"/>
+      <c r="E49" s="305"/>
+      <c r="F49" s="306"/>
+      <c r="G49" s="306"/>
+      <c r="H49" s="306"/>
+      <c r="I49" s="306"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -60274,7 +62592,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="301"/>
+      <c r="A50" s="304"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D835FAFB-2E77-4392-9B72-3DBAB283CE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D76DE0-DF9A-459B-A212-309EA480C89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -39,6 +39,7 @@
     <sheet name="24" sheetId="97" r:id="rId24"/>
     <sheet name="25" sheetId="98" r:id="rId25"/>
     <sheet name="26" sheetId="99" r:id="rId26"/>
+    <sheet name="27" sheetId="100" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1257,6 +1258,69 @@
 </comments>
 </file>
 
+<file path=xl/comments27.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{3B54DF5D-5006-412B-B929-86C83AC1EF2A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{5A143378-9BE0-4552-AFF3-E84D0A1DB10A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1699,7 +1763,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7954" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8258" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -3313,7 +3377,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="307">
+  <cellXfs count="309">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4174,6 +4238,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4655,10 +4725,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4683,10 +4753,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6089,14 +6159,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6321,19 +6391,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6355,7 +6425,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6897,10 +6967,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6925,10 +6995,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8337,14 +8407,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8574,19 +8644,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8609,7 +8679,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9208,10 +9278,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9236,10 +9306,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10641,14 +10711,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10873,19 +10943,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10907,7 +10977,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11454,10 +11524,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11482,10 +11552,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12887,14 +12957,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13119,19 +13189,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13153,7 +13223,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13700,10 +13770,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13728,10 +13798,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15133,14 +15203,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15365,19 +15435,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15399,7 +15469,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15946,10 +16016,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -15974,10 +16044,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17379,14 +17449,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17611,19 +17681,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17645,7 +17715,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18192,10 +18262,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18220,10 +18290,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19625,14 +19695,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19857,19 +19927,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19891,7 +19961,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20442,10 +20512,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20470,10 +20540,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21875,14 +21945,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22107,19 +22177,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22141,7 +22211,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22691,10 +22761,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22719,10 +22789,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24124,14 +24194,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24356,19 +24426,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24390,7 +24460,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24940,10 +25010,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -24968,10 +25038,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26367,14 +26437,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26599,19 +26669,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26633,7 +26703,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27181,10 +27251,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27209,10 +27279,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28607,14 +28677,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28839,19 +28909,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28873,7 +28943,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29421,10 +29491,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29449,10 +29519,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30858,14 +30928,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31090,19 +31160,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31124,7 +31194,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31677,10 +31747,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31705,10 +31775,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33103,14 +33173,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33335,19 +33405,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33369,7 +33439,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33917,10 +33987,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -33945,10 +34015,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35343,14 +35413,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35575,19 +35645,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35609,7 +35679,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36157,10 +36227,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36185,10 +36255,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37583,14 +37653,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37815,19 +37885,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37849,7 +37919,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38397,10 +38467,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38425,10 +38495,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39823,14 +39893,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -40055,19 +40125,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40089,7 +40159,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40637,10 +40707,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40665,10 +40735,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -42063,14 +42133,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42295,19 +42365,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42329,7 +42399,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42877,10 +42947,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -42905,10 +42975,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -44305,14 +44375,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44537,19 +44607,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44571,7 +44641,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -45126,10 +45196,10 @@
       <c r="C2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="298" t="s">
         <v>4</v>
       </c>
@@ -45154,10 +45224,10 @@
       <c r="M2" s="299" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="298" t="s">
         <v>13</v>
       </c>
@@ -46554,14 +46624,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -46786,19 +46856,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -46820,7 +46890,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -47086,12 +47156,2252 @@
       <c r="J56" s="190"/>
       <c r="L56" s="203"/>
       <c r="M56" s="193"/>
-      <c r="N56" s="194" t="s">
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26C38FB-A4A4-4FF4-AB93-E3C0A04300B8}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="300" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="300" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="302" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="302"/>
+      <c r="F2" s="300" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="300" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="301" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="300" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="300" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="301" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="301" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="301" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="303" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="303"/>
+      <c r="P2" s="300" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="300" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="300" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="300" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
         <v>120</v>
       </c>
-      <c r="O56" s="200" t="s">
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="304" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="306" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="307" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="306"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
         <v>291</v>
       </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
       <c r="P56" s="200"/>
       <c r="Q56" s="200"/>
       <c r="R56" s="214"/>
@@ -47374,10 +49684,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -47402,10 +49712,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -48809,14 +51119,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -49041,19 +51351,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -49075,7 +51385,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -49629,10 +51939,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -49657,10 +51967,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -51064,14 +53374,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51296,19 +53606,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51330,7 +53640,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51882,10 +54192,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -51910,10 +54220,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -53317,14 +55627,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53549,19 +55859,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53583,7 +55893,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -54136,10 +56446,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -54164,10 +56474,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -55571,14 +57881,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55803,19 +58113,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55837,7 +58147,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56389,10 +58699,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -56417,10 +58727,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -57824,14 +60134,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -58056,19 +60366,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -58090,7 +60400,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -58640,10 +60950,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -58668,10 +60978,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -60075,14 +62385,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -60307,19 +62617,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -60341,7 +62651,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -60891,10 +63201,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="300" t="s">
+      <c r="D2" s="302" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="300"/>
+      <c r="E2" s="302"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -60919,10 +63229,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="301" t="s">
+      <c r="N2" s="303" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="301"/>
+      <c r="O2" s="303"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -62326,14 +64636,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="302" t="s">
+      <c r="L41" s="304" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="302"/>
-      <c r="N41" s="302"/>
-      <c r="O41" s="302"/>
-      <c r="P41" s="302"/>
-      <c r="Q41" s="303"/>
+      <c r="M41" s="304"/>
+      <c r="N41" s="304"/>
+      <c r="O41" s="304"/>
+      <c r="P41" s="304"/>
+      <c r="Q41" s="305"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -62558,19 +64868,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="304" t="s">
+      <c r="A49" s="306" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="305" t="s">
+      <c r="B49" s="307" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="305"/>
-      <c r="D49" s="305"/>
-      <c r="E49" s="305"/>
-      <c r="F49" s="306"/>
-      <c r="G49" s="306"/>
-      <c r="H49" s="306"/>
-      <c r="I49" s="306"/>
+      <c r="C49" s="307"/>
+      <c r="D49" s="307"/>
+      <c r="E49" s="307"/>
+      <c r="F49" s="308"/>
+      <c r="G49" s="308"/>
+      <c r="H49" s="308"/>
+      <c r="I49" s="308"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -62592,7 +64902,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="304"/>
+      <c r="A50" s="306"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D76DE0-DF9A-459B-A212-309EA480C89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EC9EFB-1D4B-470B-926F-7DACC88EA478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -40,6 +40,7 @@
     <sheet name="25" sheetId="98" r:id="rId25"/>
     <sheet name="26" sheetId="99" r:id="rId26"/>
     <sheet name="27" sheetId="100" r:id="rId27"/>
+    <sheet name="28" sheetId="101" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1321,6 +1322,69 @@
 </comments>
 </file>
 
+<file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{0968298D-FCE9-40C7-9C8C-DFE23C67979D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{9A57D34A-2AC0-4E3F-B7CE-A4DCB7E3B5DE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1763,7 +1827,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8258" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8564" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -3377,7 +3441,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="309">
+  <cellXfs count="311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4244,6 +4308,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4725,10 +4795,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4753,10 +4823,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6159,14 +6229,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6391,19 +6461,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6425,7 +6495,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6967,10 +7037,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -6995,10 +7065,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8407,14 +8477,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8644,19 +8714,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8679,7 +8749,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9278,10 +9348,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9306,10 +9376,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10711,14 +10781,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -10943,19 +11013,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -10977,7 +11047,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11524,10 +11594,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11552,10 +11622,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -12957,14 +13027,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13189,19 +13259,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13223,7 +13293,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13770,10 +13840,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13798,10 +13868,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15203,14 +15273,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15435,19 +15505,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15469,7 +15539,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -16016,10 +16086,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -16044,10 +16114,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17449,14 +17519,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17681,19 +17751,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17715,7 +17785,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18262,10 +18332,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18290,10 +18360,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19695,14 +19765,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19927,19 +19997,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -19961,7 +20031,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20512,10 +20582,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20540,10 +20610,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -21945,14 +22015,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22177,19 +22247,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22211,7 +22281,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22761,10 +22831,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22789,10 +22859,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24194,14 +24264,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24426,19 +24496,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24460,7 +24530,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -25010,10 +25080,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -25038,10 +25108,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26437,14 +26507,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26669,19 +26739,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26703,7 +26773,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27251,10 +27321,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27279,10 +27349,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28677,14 +28747,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28909,19 +28979,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -28943,7 +29013,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29491,10 +29561,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29519,10 +29589,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30928,14 +30998,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31160,19 +31230,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31194,7 +31264,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31747,10 +31817,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31775,10 +31845,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33173,14 +33243,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33405,19 +33475,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33439,7 +33509,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33987,10 +34057,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -34015,10 +34085,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35413,14 +35483,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35645,19 +35715,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35679,7 +35749,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36227,10 +36297,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36255,10 +36325,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37653,14 +37723,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37885,19 +37955,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37919,7 +37989,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38467,10 +38537,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38495,10 +38565,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39893,14 +39963,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -40125,19 +40195,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40159,7 +40229,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40707,10 +40777,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40735,10 +40805,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -42133,14 +42203,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42365,19 +42435,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42399,7 +42469,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42947,10 +43017,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -42975,10 +43045,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -44375,14 +44445,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44607,19 +44677,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44641,7 +44711,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -45196,10 +45266,10 @@
       <c r="C2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="298" t="s">
         <v>4</v>
       </c>
@@ -45224,10 +45294,10 @@
       <c r="M2" s="299" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="298" t="s">
         <v>13</v>
       </c>
@@ -46624,14 +46694,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -46856,19 +46926,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -46890,7 +46960,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -47440,10 +47510,10 @@
       <c r="C2" s="300" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="300" t="s">
         <v>4</v>
       </c>
@@ -47468,10 +47538,10 @@
       <c r="M2" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="300" t="s">
         <v>13</v>
       </c>
@@ -48868,14 +48938,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -49100,19 +49170,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -49134,7 +49204,2251 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>161</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{353B02CB-857E-4303-9C73-28E6393C165A}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="302" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="302" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="304" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="304"/>
+      <c r="F2" s="302" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="302" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="303" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="302" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="302" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="303" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="303" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="303" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="305" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="305"/>
+      <c r="P2" s="302" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="302" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="302" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="302" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="306" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="308" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="309" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="308"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -49684,10 +51998,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -49712,10 +52026,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -51119,14 +53433,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -51351,19 +53665,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -51385,7 +53699,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -51939,10 +54253,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -51967,10 +54281,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -53374,14 +55688,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53606,19 +55920,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53640,7 +55954,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -54192,10 +56506,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -54220,10 +56534,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -55627,14 +57941,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55859,19 +58173,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55893,7 +58207,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56446,10 +58760,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -56474,10 +58788,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -57881,14 +60195,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -58113,19 +60427,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -58147,7 +60461,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -58699,10 +61013,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -58727,10 +61041,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -60134,14 +62448,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -60366,19 +62680,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -60400,7 +62714,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -60950,10 +63264,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -60978,10 +63292,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -62385,14 +64699,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -62617,19 +64931,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -62651,7 +64965,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -63201,10 +65515,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="302" t="s">
+      <c r="D2" s="304" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="302"/>
+      <c r="E2" s="304"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -63229,10 +65543,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="303" t="s">
+      <c r="N2" s="305" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="303"/>
+      <c r="O2" s="305"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -64636,14 +66950,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="304" t="s">
+      <c r="L41" s="306" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="304"/>
-      <c r="N41" s="304"/>
-      <c r="O41" s="304"/>
-      <c r="P41" s="304"/>
-      <c r="Q41" s="305"/>
+      <c r="M41" s="306"/>
+      <c r="N41" s="306"/>
+      <c r="O41" s="306"/>
+      <c r="P41" s="306"/>
+      <c r="Q41" s="307"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -64868,19 +67182,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="306" t="s">
+      <c r="A49" s="308" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="307" t="s">
+      <c r="B49" s="309" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="307"/>
-      <c r="D49" s="307"/>
-      <c r="E49" s="307"/>
-      <c r="F49" s="308"/>
-      <c r="G49" s="308"/>
-      <c r="H49" s="308"/>
-      <c r="I49" s="308"/>
+      <c r="C49" s="309"/>
+      <c r="D49" s="309"/>
+      <c r="E49" s="309"/>
+      <c r="F49" s="310"/>
+      <c r="G49" s="310"/>
+      <c r="H49" s="310"/>
+      <c r="I49" s="310"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -64902,7 +67216,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="306"/>
+      <c r="A50" s="308"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EC9EFB-1D4B-470B-926F-7DACC88EA478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="28"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -41,8 +40,9 @@
     <sheet name="26" sheetId="99" r:id="rId26"/>
     <sheet name="27" sheetId="100" r:id="rId27"/>
     <sheet name="28" sheetId="101" r:id="rId28"/>
+    <sheet name="29" sheetId="102" r:id="rId29"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -61,12 +61,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{E1678F51-B291-469C-9B5B-737656770E03}">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -93,7 +93,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{F24BA18A-B69E-4795-BD32-4127CD68F943}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -125,12 +125,12 @@
 </file>
 
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{5D2EE3B7-AF98-4F98-8DEA-456C439209D3}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{716D977C-E844-4233-A7A8-F47EC5B8FBFC}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -188,12 +188,12 @@
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{FEE1D01E-AA7A-4427-8A90-CE2B48929A27}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -219,7 +219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{506E25C7-9A1B-423D-9EAA-722B3A84D1C2}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -251,12 +251,12 @@
 </file>
 
 <file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{9EB61175-F4B0-42F5-B41B-D28FF3B18B9F}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -282,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{72A6C6CA-B79E-45D0-B3F4-72A1528CD08E}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -314,12 +314,12 @@
 </file>
 
 <file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{54FE8974-760A-41C1-9063-DFAC32DD42F5}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -345,7 +345,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{99CA011F-FF3B-4AB2-AA93-927AEAEF4FAB}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,12 +377,12 @@
 </file>
 
 <file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{8896D6FA-4023-4649-AFC0-1B4474D47FB6}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -408,7 +408,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{F92CA02A-A2E4-4CDE-BE11-9E668A16D84D}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -440,12 +440,12 @@
 </file>
 
 <file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{94600642-CF3A-43FA-A120-F6031FEE9C04}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -471,7 +471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{9767AF24-7B48-41F1-934E-6519F4D45047}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -503,12 +503,12 @@
 </file>
 
 <file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D4BF631E-4677-4071-9DCC-A07931960C33}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -534,7 +534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{EF80E771-233C-4B5B-8E1A-84647D961F56}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -566,12 +566,12 @@
 </file>
 
 <file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{67B6D405-B8E3-41B3-94BB-7C70F0A5889D}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -597,7 +597,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{2BD75881-E0B3-43DE-B041-085A08B52664}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -629,12 +629,12 @@
 </file>
 
 <file path=xl/comments18.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{9E58FDB9-61B4-48D0-994B-1D491A12427B}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -660,7 +660,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{7406D024-8BC0-4F45-80E7-0E4EDF321B2C}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -692,12 +692,12 @@
 </file>
 
 <file path=xl/comments19.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{B548A010-6137-4069-8261-695B4184F918}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -723,7 +723,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{74F66320-01AA-41F9-8A6B-910ABA673B91}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -755,12 +755,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{900B3CA3-1858-4644-8CB6-517C165C7882}">
+    <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -787,7 +787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{FA21DBD6-702E-4A8A-BAA7-9B1DC267A547}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -819,12 +819,12 @@
 </file>
 
 <file path=xl/comments20.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{ABC106DE-8665-4312-BFA0-994518E35A40}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -850,7 +850,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{1273198A-1FED-4FF9-97D8-5C79CC352C45}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -882,12 +882,12 @@
 </file>
 
 <file path=xl/comments21.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{F26236F6-A3BA-4673-AF28-2932ECBA8549}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -913,7 +913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{51B92F4E-0830-4AE0-A780-842477A31FA3}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -945,12 +945,12 @@
 </file>
 
 <file path=xl/comments22.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{01068D76-C2D7-438D-BD3F-2F2C3011B0A0}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -976,7 +976,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{51735C04-7A0A-4558-8D5E-2DFE9CC13FC1}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1008,12 +1008,12 @@
 </file>
 
 <file path=xl/comments23.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{7BC7663E-41C3-4D5C-AEDC-3D7FFBBD12FD}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1039,7 +1039,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{A1F5E7DE-5494-43F6-A109-848FC954EC22}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1071,12 +1071,12 @@
 </file>
 
 <file path=xl/comments24.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{374D61BB-323C-48A2-AC80-39513A5D9760}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1102,7 +1102,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{ED0CC90D-2D9F-40C4-ADF5-6B73AEC151CD}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1134,12 +1134,12 @@
 </file>
 
 <file path=xl/comments25.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{8BD8106C-92A6-4764-B60B-FF2345F8CAB1}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1165,7 +1165,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{4AE8BB96-9B71-43EF-BEC6-68A2834A340E}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1197,12 +1197,12 @@
 </file>
 
 <file path=xl/comments26.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{D90D1236-FC5E-4D50-96B3-BAB9EC78341A}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1228,7 +1228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{EF09AF5B-1B77-44D9-86E1-8C675C9620CC}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1260,12 +1260,12 @@
 </file>
 
 <file path=xl/comments27.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{3B54DF5D-5006-412B-B929-86C83AC1EF2A}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1291,7 +1291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{5A143378-9BE0-4552-AFF3-E84D0A1DB10A}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1323,12 +1323,12 @@
 </file>
 
 <file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{0968298D-FCE9-40C7-9C8C-DFE23C67979D}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1354,7 +1354,70 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{9A57D34A-2AC0-4E3F-B7CE-A4DCB7E3B5DE}">
+    <comment ref="B57" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments29.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1386,12 +1449,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{E0C77BF1-A0FE-4D53-83BA-C1388C967946}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1417,7 +1480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{054A0F2D-5D56-49D0-9612-27F87EB71981}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1449,12 +1512,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{49025F3A-DC5B-43C2-9A99-3795B281115F}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1480,7 +1543,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{1D07E7CF-DFC7-4019-A50C-5D185008568C}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1512,12 +1575,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{29899AE4-52AB-48F6-8811-55C9FD834C8D}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1543,7 +1606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{14942A1E-96F4-40DC-8474-C4F4734FD040}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1575,12 +1638,12 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{234B48B7-CA8B-4A67-95A1-AFDFA49A4242}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1606,7 +1669,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{4521BB7A-0467-4F10-A499-853EF875F88C}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1638,12 +1701,12 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{434BF7E3-B463-4E95-97AC-9EA7E6AD3F0A}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1669,7 +1732,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{997B7B64-3A48-4264-A882-0DF0A76990DD}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1701,12 +1764,12 @@
 </file>
 
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{ADB26EDF-2948-4678-90BB-723F41CD1DB1}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1732,7 +1795,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{A498641B-6091-4028-9F77-BF5274CA418F}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1764,12 +1827,12 @@
 </file>
 
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{5031D530-A46C-43B0-960A-868C056BDF27}">
+    <comment ref="J11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1795,7 +1858,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{F88553D2-EA35-41D6-A3A1-03791F6F222B}">
+    <comment ref="B57" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -1827,7 +1890,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8564" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8870" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -2921,7 +2984,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -3441,7 +3504,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="311">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4314,6 +4377,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4331,64 +4400,64 @@
     </xf>
   </cellXfs>
   <cellStyles count="58">
-    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2"/>
+    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 3 2" xfId="3"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 12" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Обычный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="Обычный 2 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="Обычный 2 10 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Обычный 2 10 2 2" xfId="14" xr:uid="{E74DFC9D-8041-4F23-BD14-35F55D65D50E}"/>
-    <cellStyle name="Обычный 2 10 2 2 2" xfId="20" xr:uid="{FD992A63-5D74-4521-9F60-F2969D8662FD}"/>
-    <cellStyle name="Обычный 2 10 2 2 2 2" xfId="32" xr:uid="{08F00831-5BCE-4390-8B1A-3F804B463574}"/>
-    <cellStyle name="Обычный 2 10 2 2 2 2 2" xfId="56" xr:uid="{21B3166D-3E65-4C1F-9375-BC69326C58C7}"/>
-    <cellStyle name="Обычный 2 10 2 2 2 3" xfId="44" xr:uid="{603DDDD9-C69F-4D65-AF8A-96019799DEBC}"/>
-    <cellStyle name="Обычный 2 10 2 2 3" xfId="26" xr:uid="{751D4658-A9E8-4A0F-8862-3C98AB669DFF}"/>
-    <cellStyle name="Обычный 2 10 2 2 3 2" xfId="50" xr:uid="{AB6A3F23-5F51-4322-A2B8-D4963520435A}"/>
-    <cellStyle name="Обычный 2 10 2 2 4" xfId="38" xr:uid="{29533633-EB77-4483-8A9F-76F009951E71}"/>
-    <cellStyle name="Обычный 2 10 2 3" xfId="17" xr:uid="{E80116E7-FE17-40D3-A026-2837402DB1A7}"/>
-    <cellStyle name="Обычный 2 10 2 3 2" xfId="29" xr:uid="{034B2907-6E31-4EF1-9DC0-B21ED2B896A1}"/>
-    <cellStyle name="Обычный 2 10 2 3 2 2" xfId="53" xr:uid="{7504D7F1-C464-4E32-87D3-411B1836F3E1}"/>
-    <cellStyle name="Обычный 2 10 2 3 3" xfId="41" xr:uid="{2E47E696-9BB4-44B3-AEFA-CA19B71620EE}"/>
-    <cellStyle name="Обычный 2 10 2 4" xfId="23" xr:uid="{43669422-FE9A-410B-99A9-699ED7E06CB3}"/>
-    <cellStyle name="Обычный 2 10 2 4 2" xfId="47" xr:uid="{B21AD92F-3CC3-427A-BAD6-4E9706F206B8}"/>
-    <cellStyle name="Обычный 2 10 2 5" xfId="35" xr:uid="{7725FC74-1C38-4FBA-8A6D-39BF6576F578}"/>
-    <cellStyle name="Обычный 2 10 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Обычный 2 10 3 2" xfId="15" xr:uid="{EBAAEE4E-619B-4F59-9CE9-DC96C1B91F11}"/>
-    <cellStyle name="Обычный 2 10 3 2 2" xfId="21" xr:uid="{2135B7D5-5E3A-4848-9D82-D3CD01D0F369}"/>
-    <cellStyle name="Обычный 2 10 3 2 2 2" xfId="33" xr:uid="{D42B64BB-5002-4EE1-A5F7-9AE8E44D2E46}"/>
-    <cellStyle name="Обычный 2 10 3 2 2 2 2" xfId="57" xr:uid="{DE360249-6346-40F8-98B3-871C0944D2C6}"/>
-    <cellStyle name="Обычный 2 10 3 2 2 3" xfId="45" xr:uid="{7C9BDD0D-AEC6-4491-B945-C7DFD76BE2E6}"/>
-    <cellStyle name="Обычный 2 10 3 2 3" xfId="27" xr:uid="{41A5FCC0-9D82-4DD6-ADFB-825BB3047E92}"/>
-    <cellStyle name="Обычный 2 10 3 2 3 2" xfId="51" xr:uid="{A7BED3A5-6E1D-449E-A9F7-E946ABDBB3DF}"/>
-    <cellStyle name="Обычный 2 10 3 2 4" xfId="39" xr:uid="{3D5D0085-A012-4F10-B1FA-C37772486253}"/>
-    <cellStyle name="Обычный 2 10 3 3" xfId="18" xr:uid="{211B4B32-A8D8-495D-9902-B914C98B6158}"/>
-    <cellStyle name="Обычный 2 10 3 3 2" xfId="30" xr:uid="{58E33D61-28C2-45BD-9097-7D3461707319}"/>
-    <cellStyle name="Обычный 2 10 3 3 2 2" xfId="54" xr:uid="{D2451DD4-EF43-4326-91E0-A0CE783EAF96}"/>
-    <cellStyle name="Обычный 2 10 3 3 3" xfId="42" xr:uid="{206C9570-FC1B-4C9B-9863-B2724A879F98}"/>
-    <cellStyle name="Обычный 2 10 3 4" xfId="24" xr:uid="{FE69C11B-198E-425A-A485-C6825A2C525B}"/>
-    <cellStyle name="Обычный 2 10 3 4 2" xfId="48" xr:uid="{3FF3400A-1458-4033-83D7-7E3AA188B202}"/>
-    <cellStyle name="Обычный 2 10 3 5" xfId="36" xr:uid="{E963D7F5-DA4B-40A8-A57A-21E3BB2D4761}"/>
-    <cellStyle name="Обычный 2 10 4" xfId="13" xr:uid="{99717109-5101-4703-93ED-3072A0B366BE}"/>
-    <cellStyle name="Обычный 2 10 4 2" xfId="19" xr:uid="{022FA9DC-2E75-4D62-8AD2-205C4EC10B7B}"/>
-    <cellStyle name="Обычный 2 10 4 2 2" xfId="31" xr:uid="{421772C4-CAA0-4269-8CF7-CD951135E697}"/>
-    <cellStyle name="Обычный 2 10 4 2 2 2" xfId="55" xr:uid="{C0D148CC-E128-4C83-8E6E-9B2B4E469BA6}"/>
-    <cellStyle name="Обычный 2 10 4 2 3" xfId="43" xr:uid="{B89C96F2-B05F-42FE-9D6D-4985073D5412}"/>
-    <cellStyle name="Обычный 2 10 4 3" xfId="25" xr:uid="{0B82E204-C086-4EF6-89C9-FB9215CCD787}"/>
-    <cellStyle name="Обычный 2 10 4 3 2" xfId="49" xr:uid="{0755B5A1-9E33-4DD7-8AEC-ADED399EFC38}"/>
-    <cellStyle name="Обычный 2 10 4 4" xfId="37" xr:uid="{7086A9F3-0812-4A4B-B69D-6F9FB02AFD73}"/>
-    <cellStyle name="Обычный 2 10 5" xfId="16" xr:uid="{5E610AE0-C0A6-484C-8114-C2A1798F136A}"/>
-    <cellStyle name="Обычный 2 10 5 2" xfId="28" xr:uid="{B29A9444-1F16-4B34-A7D7-835E3EEEF3E6}"/>
-    <cellStyle name="Обычный 2 10 5 2 2" xfId="52" xr:uid="{D0CE0D6C-0D22-472D-972E-3B0B1844DEEE}"/>
-    <cellStyle name="Обычный 2 10 5 3" xfId="40" xr:uid="{2380B564-494A-4018-B74D-D8DE5C9004D7}"/>
-    <cellStyle name="Обычный 2 10 6" xfId="22" xr:uid="{79774DA3-764A-44F7-BAB1-2BB896AFBB7E}"/>
-    <cellStyle name="Обычный 2 10 6 2" xfId="46" xr:uid="{DFE7EC8A-3C4C-4A1C-9B46-67F3A05CCFB4}"/>
-    <cellStyle name="Обычный 2 10 7" xfId="34" xr:uid="{B5BA9F10-C528-4666-A942-4607F9D3CACB}"/>
-    <cellStyle name="Обычный 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="Обычный 3 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Обычный 4" xfId="1" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="Обычный 5" xfId="9" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
-    <cellStyle name="Обычный 9" xfId="10" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 12" xfId="4"/>
+    <cellStyle name="Обычный 2" xfId="5"/>
+    <cellStyle name="Обычный 2 10" xfId="6"/>
+    <cellStyle name="Обычный 2 10 2" xfId="11"/>
+    <cellStyle name="Обычный 2 10 2 2" xfId="14"/>
+    <cellStyle name="Обычный 2 10 2 2 2" xfId="20"/>
+    <cellStyle name="Обычный 2 10 2 2 2 2" xfId="32"/>
+    <cellStyle name="Обычный 2 10 2 2 2 2 2" xfId="56"/>
+    <cellStyle name="Обычный 2 10 2 2 2 3" xfId="44"/>
+    <cellStyle name="Обычный 2 10 2 2 3" xfId="26"/>
+    <cellStyle name="Обычный 2 10 2 2 3 2" xfId="50"/>
+    <cellStyle name="Обычный 2 10 2 2 4" xfId="38"/>
+    <cellStyle name="Обычный 2 10 2 3" xfId="17"/>
+    <cellStyle name="Обычный 2 10 2 3 2" xfId="29"/>
+    <cellStyle name="Обычный 2 10 2 3 2 2" xfId="53"/>
+    <cellStyle name="Обычный 2 10 2 3 3" xfId="41"/>
+    <cellStyle name="Обычный 2 10 2 4" xfId="23"/>
+    <cellStyle name="Обычный 2 10 2 4 2" xfId="47"/>
+    <cellStyle name="Обычный 2 10 2 5" xfId="35"/>
+    <cellStyle name="Обычный 2 10 3" xfId="12"/>
+    <cellStyle name="Обычный 2 10 3 2" xfId="15"/>
+    <cellStyle name="Обычный 2 10 3 2 2" xfId="21"/>
+    <cellStyle name="Обычный 2 10 3 2 2 2" xfId="33"/>
+    <cellStyle name="Обычный 2 10 3 2 2 2 2" xfId="57"/>
+    <cellStyle name="Обычный 2 10 3 2 2 3" xfId="45"/>
+    <cellStyle name="Обычный 2 10 3 2 3" xfId="27"/>
+    <cellStyle name="Обычный 2 10 3 2 3 2" xfId="51"/>
+    <cellStyle name="Обычный 2 10 3 2 4" xfId="39"/>
+    <cellStyle name="Обычный 2 10 3 3" xfId="18"/>
+    <cellStyle name="Обычный 2 10 3 3 2" xfId="30"/>
+    <cellStyle name="Обычный 2 10 3 3 2 2" xfId="54"/>
+    <cellStyle name="Обычный 2 10 3 3 3" xfId="42"/>
+    <cellStyle name="Обычный 2 10 3 4" xfId="24"/>
+    <cellStyle name="Обычный 2 10 3 4 2" xfId="48"/>
+    <cellStyle name="Обычный 2 10 3 5" xfId="36"/>
+    <cellStyle name="Обычный 2 10 4" xfId="13"/>
+    <cellStyle name="Обычный 2 10 4 2" xfId="19"/>
+    <cellStyle name="Обычный 2 10 4 2 2" xfId="31"/>
+    <cellStyle name="Обычный 2 10 4 2 2 2" xfId="55"/>
+    <cellStyle name="Обычный 2 10 4 2 3" xfId="43"/>
+    <cellStyle name="Обычный 2 10 4 3" xfId="25"/>
+    <cellStyle name="Обычный 2 10 4 3 2" xfId="49"/>
+    <cellStyle name="Обычный 2 10 4 4" xfId="37"/>
+    <cellStyle name="Обычный 2 10 5" xfId="16"/>
+    <cellStyle name="Обычный 2 10 5 2" xfId="28"/>
+    <cellStyle name="Обычный 2 10 5 2 2" xfId="52"/>
+    <cellStyle name="Обычный 2 10 5 3" xfId="40"/>
+    <cellStyle name="Обычный 2 10 6" xfId="22"/>
+    <cellStyle name="Обычный 2 10 6 2" xfId="46"/>
+    <cellStyle name="Обычный 2 10 7" xfId="34"/>
+    <cellStyle name="Обычный 3" xfId="7"/>
+    <cellStyle name="Обычный 3 2 2" xfId="8"/>
+    <cellStyle name="Обычный 4" xfId="1"/>
+    <cellStyle name="Обычный 5" xfId="9"/>
+    <cellStyle name="Обычный 9" xfId="10"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4704,7 +4773,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4795,10 +4864,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4823,10 +4892,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6229,14 +6298,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6461,19 +6530,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6495,7 +6564,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -6946,7 +7015,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96893D9D-B689-479A-9893-6422F008690C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7037,10 +7106,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -7065,10 +7134,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8477,14 +8546,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8714,19 +8783,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8749,7 +8818,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9257,7 +9326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABF90C2-50A5-4D46-8FFA-36A9CB196FEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9348,10 +9417,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9376,10 +9445,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10781,14 +10850,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -11013,19 +11082,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -11047,7 +11116,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11503,7 +11572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D46DCC6-0884-49C2-9AC3-722C8A1E0583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11594,10 +11663,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11622,10 +11691,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -13027,14 +13096,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13259,19 +13328,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13293,7 +13362,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13749,7 +13818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D6DF7C-F672-4A22-B8AA-ADA4A4FC29A1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13840,10 +13909,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13868,10 +13937,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15273,14 +15342,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15505,19 +15574,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15539,7 +15608,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -15995,7 +16064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B267B304-39CA-498E-ABCF-A6976A0BA24B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16086,10 +16155,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -16114,10 +16183,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17519,14 +17588,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17751,19 +17820,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17785,7 +17854,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18241,7 +18310,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C856D3D-AC0A-4AC2-AA5A-929A455E8D63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18332,10 +18401,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18360,10 +18429,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19765,14 +19834,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -19997,19 +20066,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -20031,7 +20100,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20491,7 +20560,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2077F5E2-7FD1-48DF-B0B6-945646DA0758}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20582,10 +20651,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20610,10 +20679,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -22015,14 +22084,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22247,19 +22316,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22281,7 +22350,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22740,7 +22809,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0060BF9E-50ED-4DD7-BE69-520877427C6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22831,10 +22900,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22859,10 +22928,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24264,14 +24333,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24496,19 +24565,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24530,7 +24599,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -24989,7 +25058,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{794C13C1-701E-42C8-A9C9-9575D79A0014}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25080,10 +25149,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -25108,10 +25177,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26507,14 +26576,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26739,19 +26808,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26773,7 +26842,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27230,7 +27299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D91EF2C-BFD5-4484-8751-A8A329463013}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27321,10 +27390,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27349,10 +27418,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28747,14 +28816,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -28979,19 +29048,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -29013,7 +29082,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29470,7 +29539,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4E7AF6-D8AB-4203-8F82-86B191D90A6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -29561,10 +29630,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29589,10 +29658,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -30998,14 +31067,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31230,19 +31299,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31264,7 +31333,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31726,7 +31795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7800A18-1E39-4A30-A7E9-0922B0679383}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31817,10 +31886,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31845,10 +31914,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33243,14 +33312,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33475,19 +33544,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33509,7 +33578,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -33966,7 +34035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA72948F-12F3-4979-BDB8-6392E09A3342}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -34057,10 +34126,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -34085,10 +34154,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35483,14 +35552,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35715,19 +35784,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35749,7 +35818,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36206,7 +36275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B13517E4-767D-472D-8205-3BE035067356}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -36297,10 +36366,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36325,10 +36394,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37723,14 +37792,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -37955,19 +38024,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -37989,7 +38058,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38446,7 +38515,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ABC156-14C1-4D92-B9E5-84603C681761}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -38537,10 +38606,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38565,10 +38634,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -39963,14 +40032,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -40195,19 +40264,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40229,7 +40298,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40686,7 +40755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{161832FD-6616-42F7-9BC3-0C24AF2A2D32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -40777,10 +40846,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40805,10 +40874,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -42203,14 +42272,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42435,19 +42504,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42469,7 +42538,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42926,7 +42995,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3E2ED0-F427-4EF4-A819-09EA6253010F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -43017,10 +43086,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -43045,10 +43114,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -44445,14 +44514,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44677,19 +44746,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44711,7 +44780,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -45175,7 +45244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B7143B-7020-4399-88FF-E0A9BDFF5C07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -45266,10 +45335,10 @@
       <c r="C2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="298" t="s">
         <v>4</v>
       </c>
@@ -45294,10 +45363,10 @@
       <c r="M2" s="299" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="298" t="s">
         <v>13</v>
       </c>
@@ -46694,14 +46763,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -46926,19 +46995,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -46960,7 +47029,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -47419,7 +47488,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E26C38FB-A4A4-4FF4-AB93-E3C0A04300B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -47510,10 +47579,10 @@
       <c r="C2" s="300" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="300" t="s">
         <v>4</v>
       </c>
@@ -47538,10 +47607,10 @@
       <c r="M2" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="300" t="s">
         <v>13</v>
       </c>
@@ -48938,14 +49007,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -49170,19 +49239,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -49204,7 +49273,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -49663,7 +49732,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{353B02CB-857E-4303-9C73-28E6393C165A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -49754,10 +49823,10 @@
       <c r="C2" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="302" t="s">
         <v>4</v>
       </c>
@@ -49782,10 +49851,10 @@
       <c r="M2" s="303" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="302" t="s">
         <v>13</v>
       </c>
@@ -51182,14 +51251,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -51414,19 +51483,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -51448,7 +51517,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -51906,8 +51975,2252 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="304" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="304" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="306" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="306"/>
+      <c r="F2" s="304" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="304" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="305" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="304" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="304" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="305" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="305" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="305" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="307" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="307"/>
+      <c r="P2" s="304" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="304" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="304" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="304" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="308" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="310" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="311" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="310"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>160</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E19CCF3-169C-455B-9727-8F7303CA5C63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -51998,10 +54311,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -52026,10 +54339,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -53433,14 +55746,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -53665,19 +55978,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -53699,7 +56012,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -54162,7 +56475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0192B67-2EA9-42A2-9992-9F8EF1BD70AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -54253,10 +56566,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -54281,10 +56594,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -55688,14 +58001,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55920,19 +58233,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -55954,7 +58267,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56415,7 +58728,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5568454-0F79-405A-8ACF-38DAD9ADD25D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -56506,10 +58819,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -56534,10 +58847,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -57941,14 +60254,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -58173,19 +60486,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -58207,7 +60520,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -58669,7 +60982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C25D682-3F15-4960-B8B7-5E90C54B98F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58760,10 +61073,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -58788,10 +61101,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -60195,14 +62508,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -60427,19 +62740,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -60461,7 +62774,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -60922,7 +63235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CCD737-670F-4F6A-A01D-83CFC758F5D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61013,10 +63326,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -61041,10 +63354,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -62448,14 +64761,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -62680,19 +64993,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -62714,7 +65027,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -63173,7 +65486,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E299F7EE-090B-4E1E-A3C3-06D5D71EAAD1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63264,10 +65577,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -63292,10 +65605,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -64699,14 +67012,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -64931,19 +67244,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -64965,7 +67278,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -65424,7 +67737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{969E21A2-B8E1-4E0F-9A9C-1A6322EF75C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -65515,10 +67828,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="304" t="s">
+      <c r="D2" s="306" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="304"/>
+      <c r="E2" s="306"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -65543,10 +67856,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="305" t="s">
+      <c r="N2" s="307" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="305"/>
+      <c r="O2" s="307"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -66950,14 +69263,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="306" t="s">
+      <c r="L41" s="308" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="306"/>
-      <c r="N41" s="306"/>
-      <c r="O41" s="306"/>
-      <c r="P41" s="306"/>
-      <c r="Q41" s="307"/>
+      <c r="M41" s="308"/>
+      <c r="N41" s="308"/>
+      <c r="O41" s="308"/>
+      <c r="P41" s="308"/>
+      <c r="Q41" s="309"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -67182,19 +69495,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="308" t="s">
+      <c r="A49" s="310" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="309" t="s">
+      <c r="B49" s="311" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="309"/>
-      <c r="D49" s="309"/>
-      <c r="E49" s="309"/>
-      <c r="F49" s="310"/>
-      <c r="G49" s="310"/>
-      <c r="H49" s="310"/>
-      <c r="I49" s="310"/>
+      <c r="C49" s="311"/>
+      <c r="D49" s="311"/>
+      <c r="E49" s="311"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
+      <c r="H49" s="312"/>
+      <c r="I49" s="312"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -67216,7 +69529,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="308"/>
+      <c r="A50" s="310"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B0A7EE-B13A-4786-B400-B03E9A0C881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="28"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -41,8 +42,9 @@
     <sheet name="27" sheetId="100" r:id="rId27"/>
     <sheet name="28" sheetId="101" r:id="rId28"/>
     <sheet name="29" sheetId="102" r:id="rId29"/>
+    <sheet name="30" sheetId="103" r:id="rId30"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -61,12 +63,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -93,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -125,12 +127,12 @@
 </file>
 
 <file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -156,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000002000000}">
       <text>
         <r>
           <rPr>
@@ -188,12 +190,12 @@
 </file>
 
 <file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -219,7 +221,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0A00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -251,12 +253,12 @@
 </file>
 
 <file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -282,7 +284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0B00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -314,12 +316,12 @@
 </file>
 
 <file path=xl/comments13.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0C00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -345,7 +347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0C00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -377,12 +379,12 @@
 </file>
 
 <file path=xl/comments14.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0D00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -408,7 +410,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0D00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -440,12 +442,12 @@
 </file>
 
 <file path=xl/comments15.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0E00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -471,7 +473,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0E00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -503,12 +505,12 @@
 </file>
 
 <file path=xl/comments16.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0F00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -534,7 +536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0F00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -566,12 +568,12 @@
 </file>
 
 <file path=xl/comments17.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -597,7 +599,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -629,12 +631,12 @@
 </file>
 
 <file path=xl/comments18.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -660,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -692,12 +694,12 @@
 </file>
 
 <file path=xl/comments19.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -723,7 +725,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -755,12 +757,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="H4" authorId="0" shapeId="0">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -787,7 +789,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
         <r>
           <rPr>
@@ -819,12 +821,12 @@
 </file>
 
 <file path=xl/comments20.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -850,7 +852,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -882,12 +884,12 @@
 </file>
 
 <file path=xl/comments21.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -913,7 +915,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -945,12 +947,12 @@
 </file>
 
 <file path=xl/comments22.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -976,7 +978,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1500-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1008,12 +1010,12 @@
 </file>
 
 <file path=xl/comments23.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1039,7 +1041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1071,12 +1073,12 @@
 </file>
 
 <file path=xl/comments24.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1700-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1102,7 +1104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1700-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1134,12 +1136,12 @@
 </file>
 
 <file path=xl/comments25.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1165,7 +1167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1800-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1197,12 +1199,12 @@
 </file>
 
 <file path=xl/comments26.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1900-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1228,7 +1230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1900-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1260,12 +1262,12 @@
 </file>
 
 <file path=xl/comments27.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1291,7 +1293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1A00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1323,12 +1325,12 @@
 </file>
 
 <file path=xl/comments28.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1354,7 +1356,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1B00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1386,12 +1388,12 @@
 </file>
 
 <file path=xl/comments29.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1C00-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1417,7 +1419,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-1C00-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1449,12 +1451,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1480,7 +1482,70 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments30.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{6EB8D5C4-D439-488F-AA5C-66597A2E7D00}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{E73E5057-DBDF-4BA2-8BCE-3266BCF7608E}">
       <text>
         <r>
           <rPr>
@@ -1512,12 +1577,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1543,7 +1608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1575,12 +1640,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1606,7 +1671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1638,12 +1703,12 @@
 </file>
 
 <file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1669,7 +1734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1701,12 +1766,12 @@
 </file>
 
 <file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1732,7 +1797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1764,12 +1829,12 @@
 </file>
 
 <file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1795,7 +1860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1827,12 +1892,12 @@
 </file>
 
 <file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Кайлюбаев Ерлан Сейтканулы</author>
   </authors>
   <commentList>
-    <comment ref="J11" authorId="0" shapeId="0">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
       <text>
         <r>
           <rPr>
@@ -1858,7 +1923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
       <text>
         <r>
           <rPr>
@@ -1890,7 +1955,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8870" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -2984,7 +3049,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -3504,7 +3569,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4383,6 +4448,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4400,64 +4471,64 @@
     </xf>
   </cellXfs>
   <cellStyles count="58">
-    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2"/>
-    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 3 2" xfId="3"/>
+    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal_Transport daily dispatch report  16-22 ,  March  2009 3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 12" xfId="4"/>
-    <cellStyle name="Обычный 2" xfId="5"/>
-    <cellStyle name="Обычный 2 10" xfId="6"/>
-    <cellStyle name="Обычный 2 10 2" xfId="11"/>
-    <cellStyle name="Обычный 2 10 2 2" xfId="14"/>
-    <cellStyle name="Обычный 2 10 2 2 2" xfId="20"/>
-    <cellStyle name="Обычный 2 10 2 2 2 2" xfId="32"/>
-    <cellStyle name="Обычный 2 10 2 2 2 2 2" xfId="56"/>
-    <cellStyle name="Обычный 2 10 2 2 2 3" xfId="44"/>
-    <cellStyle name="Обычный 2 10 2 2 3" xfId="26"/>
-    <cellStyle name="Обычный 2 10 2 2 3 2" xfId="50"/>
-    <cellStyle name="Обычный 2 10 2 2 4" xfId="38"/>
-    <cellStyle name="Обычный 2 10 2 3" xfId="17"/>
-    <cellStyle name="Обычный 2 10 2 3 2" xfId="29"/>
-    <cellStyle name="Обычный 2 10 2 3 2 2" xfId="53"/>
-    <cellStyle name="Обычный 2 10 2 3 3" xfId="41"/>
-    <cellStyle name="Обычный 2 10 2 4" xfId="23"/>
-    <cellStyle name="Обычный 2 10 2 4 2" xfId="47"/>
-    <cellStyle name="Обычный 2 10 2 5" xfId="35"/>
-    <cellStyle name="Обычный 2 10 3" xfId="12"/>
-    <cellStyle name="Обычный 2 10 3 2" xfId="15"/>
-    <cellStyle name="Обычный 2 10 3 2 2" xfId="21"/>
-    <cellStyle name="Обычный 2 10 3 2 2 2" xfId="33"/>
-    <cellStyle name="Обычный 2 10 3 2 2 2 2" xfId="57"/>
-    <cellStyle name="Обычный 2 10 3 2 2 3" xfId="45"/>
-    <cellStyle name="Обычный 2 10 3 2 3" xfId="27"/>
-    <cellStyle name="Обычный 2 10 3 2 3 2" xfId="51"/>
-    <cellStyle name="Обычный 2 10 3 2 4" xfId="39"/>
-    <cellStyle name="Обычный 2 10 3 3" xfId="18"/>
-    <cellStyle name="Обычный 2 10 3 3 2" xfId="30"/>
-    <cellStyle name="Обычный 2 10 3 3 2 2" xfId="54"/>
-    <cellStyle name="Обычный 2 10 3 3 3" xfId="42"/>
-    <cellStyle name="Обычный 2 10 3 4" xfId="24"/>
-    <cellStyle name="Обычный 2 10 3 4 2" xfId="48"/>
-    <cellStyle name="Обычный 2 10 3 5" xfId="36"/>
-    <cellStyle name="Обычный 2 10 4" xfId="13"/>
-    <cellStyle name="Обычный 2 10 4 2" xfId="19"/>
-    <cellStyle name="Обычный 2 10 4 2 2" xfId="31"/>
-    <cellStyle name="Обычный 2 10 4 2 2 2" xfId="55"/>
-    <cellStyle name="Обычный 2 10 4 2 3" xfId="43"/>
-    <cellStyle name="Обычный 2 10 4 3" xfId="25"/>
-    <cellStyle name="Обычный 2 10 4 3 2" xfId="49"/>
-    <cellStyle name="Обычный 2 10 4 4" xfId="37"/>
-    <cellStyle name="Обычный 2 10 5" xfId="16"/>
-    <cellStyle name="Обычный 2 10 5 2" xfId="28"/>
-    <cellStyle name="Обычный 2 10 5 2 2" xfId="52"/>
-    <cellStyle name="Обычный 2 10 5 3" xfId="40"/>
-    <cellStyle name="Обычный 2 10 6" xfId="22"/>
-    <cellStyle name="Обычный 2 10 6 2" xfId="46"/>
-    <cellStyle name="Обычный 2 10 7" xfId="34"/>
-    <cellStyle name="Обычный 3" xfId="7"/>
-    <cellStyle name="Обычный 3 2 2" xfId="8"/>
-    <cellStyle name="Обычный 4" xfId="1"/>
-    <cellStyle name="Обычный 5" xfId="9"/>
-    <cellStyle name="Обычный 9" xfId="10"/>
+    <cellStyle name="Обычный 12" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Обычный 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Обычный 2 10" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="Обычный 2 10 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Обычный 2 10 2 2" xfId="14" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 2 2" xfId="32" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 2 2 2" xfId="56" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 2 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 3" xfId="26" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 3 2" xfId="50" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Обычный 2 10 2 2 4" xfId="38" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Обычный 2 10 2 3" xfId="17" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Обычный 2 10 2 3 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Обычный 2 10 2 3 2 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Обычный 2 10 2 3 3" xfId="41" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Обычный 2 10 2 4" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Обычный 2 10 2 4 2" xfId="47" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Обычный 2 10 2 5" xfId="35" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Обычный 2 10 3" xfId="12" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Обычный 2 10 3 2" xfId="15" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 2 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 2 2 2" xfId="57" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 2 3" xfId="45" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 3" xfId="27" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 3 2" xfId="51" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Обычный 2 10 3 2 4" xfId="39" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Обычный 2 10 3 3" xfId="18" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Обычный 2 10 3 3 2" xfId="30" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Обычный 2 10 3 3 2 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Обычный 2 10 3 3 3" xfId="42" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Обычный 2 10 3 4" xfId="24" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Обычный 2 10 3 4 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Обычный 2 10 3 5" xfId="36" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Обычный 2 10 4" xfId="13" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Обычный 2 10 4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Обычный 2 10 4 2 2" xfId="31" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Обычный 2 10 4 2 2 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Обычный 2 10 4 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Обычный 2 10 4 3" xfId="25" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Обычный 2 10 4 3 2" xfId="49" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Обычный 2 10 4 4" xfId="37" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Обычный 2 10 5" xfId="16" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Обычный 2 10 5 2" xfId="28" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Обычный 2 10 5 2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Обычный 2 10 5 3" xfId="40" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Обычный 2 10 6" xfId="22" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Обычный 2 10 6 2" xfId="46" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Обычный 2 10 7" xfId="34" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Обычный 3" xfId="7" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Обычный 3 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Обычный 4" xfId="1" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Обычный 5" xfId="9" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Обычный 9" xfId="10" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -4773,7 +4844,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4864,10 +4935,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4892,10 +4963,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6298,14 +6369,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6530,19 +6601,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6564,7 +6635,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -7015,7 +7086,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7106,10 +7177,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -7134,10 +7205,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8546,14 +8617,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8783,19 +8854,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8818,7 +8889,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9326,7 +9397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9417,10 +9488,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9445,10 +9516,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10850,14 +10921,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -11082,19 +11153,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -11116,7 +11187,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11572,7 +11643,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11663,10 +11734,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11691,10 +11762,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -13096,14 +13167,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13328,19 +13399,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13362,7 +13433,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13818,7 +13889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -13909,10 +13980,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -13937,10 +14008,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15342,14 +15413,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15574,19 +15645,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15608,7 +15679,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -16064,7 +16135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -16155,10 +16226,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -16183,10 +16254,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17588,14 +17659,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17820,19 +17891,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17854,7 +17925,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18310,7 +18381,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18401,10 +18472,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18429,10 +18500,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19834,14 +19905,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -20066,19 +20137,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -20100,7 +20171,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20560,7 +20631,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -20651,10 +20722,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20679,10 +20750,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -22084,14 +22155,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22316,19 +22387,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22350,7 +22421,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22809,7 +22880,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -22900,10 +22971,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22928,10 +22999,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24333,14 +24404,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24565,19 +24636,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24599,7 +24670,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -25058,7 +25129,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -25149,10 +25220,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -25177,10 +25248,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26576,14 +26647,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26808,19 +26879,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26842,7 +26913,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27299,7 +27370,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -27390,10 +27461,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27418,10 +27489,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28816,14 +28887,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -29048,19 +29119,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -29082,7 +29153,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29539,7 +29610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -29630,10 +29701,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29658,10 +29729,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -31067,14 +31138,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31299,19 +31370,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31333,7 +31404,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31795,7 +31866,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -31886,10 +31957,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31914,10 +31985,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33312,14 +33383,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33544,19 +33615,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33578,7 +33649,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -34035,7 +34106,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -34126,10 +34197,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -34154,10 +34225,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35552,14 +35623,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35784,19 +35855,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35818,7 +35889,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36275,7 +36346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -36366,10 +36437,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36394,10 +36465,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37792,14 +37863,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -38024,19 +38095,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -38058,7 +38129,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38515,7 +38586,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -38606,10 +38677,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38634,10 +38705,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -40032,14 +40103,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -40264,19 +40335,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40298,7 +40369,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40755,7 +40826,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -40846,10 +40917,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40874,10 +40945,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -42272,14 +42343,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42504,19 +42575,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42538,7 +42609,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -42995,7 +43066,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -43086,10 +43157,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -43114,10 +43185,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -44514,14 +44585,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44746,19 +44817,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44780,7 +44851,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -45244,7 +45315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -45335,10 +45406,10 @@
       <c r="C2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="298" t="s">
         <v>4</v>
       </c>
@@ -45363,10 +45434,10 @@
       <c r="M2" s="299" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="298" t="s">
         <v>13</v>
       </c>
@@ -46763,14 +46834,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -46995,19 +47066,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -47029,7 +47100,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -47488,7 +47559,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -47579,10 +47650,10 @@
       <c r="C2" s="300" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="300" t="s">
         <v>4</v>
       </c>
@@ -47607,10 +47678,10 @@
       <c r="M2" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="300" t="s">
         <v>13</v>
       </c>
@@ -49007,14 +49078,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -49239,19 +49310,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -49273,7 +49344,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -49732,7 +49803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -49823,10 +49894,10 @@
       <c r="C2" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="302" t="s">
         <v>4</v>
       </c>
@@ -49851,10 +49922,10 @@
       <c r="M2" s="303" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="302" t="s">
         <v>13</v>
       </c>
@@ -51251,14 +51322,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -51483,19 +51554,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -51517,7 +51588,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -51976,7 +52047,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -52067,10 +52138,10 @@
       <c r="C2" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="304" t="s">
         <v>4</v>
       </c>
@@ -52095,10 +52166,10 @@
       <c r="M2" s="305" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="304" t="s">
         <v>13</v>
       </c>
@@ -53495,14 +53566,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -53727,19 +53798,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -53761,7 +53832,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -54220,7 +54291,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -54311,10 +54382,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -54339,10 +54410,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -55746,14 +55817,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -55978,19 +56049,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -56012,7 +56083,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56474,8 +56545,2252 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF90468-0A67-4BE7-A813-A185CC11259C}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="306" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="306" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="308" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="308"/>
+      <c r="F2" s="306" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="306" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="307" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="306" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="306" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="307" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="307" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="307" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="309" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="309"/>
+      <c r="P2" s="306" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="306" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="306" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="306" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="310" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+      <c r="M45" s="219" t="s">
+        <v>181</v>
+      </c>
+      <c r="N45" s="219">
+        <v>14</v>
+      </c>
+      <c r="O45" s="219">
+        <v>14</v>
+      </c>
+      <c r="P45" s="220">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="221"/>
+      <c r="S45" s="240"/>
+      <c r="T45" s="229"/>
+    </row>
+    <row r="46" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="226"/>
+      <c r="B46" s="226"/>
+      <c r="C46" s="226"/>
+      <c r="D46" s="226"/>
+      <c r="E46" s="226"/>
+      <c r="F46" s="226"/>
+      <c r="G46" s="225"/>
+      <c r="H46" s="225"/>
+      <c r="I46" s="225"/>
+      <c r="J46" s="241"/>
+      <c r="K46" s="233"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143" t="s">
+        <v>187</v>
+      </c>
+      <c r="N46" s="143">
+        <v>8</v>
+      </c>
+      <c r="O46" s="143">
+        <v>8</v>
+      </c>
+      <c r="P46" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="200"/>
+      <c r="R46" s="148"/>
+      <c r="S46" s="228"/>
+      <c r="T46" s="229"/>
+    </row>
+    <row r="47" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="225"/>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="225"/>
+      <c r="I47" s="225"/>
+      <c r="J47" s="242"/>
+      <c r="L47" s="150"/>
+      <c r="M47" s="146" t="s">
+        <v>193</v>
+      </c>
+      <c r="N47" s="152">
+        <v>170</v>
+      </c>
+      <c r="O47" s="152">
+        <v>170</v>
+      </c>
+      <c r="P47" s="153">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="207"/>
+      <c r="R47" s="208"/>
+      <c r="S47" s="243"/>
+      <c r="T47" s="229"/>
+    </row>
+    <row r="48" spans="1:20" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A48" s="226"/>
+      <c r="B48" s="226"/>
+      <c r="C48" s="226"/>
+      <c r="D48" s="226"/>
+      <c r="E48" s="226"/>
+      <c r="F48" s="226"/>
+      <c r="G48" s="226"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="242"/>
+      <c r="L48" s="202"/>
+      <c r="M48" s="202"/>
+      <c r="N48" s="202"/>
+      <c r="O48" s="202"/>
+      <c r="P48" s="202"/>
+      <c r="Q48" s="209"/>
+      <c r="R48" s="210"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="229"/>
+    </row>
+    <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A49" s="312" t="s">
+        <v>196</v>
+      </c>
+      <c r="B49" s="313" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
+      <c r="J49" s="242"/>
+      <c r="L49" s="141" t="s">
+        <v>194</v>
+      </c>
+      <c r="M49" s="141"/>
+      <c r="N49" s="141">
+        <v>30</v>
+      </c>
+      <c r="O49" s="141">
+        <v>28</v>
+      </c>
+      <c r="P49" s="151">
+        <v>-2</v>
+      </c>
+      <c r="Q49" s="296" t="s">
+        <v>362</v>
+      </c>
+      <c r="R49" s="211"/>
+      <c r="S49" s="245"/>
+    </row>
+    <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="312"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>160</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -56566,10 +58881,10 @@
       <c r="C2" s="124" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="124" t="s">
         <v>4</v>
       </c>
@@ -56594,10 +58909,10 @@
       <c r="M2" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="124" t="s">
         <v>13</v>
       </c>
@@ -58001,14 +60316,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -58233,19 +60548,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -58267,7 +60582,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -58728,7 +61043,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58819,10 +61134,10 @@
       <c r="C2" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="126" t="s">
         <v>4</v>
       </c>
@@ -58847,10 +61162,10 @@
       <c r="M2" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="126" t="s">
         <v>13</v>
       </c>
@@ -60254,14 +62569,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -60486,19 +62801,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -60520,7 +62835,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -60982,7 +63297,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -61073,10 +63388,10 @@
       <c r="C2" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="129" t="s">
         <v>4</v>
       </c>
@@ -61101,10 +63416,10 @@
       <c r="M2" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="129" t="s">
         <v>13</v>
       </c>
@@ -62508,14 +64823,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -62740,19 +65055,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -62774,7 +65089,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -63235,7 +65550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -63326,10 +65641,10 @@
       <c r="C2" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="131" t="s">
         <v>4</v>
       </c>
@@ -63354,10 +65669,10 @@
       <c r="M2" s="132" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="131" t="s">
         <v>13</v>
       </c>
@@ -64761,14 +67076,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -64993,19 +67308,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -65027,7 +67342,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -65486,7 +67801,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -65577,10 +67892,10 @@
       <c r="C2" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="133" t="s">
         <v>4</v>
       </c>
@@ -65605,10 +67920,10 @@
       <c r="M2" s="134" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="133" t="s">
         <v>13</v>
       </c>
@@ -67012,14 +69327,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -67244,19 +69559,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -67278,7 +69593,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -67737,7 +70052,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T62"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -67828,10 +70143,10 @@
       <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="306" t="s">
+      <c r="D2" s="308" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="306"/>
+      <c r="E2" s="308"/>
       <c r="F2" s="135" t="s">
         <v>4</v>
       </c>
@@ -67856,10 +70171,10 @@
       <c r="M2" s="136" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="307" t="s">
+      <c r="N2" s="309" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="307"/>
+      <c r="O2" s="309"/>
       <c r="P2" s="135" t="s">
         <v>13</v>
       </c>
@@ -69263,14 +71578,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="308" t="s">
+      <c r="L41" s="310" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="308"/>
-      <c r="N41" s="308"/>
-      <c r="O41" s="308"/>
-      <c r="P41" s="308"/>
-      <c r="Q41" s="309"/>
+      <c r="M41" s="310"/>
+      <c r="N41" s="310"/>
+      <c r="O41" s="310"/>
+      <c r="P41" s="310"/>
+      <c r="Q41" s="311"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -69495,19 +71810,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="310" t="s">
+      <c r="A49" s="312" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="311" t="s">
+      <c r="B49" s="313" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="311"/>
-      <c r="D49" s="311"/>
-      <c r="E49" s="311"/>
-      <c r="F49" s="312"/>
-      <c r="G49" s="312"/>
-      <c r="H49" s="312"/>
-      <c r="I49" s="312"/>
+      <c r="C49" s="313"/>
+      <c r="D49" s="313"/>
+      <c r="E49" s="313"/>
+      <c r="F49" s="314"/>
+      <c r="G49" s="314"/>
+      <c r="H49" s="314"/>
+      <c r="I49" s="314"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -69529,7 +71844,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="310"/>
+      <c r="A50" s="312"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>

--- a/raw/MS.xlsx
+++ b/raw/MS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\ДТТ\Диспетчер\Сводки Ерлан - Бауыржан\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8B0A7EE-B13A-4786-B400-B03E9A0C881B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B694AFF-77CE-4A21-BAAD-056E499B0FD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="29" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="2" r:id="rId1"/>
@@ -43,6 +43,7 @@
     <sheet name="28" sheetId="101" r:id="rId28"/>
     <sheet name="29" sheetId="102" r:id="rId29"/>
     <sheet name="30" sheetId="103" r:id="rId30"/>
+    <sheet name="31" sheetId="104" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1576,6 +1577,69 @@
 </comments>
 </file>
 
+<file path=xl/comments31.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Кайлюбаев Ерлан Сейтканулы</author>
+  </authors>
+  <commentList>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{7AE9ED6B-442E-4623-879F-EEDD0F607FC2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+03-10-2026 бастап қосылды обновление</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B57" authorId="0" shapeId="0" xr:uid="{12E8FB81-D2B8-4963-B3AE-1BE4D6621B7C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t>Кайлюбаев Ерлан Сейтканулы:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="204"/>
+          </rPr>
+          <t xml:space="preserve">
+Келісім шарт 10 күнге
+25-09-2026 бастады түстен кейін.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
@@ -1955,7 +2019,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9482" uniqueCount="363">
   <si>
     <t>№</t>
   </si>
@@ -3569,7 +3633,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="315">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4454,6 +4518,12 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4935,10 +5005,10 @@
       <c r="C2" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="113" t="s">
         <v>4</v>
       </c>
@@ -4963,10 +5033,10 @@
       <c r="M2" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="113" t="s">
         <v>13</v>
       </c>
@@ -6369,14 +6439,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -6601,19 +6671,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -6635,7 +6705,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -7177,10 +7247,10 @@
       <c r="C2" s="250" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="250" t="s">
         <v>4</v>
       </c>
@@ -7205,10 +7275,10 @@
       <c r="M2" s="251" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="250" t="s">
         <v>13</v>
       </c>
@@ -8617,14 +8687,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
       <c r="R41" s="138"/>
       <c r="S41" s="138"/>
       <c r="T41" s="138"/>
@@ -8854,19 +8924,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="K49" s="138"/>
       <c r="L49" s="141" t="s">
@@ -8889,7 +8959,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -9488,10 +9558,10 @@
       <c r="C2" s="257" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="257" t="s">
         <v>4</v>
       </c>
@@ -9516,10 +9586,10 @@
       <c r="M2" s="258" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="257" t="s">
         <v>13</v>
       </c>
@@ -10921,14 +10991,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -11153,19 +11223,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -11187,7 +11257,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -11734,10 +11804,10 @@
       <c r="C2" s="259" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="259" t="s">
         <v>4</v>
       </c>
@@ -11762,10 +11832,10 @@
       <c r="M2" s="260" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="259" t="s">
         <v>13</v>
       </c>
@@ -13167,14 +13237,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -13399,19 +13469,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -13433,7 +13503,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -13980,10 +14050,10 @@
       <c r="C2" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="261" t="s">
         <v>4</v>
       </c>
@@ -14008,10 +14078,10 @@
       <c r="M2" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="261" t="s">
         <v>13</v>
       </c>
@@ -15413,14 +15483,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -15645,19 +15715,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -15679,7 +15749,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -16226,10 +16296,10 @@
       <c r="C2" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="263" t="s">
         <v>4</v>
       </c>
@@ -16254,10 +16324,10 @@
       <c r="M2" s="264" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="263" t="s">
         <v>13</v>
       </c>
@@ -17659,14 +17729,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -17891,19 +17961,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -17925,7 +17995,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -18472,10 +18542,10 @@
       <c r="C2" s="265" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="265" t="s">
         <v>4</v>
       </c>
@@ -18500,10 +18570,10 @@
       <c r="M2" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="265" t="s">
         <v>13</v>
       </c>
@@ -19905,14 +19975,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -20137,19 +20207,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -20171,7 +20241,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -20722,10 +20792,10 @@
       <c r="C2" s="267" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="267" t="s">
         <v>4</v>
       </c>
@@ -20750,10 +20820,10 @@
       <c r="M2" s="268" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="267" t="s">
         <v>13</v>
       </c>
@@ -22155,14 +22225,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -22387,19 +22457,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -22421,7 +22491,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -22971,10 +23041,10 @@
       <c r="C2" s="270" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="270" t="s">
         <v>4</v>
       </c>
@@ -22999,10 +23069,10 @@
       <c r="M2" s="271" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="270" t="s">
         <v>13</v>
       </c>
@@ -24404,14 +24474,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -24636,19 +24706,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -24670,7 +24740,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -25220,10 +25290,10 @@
       <c r="C2" s="278" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="278" t="s">
         <v>4</v>
       </c>
@@ -25248,10 +25318,10 @@
       <c r="M2" s="279" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="278" t="s">
         <v>13</v>
       </c>
@@ -26647,14 +26717,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -26879,19 +26949,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -26913,7 +26983,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -27461,10 +27531,10 @@
       <c r="C2" s="280" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="280" t="s">
         <v>4</v>
       </c>
@@ -27489,10 +27559,10 @@
       <c r="M2" s="281" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="280" t="s">
         <v>13</v>
       </c>
@@ -28887,14 +28957,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -29119,19 +29189,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -29153,7 +29223,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -29701,10 +29771,10 @@
       <c r="C2" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="115" t="s">
         <v>4</v>
       </c>
@@ -29729,10 +29799,10 @@
       <c r="M2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="115" t="s">
         <v>13</v>
       </c>
@@ -31138,14 +31208,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -31370,19 +31440,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -31404,7 +31474,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -31957,10 +32027,10 @@
       <c r="C2" s="284" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="284" t="s">
         <v>4</v>
       </c>
@@ -31985,10 +32055,10 @@
       <c r="M2" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="284" t="s">
         <v>13</v>
       </c>
@@ -33383,14 +33453,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -33615,19 +33685,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -33649,7 +33719,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -34197,10 +34267,10 @@
       <c r="C2" s="286" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="286" t="s">
         <v>4</v>
       </c>
@@ -34225,10 +34295,10 @@
       <c r="M2" s="287" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="286" t="s">
         <v>13</v>
       </c>
@@ -35623,14 +35693,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -35855,19 +35925,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -35889,7 +35959,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -36437,10 +36507,10 @@
       <c r="C2" s="288" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="288" t="s">
         <v>4</v>
       </c>
@@ -36465,10 +36535,10 @@
       <c r="M2" s="289" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="288" t="s">
         <v>13</v>
       </c>
@@ -37863,14 +37933,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -38095,19 +38165,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -38129,7 +38199,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -38677,10 +38747,10 @@
       <c r="C2" s="290" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="290" t="s">
         <v>4</v>
       </c>
@@ -38705,10 +38775,10 @@
       <c r="M2" s="291" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="290" t="s">
         <v>13</v>
       </c>
@@ -40103,14 +40173,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -40335,19 +40405,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -40369,7 +40439,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -40917,10 +40987,10 @@
       <c r="C2" s="292" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="292" t="s">
         <v>4</v>
       </c>
@@ -40945,10 +41015,10 @@
       <c r="M2" s="293" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="292" t="s">
         <v>13</v>
       </c>
@@ -42343,14 +42413,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -42575,19 +42645,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -42609,7 +42679,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -43157,10 +43227,10 @@
       <c r="C2" s="294" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="294" t="s">
         <v>4</v>
       </c>
@@ -43185,10 +43255,10 @@
       <c r="M2" s="295" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="294" t="s">
         <v>13</v>
       </c>
@@ -44585,14 +44655,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -44817,19 +44887,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -44851,7 +44921,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -45406,10 +45476,10 @@
       <c r="C2" s="298" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="298" t="s">
         <v>4</v>
       </c>
@@ -45434,10 +45504,10 @@
       <c r="M2" s="299" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="298" t="s">
         <v>13</v>
       </c>
@@ -46834,14 +46904,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -47066,19 +47136,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -47100,7 +47170,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -47650,10 +47720,10 @@
       <c r="C2" s="300" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="300" t="s">
         <v>4</v>
       </c>
@@ -47678,10 +47748,10 @@
       <c r="M2" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="300" t="s">
         <v>13</v>
       </c>
@@ -49078,14 +49148,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -49310,19 +49380,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -49344,7 +49414,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -49894,10 +49964,10 @@
       <c r="C2" s="302" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="302" t="s">
         <v>4</v>
       </c>
@@ -49922,10 +49992,10 @@
       <c r="M2" s="303" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="302" t="s">
         <v>13</v>
       </c>
@@ -51322,14 +51392,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -51554,19 +51624,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -51588,7 +51658,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -52138,10 +52208,10 @@
       <c r="C2" s="304" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="304" t="s">
         <v>4</v>
       </c>
@@ -52166,10 +52236,10 @@
       <c r="M2" s="305" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="304" t="s">
         <v>13</v>
       </c>
@@ -53566,14 +53636,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -53798,19 +53868,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -53832,7 +53902,7 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="146" t="s">
         <v>198</v>
       </c>
@@ -54382,10 +54452,10 @@
       <c r="C2" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="120" t="s">
         <v>4</v>
       </c>
@@ -54410,10 +54480,10 @@
       <c r="M2" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="120" t="s">
         <v>13</v>
       </c>
@@ -55817,14 +55887,14 @@
       <c r="I41" s="93"/>
       <c r="J41" s="95"/>
       <c r="K41" s="95"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="86"/>
@@ -56049,19 +56119,19 @@
       <c r="T48" s="92"/>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="105"/>
       <c r="L49" s="4" t="s">
         <v>194</v>
@@ -56083,7 +56153,7 @@
       <c r="S49" s="108"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
       <c r="B50" s="9" t="s">
         <v>198</v>
       </c>
@@ -56637,10 +56707,10 @@
       <c r="C2" s="306" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="308" t="s">
+      <c r="D2" s="310" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="308"/>
+      <c r="E2" s="310"/>
       <c r="F2" s="306" t="s">
         <v>4</v>
       </c>
@@ -56665,10 +56735,10 @@
       <c r="M2" s="307" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="309" t="s">
+      <c r="N2" s="311" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="309"/>
+      <c r="O2" s="311"/>
       <c r="P2" s="306" t="s">
         <v>13</v>
       </c>
@@ -58065,14 +58135,14 @@
       <c r="I41" s="230"/>
       <c r="J41" s="232"/>
       <c r="K41" s="232"/>
-      <c r="L41" s="310" t="s">
+      <c r="L41" s="312" t="s">
         <v>176</v>
       </c>
-      <c r="M41" s="310"/>
-      <c r="N41" s="310"/>
-      <c r="O41" s="310"/>
-      <c r="P41" s="310"/>
-      <c r="Q41" s="311"/>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
     </row>
     <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="223"/>
@@ -58297,19 +58367,19 @@
       <c r="T48" s="229"/>
     </row>
     <row r="49" spans="1:19" ht="26.4" x14ac:dyDescent="0.25">
-      <c r="A49" s="312" t="s">
+      <c r="A49" s="314" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="313" t="s">
+      <c r="B49" s="315" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="313"/>
-      <c r="D49" s="313"/>
-      <c r="E49" s="313"/>
-      <c r="F49" s="314"/>
-      <c r="G49" s="314"/>
-      <c r="H49" s="314"/>
-      <c r="I49" s="314"/>
+      <c r="C49" s="315"/>
+      <c r="D49" s="315"/>
+      <c r="E49" s="315"/>
+      <c r="F49" s="316"/>
+      <c r="G49" s="316"/>
+      <c r="H49" s="316"/>
+      <c r="I49" s="316"/>
       <c r="J49" s="242"/>
       <c r="L49" s="141" t="s">
         <v>194</v>
@@ -58331,7 +58401,2251 @@
       <c r="S49" s="245"/>
     </row>
     <row r="50" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
-      <c r="A50" s="312"/>
+      <c r="A50" s="314"/>
+      <c r="B50" s="146" t="s">
+        <v>198</v>
+      </c>
+      <c r="C50" s="146" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="146" t="s">
+        <v>200</v>
+      </c>
+      <c r="F50" s="146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G50" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="H50" s="173" t="s">
+        <v>202</v>
+      </c>
+      <c r="I50" s="158" t="s">
+        <v>184</v>
+      </c>
+      <c r="J50" s="242"/>
+      <c r="L50" s="229"/>
+      <c r="M50" s="229"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="229"/>
+      <c r="P50" s="229"/>
+      <c r="Q50" s="229"/>
+      <c r="R50" s="229"/>
+      <c r="S50" s="229"/>
+    </row>
+    <row r="51" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="200"/>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
+      <c r="I51" s="198"/>
+      <c r="J51" s="198"/>
+      <c r="L51" s="229"/>
+      <c r="M51" s="229"/>
+      <c r="N51" s="229"/>
+      <c r="O51" s="229"/>
+      <c r="P51" s="229"/>
+      <c r="Q51" s="229"/>
+      <c r="R51" s="229"/>
+      <c r="S51" s="229"/>
+    </row>
+    <row r="52" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A52" s="200">
+        <v>13</v>
+      </c>
+      <c r="B52" s="200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C52" s="145">
+        <v>160</v>
+      </c>
+      <c r="D52" s="158">
+        <v>170</v>
+      </c>
+      <c r="E52" s="176">
+        <v>130</v>
+      </c>
+      <c r="F52" s="146">
+        <v>40</v>
+      </c>
+      <c r="G52" s="158">
+        <v>170</v>
+      </c>
+      <c r="H52" s="173">
+        <v>10</v>
+      </c>
+      <c r="I52" s="175">
+        <v>0</v>
+      </c>
+      <c r="J52" s="200" t="s">
+        <v>202</v>
+      </c>
+      <c r="L52" s="229"/>
+      <c r="M52" s="229"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="229"/>
+      <c r="Q52" s="229"/>
+      <c r="R52" s="229"/>
+      <c r="S52" s="229"/>
+    </row>
+    <row r="53" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A53" s="200">
+        <v>16</v>
+      </c>
+      <c r="B53" s="200" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="145">
+        <v>4</v>
+      </c>
+      <c r="D53" s="158">
+        <v>4</v>
+      </c>
+      <c r="E53" s="141">
+        <v>4</v>
+      </c>
+      <c r="F53" s="146">
+        <v>0</v>
+      </c>
+      <c r="G53" s="158">
+        <v>3</v>
+      </c>
+      <c r="H53" s="173">
+        <v>0</v>
+      </c>
+      <c r="I53" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J53" s="190" t="s">
+        <v>291</v>
+      </c>
+      <c r="L53" s="203"/>
+      <c r="M53" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="N53" s="140" t="s">
+        <v>204</v>
+      </c>
+      <c r="O53" s="140" t="s">
+        <v>205</v>
+      </c>
+      <c r="P53" s="140"/>
+      <c r="Q53" s="182" t="s">
+        <v>206</v>
+      </c>
+      <c r="R53" s="215"/>
+      <c r="S53" s="229"/>
+    </row>
+    <row r="54" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="200">
+        <v>19</v>
+      </c>
+      <c r="B54" s="200" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="145">
+        <v>0</v>
+      </c>
+      <c r="D54" s="158">
+        <v>0</v>
+      </c>
+      <c r="E54" s="141">
+        <v>0</v>
+      </c>
+      <c r="F54" s="146">
+        <v>0</v>
+      </c>
+      <c r="G54" s="158">
+        <v>0</v>
+      </c>
+      <c r="H54" s="173">
+        <v>0</v>
+      </c>
+      <c r="I54" s="175">
+        <v>0</v>
+      </c>
+      <c r="J54" s="190"/>
+      <c r="L54" s="203"/>
+      <c r="M54" s="254" t="s">
+        <v>290</v>
+      </c>
+      <c r="N54" s="252" t="s">
+        <v>268</v>
+      </c>
+      <c r="O54" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P54" s="200"/>
+      <c r="Q54" s="199" t="s">
+        <v>207</v>
+      </c>
+      <c r="R54" s="214"/>
+      <c r="S54" s="229"/>
+    </row>
+    <row r="55" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="200">
+        <v>20</v>
+      </c>
+      <c r="B55" s="200" t="s">
+        <v>212</v>
+      </c>
+      <c r="C55" s="145">
+        <v>19</v>
+      </c>
+      <c r="D55" s="158">
+        <v>19</v>
+      </c>
+      <c r="E55" s="141">
+        <v>19</v>
+      </c>
+      <c r="F55" s="146">
+        <v>0</v>
+      </c>
+      <c r="G55" s="158">
+        <v>19</v>
+      </c>
+      <c r="H55" s="173">
+        <v>0</v>
+      </c>
+      <c r="I55" s="175">
+        <v>0</v>
+      </c>
+      <c r="J55" s="200"/>
+      <c r="L55" s="203"/>
+      <c r="M55" s="256" t="s">
+        <v>325</v>
+      </c>
+      <c r="N55" s="255" t="s">
+        <v>283</v>
+      </c>
+      <c r="O55" s="253" t="s">
+        <v>291</v>
+      </c>
+      <c r="P55" s="200"/>
+      <c r="Q55" s="199" t="s">
+        <v>209</v>
+      </c>
+      <c r="R55" s="214"/>
+      <c r="S55" s="229"/>
+    </row>
+    <row r="56" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A56" s="200">
+        <v>30</v>
+      </c>
+      <c r="B56" s="200" t="s">
+        <v>213</v>
+      </c>
+      <c r="C56" s="151">
+        <v>0</v>
+      </c>
+      <c r="D56" s="158">
+        <v>0</v>
+      </c>
+      <c r="E56" s="146">
+        <v>0</v>
+      </c>
+      <c r="F56" s="146">
+        <v>0</v>
+      </c>
+      <c r="G56" s="158">
+        <v>0</v>
+      </c>
+      <c r="H56" s="173">
+        <v>0</v>
+      </c>
+      <c r="I56" s="175">
+        <v>0</v>
+      </c>
+      <c r="J56" s="190"/>
+      <c r="L56" s="203"/>
+      <c r="M56" s="193"/>
+      <c r="N56" s="194"/>
+      <c r="O56" s="200"/>
+      <c r="P56" s="200"/>
+      <c r="Q56" s="200"/>
+      <c r="R56" s="214"/>
+      <c r="S56" s="229"/>
+    </row>
+    <row r="57" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A57" s="200">
+        <v>38</v>
+      </c>
+      <c r="B57" s="297" t="s">
+        <v>288</v>
+      </c>
+      <c r="C57" s="151">
+        <v>0</v>
+      </c>
+      <c r="D57" s="158">
+        <v>0</v>
+      </c>
+      <c r="E57" s="146">
+        <v>0</v>
+      </c>
+      <c r="F57" s="146">
+        <v>0</v>
+      </c>
+      <c r="G57" s="158">
+        <v>0</v>
+      </c>
+      <c r="H57" s="173">
+        <v>0</v>
+      </c>
+      <c r="I57" s="175">
+        <v>0</v>
+      </c>
+      <c r="J57" s="190"/>
+      <c r="L57" s="203"/>
+      <c r="M57" s="193"/>
+      <c r="N57" s="194"/>
+      <c r="O57" s="200"/>
+      <c r="P57" s="200"/>
+      <c r="Q57" s="200"/>
+      <c r="R57" s="214"/>
+      <c r="S57" s="229"/>
+    </row>
+    <row r="58" spans="1:19" ht="13.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="200">
+        <v>27</v>
+      </c>
+      <c r="B58" s="200" t="s">
+        <v>214</v>
+      </c>
+      <c r="C58" s="151">
+        <v>2</v>
+      </c>
+      <c r="D58" s="158">
+        <v>2</v>
+      </c>
+      <c r="E58" s="146">
+        <v>1</v>
+      </c>
+      <c r="F58" s="146">
+        <v>1</v>
+      </c>
+      <c r="G58" s="158">
+        <v>2</v>
+      </c>
+      <c r="H58" s="173">
+        <v>0</v>
+      </c>
+      <c r="I58" s="175">
+        <v>0</v>
+      </c>
+      <c r="J58" s="190"/>
+      <c r="S58" s="229"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" s="200">
+        <v>40</v>
+      </c>
+      <c r="B59" s="200" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="151">
+        <v>4</v>
+      </c>
+      <c r="D59" s="158">
+        <v>4</v>
+      </c>
+      <c r="E59" s="146">
+        <v>4</v>
+      </c>
+      <c r="F59" s="146">
+        <v>0</v>
+      </c>
+      <c r="G59" s="158">
+        <v>4</v>
+      </c>
+      <c r="H59" s="173">
+        <v>0</v>
+      </c>
+      <c r="I59" s="175">
+        <v>0</v>
+      </c>
+      <c r="J59" s="200"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A60" s="200">
+        <v>63</v>
+      </c>
+      <c r="B60" s="200" t="s">
+        <v>216</v>
+      </c>
+      <c r="C60" s="151">
+        <v>1</v>
+      </c>
+      <c r="D60" s="158">
+        <v>1</v>
+      </c>
+      <c r="E60" s="146">
+        <v>0</v>
+      </c>
+      <c r="F60" s="146">
+        <v>0</v>
+      </c>
+      <c r="G60" s="158">
+        <v>0</v>
+      </c>
+      <c r="H60" s="173">
+        <v>0</v>
+      </c>
+      <c r="I60" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J60" s="200" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="201"/>
+      <c r="B61" s="202"/>
+      <c r="C61" s="213"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="202"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="202"/>
+    </row>
+    <row r="62" spans="1:19" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="201"/>
+      <c r="B62" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="C62" s="146">
+        <v>192</v>
+      </c>
+      <c r="D62" s="158">
+        <v>200</v>
+      </c>
+      <c r="E62" s="146">
+        <v>158</v>
+      </c>
+      <c r="F62" s="146">
+        <v>41</v>
+      </c>
+      <c r="G62" s="158">
+        <f>SUM(G52:G60)</f>
+        <v>198</v>
+      </c>
+      <c r="H62" s="173">
+        <v>10</v>
+      </c>
+      <c r="I62" s="175">
+        <v>-1</v>
+      </c>
+      <c r="J62" s="203"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="L41:Q41"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:I49"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B520BB9-D9D3-4B8C-91AA-4D7C95D2A2BC}">
+  <dimension ref="A1:T62"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.44140625" style="138" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="138" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" style="138" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" style="138" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" style="138" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" style="138" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="138" customWidth="1"/>
+    <col min="8" max="8" width="18.44140625" style="138" customWidth="1"/>
+    <col min="9" max="9" width="16" style="138" customWidth="1"/>
+    <col min="10" max="10" width="19.6640625" style="138" customWidth="1"/>
+    <col min="11" max="11" width="17" style="138" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="138" customWidth="1"/>
+    <col min="13" max="13" width="15.5546875" style="138" customWidth="1"/>
+    <col min="14" max="14" width="16.6640625" style="138" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" style="138" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" style="138" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="138" customWidth="1"/>
+    <col min="18" max="18" width="16.77734375" style="138" customWidth="1"/>
+    <col min="19" max="19" width="15.88671875" style="138" customWidth="1"/>
+    <col min="20" max="20" width="17" style="138" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="138"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A1" s="155"/>
+      <c r="B1" s="147">
+        <v>7</v>
+      </c>
+      <c r="C1" s="147">
+        <v>13</v>
+      </c>
+      <c r="D1" s="147">
+        <v>12</v>
+      </c>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147">
+        <v>18</v>
+      </c>
+      <c r="G1" s="147">
+        <v>11</v>
+      </c>
+      <c r="H1" s="147">
+        <v>11</v>
+      </c>
+      <c r="I1" s="147">
+        <v>2</v>
+      </c>
+      <c r="J1" s="147">
+        <v>6</v>
+      </c>
+      <c r="K1" s="147">
+        <v>16</v>
+      </c>
+      <c r="L1" s="147">
+        <v>15</v>
+      </c>
+      <c r="M1" s="147">
+        <v>6</v>
+      </c>
+      <c r="N1" s="147">
+        <v>21</v>
+      </c>
+      <c r="O1" s="147"/>
+      <c r="P1" s="147">
+        <v>1</v>
+      </c>
+      <c r="Q1" s="147">
+        <v>15</v>
+      </c>
+      <c r="R1" s="147">
+        <v>11</v>
+      </c>
+      <c r="S1" s="147">
+        <v>5</v>
+      </c>
+      <c r="T1" s="148"/>
+    </row>
+    <row r="2" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A2" s="146" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="308" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="308" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="310" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="310"/>
+      <c r="F2" s="308" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="308" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="309" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="308" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="308" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="309" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="309" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="309" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="311" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="311"/>
+      <c r="P2" s="308" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" s="308" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="308" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="308" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="149" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="146">
+        <v>1</v>
+      </c>
+      <c r="B3" s="192" t="s">
+        <v>226</v>
+      </c>
+      <c r="C3" s="191" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" s="191" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" s="193" t="s">
+        <v>356</v>
+      </c>
+      <c r="F3" s="191" t="s">
+        <v>294</v>
+      </c>
+      <c r="G3" s="191" t="s">
+        <v>295</v>
+      </c>
+      <c r="H3" s="192" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="283"/>
+      <c r="J3" s="192" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="191" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="193" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="193" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="191" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="192" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="192" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" s="192" t="s">
+        <v>231</v>
+      </c>
+      <c r="S3" s="192" t="s">
+        <v>221</v>
+      </c>
+      <c r="T3" s="200"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="146">
+        <v>2</v>
+      </c>
+      <c r="B4" s="192" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="191" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="191" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" s="193" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="192" t="s">
+        <v>233</v>
+      </c>
+      <c r="G4" s="192" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="192"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="139">
+        <v>1</v>
+      </c>
+      <c r="K4" s="191" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" s="192" t="s">
+        <v>30</v>
+      </c>
+      <c r="M4" s="192" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="191" t="s">
+        <v>297</v>
+      </c>
+      <c r="O4" s="192" t="s">
+        <v>144</v>
+      </c>
+      <c r="P4" s="283"/>
+      <c r="Q4" s="191" t="s">
+        <v>298</v>
+      </c>
+      <c r="R4" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="178" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="188"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="146">
+        <v>3</v>
+      </c>
+      <c r="B5" s="192" t="s">
+        <v>355</v>
+      </c>
+      <c r="C5" s="191" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="191" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="193" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="191" t="s">
+        <v>300</v>
+      </c>
+      <c r="G5" s="192" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="139">
+        <v>1</v>
+      </c>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="192" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="192" t="s">
+        <v>38</v>
+      </c>
+      <c r="M5" s="193" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5" s="191" t="s">
+        <v>301</v>
+      </c>
+      <c r="O5" s="192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="283"/>
+      <c r="Q5" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="R5" s="193" t="s">
+        <v>41</v>
+      </c>
+      <c r="S5" s="194"/>
+      <c r="T5" s="200"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="146">
+        <v>4</v>
+      </c>
+      <c r="B6" s="192" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="192" t="s">
+        <v>130</v>
+      </c>
+      <c r="D6" s="193" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="283"/>
+      <c r="F6" s="191" t="s">
+        <v>302</v>
+      </c>
+      <c r="G6" s="193" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" s="196"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="192" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="193" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6" s="192" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="192" t="s">
+        <v>237</v>
+      </c>
+      <c r="O6" s="192" t="s">
+        <v>152</v>
+      </c>
+      <c r="P6" s="283"/>
+      <c r="Q6" s="193" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="193" t="s">
+        <v>50</v>
+      </c>
+      <c r="S6" s="283"/>
+      <c r="T6" s="200"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="146">
+        <v>5</v>
+      </c>
+      <c r="B7" s="192" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="192" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="192" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="283"/>
+      <c r="F7" s="192" t="s">
+        <v>260</v>
+      </c>
+      <c r="G7" s="193" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="154" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="154" t="s">
+        <v>56</v>
+      </c>
+      <c r="K7" s="193" t="s">
+        <v>57</v>
+      </c>
+      <c r="L7" s="193" t="s">
+        <v>58</v>
+      </c>
+      <c r="M7" s="193" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="191" t="s">
+        <v>303</v>
+      </c>
+      <c r="O7" s="283"/>
+      <c r="P7" s="139">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="192" t="s">
+        <v>60</v>
+      </c>
+      <c r="R7" s="191" t="s">
+        <v>304</v>
+      </c>
+      <c r="S7" s="193" t="s">
+        <v>253</v>
+      </c>
+      <c r="T7" s="200"/>
+    </row>
+    <row r="8" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="146">
+        <v>6</v>
+      </c>
+      <c r="B8" s="283"/>
+      <c r="C8" s="193" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="192" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="283"/>
+      <c r="F8" s="191" t="s">
+        <v>305</v>
+      </c>
+      <c r="G8" s="193" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="191" t="s">
+        <v>306</v>
+      </c>
+      <c r="I8" s="192" t="s">
+        <v>65</v>
+      </c>
+      <c r="J8" s="192" t="s">
+        <v>219</v>
+      </c>
+      <c r="K8" s="192" t="s">
+        <v>66</v>
+      </c>
+      <c r="L8" s="193" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="193" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="255" t="s">
+        <v>307</v>
+      </c>
+      <c r="O8" s="283"/>
+      <c r="P8" s="283"/>
+      <c r="Q8" s="192" t="s">
+        <v>254</v>
+      </c>
+      <c r="R8" s="193" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" s="274"/>
+      <c r="T8" s="200" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="146">
+        <v>7</v>
+      </c>
+      <c r="B9" s="283"/>
+      <c r="C9" s="191" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="192" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="193"/>
+      <c r="F9" s="192" t="s">
+        <v>282</v>
+      </c>
+      <c r="G9" s="193" t="s">
+        <v>255</v>
+      </c>
+      <c r="H9" s="192" t="s">
+        <v>72</v>
+      </c>
+      <c r="I9" s="192" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="192" t="s">
+        <v>74</v>
+      </c>
+      <c r="K9" s="193" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="192" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="283"/>
+      <c r="N9" s="192" t="s">
+        <v>243</v>
+      </c>
+      <c r="O9" s="283"/>
+      <c r="P9" s="283"/>
+      <c r="Q9" s="191" t="s">
+        <v>309</v>
+      </c>
+      <c r="R9" s="193" t="s">
+        <v>69</v>
+      </c>
+      <c r="S9" s="283"/>
+      <c r="T9" s="200"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="146">
+        <v>8</v>
+      </c>
+      <c r="B10" s="283"/>
+      <c r="C10" s="192" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="192" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="193"/>
+      <c r="F10" s="192" t="s">
+        <v>244</v>
+      </c>
+      <c r="G10" s="193" t="s">
+        <v>79</v>
+      </c>
+      <c r="H10" s="192" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="283"/>
+      <c r="J10" s="192" t="s">
+        <v>321</v>
+      </c>
+      <c r="K10" s="192" t="s">
+        <v>81</v>
+      </c>
+      <c r="L10" s="193" t="s">
+        <v>82</v>
+      </c>
+      <c r="M10" s="283"/>
+      <c r="N10" s="178" t="s">
+        <v>83</v>
+      </c>
+      <c r="O10" s="283"/>
+      <c r="P10" s="283"/>
+      <c r="R10" s="283"/>
+      <c r="S10" s="154" t="s">
+        <v>84</v>
+      </c>
+      <c r="T10" s="200"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="146">
+        <v>9</v>
+      </c>
+      <c r="B11" s="283"/>
+      <c r="C11" s="192" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="193" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="283"/>
+      <c r="F11" s="193" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="193" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="192" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="139"/>
+      <c r="J11" s="191" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="193" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="193" t="s">
+        <v>92</v>
+      </c>
+      <c r="O11" s="283"/>
+      <c r="P11" s="283"/>
+      <c r="Q11" s="139" t="s">
+        <v>93</v>
+      </c>
+      <c r="R11" s="283"/>
+      <c r="S11" s="193" t="s">
+        <v>94</v>
+      </c>
+      <c r="T11" s="200"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="146">
+        <v>10</v>
+      </c>
+      <c r="B12" s="139"/>
+      <c r="C12" s="192" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="192" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="193"/>
+      <c r="F12" s="192" t="s">
+        <v>267</v>
+      </c>
+      <c r="G12" s="192" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="192" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="139">
+        <v>2</v>
+      </c>
+      <c r="J12" s="194" t="s">
+        <v>268</v>
+      </c>
+      <c r="K12" s="193" t="s">
+        <v>90</v>
+      </c>
+      <c r="L12" s="283"/>
+      <c r="M12" s="192"/>
+      <c r="N12" s="191" t="s">
+        <v>360</v>
+      </c>
+      <c r="O12" s="283"/>
+      <c r="P12" s="283"/>
+      <c r="Q12" s="139"/>
+      <c r="R12" s="139"/>
+      <c r="S12" s="283"/>
+      <c r="T12" s="200"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="146">
+        <v>11</v>
+      </c>
+      <c r="B13" s="139">
+        <v>5</v>
+      </c>
+      <c r="C13" s="200"/>
+      <c r="D13" s="192" t="s">
+        <v>269</v>
+      </c>
+      <c r="E13" s="193"/>
+      <c r="F13" s="193" t="s">
+        <v>101</v>
+      </c>
+      <c r="G13" s="192" t="s">
+        <v>270</v>
+      </c>
+      <c r="H13" s="192" t="s">
+        <v>271</v>
+      </c>
+      <c r="I13" s="283"/>
+      <c r="J13" s="283"/>
+      <c r="K13" s="193" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="192" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="139"/>
+      <c r="N13" s="192" t="s">
+        <v>361</v>
+      </c>
+      <c r="O13" s="283"/>
+      <c r="P13" s="283"/>
+      <c r="Q13" s="139"/>
+      <c r="R13" s="139"/>
+      <c r="S13" s="139">
+        <v>1</v>
+      </c>
+      <c r="T13" s="200"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="146">
+        <v>12</v>
+      </c>
+      <c r="B14" s="181" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="200"/>
+      <c r="D14" s="192" t="s">
+        <v>273</v>
+      </c>
+      <c r="E14" s="193"/>
+      <c r="F14" s="192" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="200"/>
+      <c r="H14" s="192" t="s">
+        <v>107</v>
+      </c>
+      <c r="I14" s="283"/>
+      <c r="J14" s="139"/>
+      <c r="K14" s="193" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="192" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="194"/>
+      <c r="N14" s="192" t="s">
+        <v>274</v>
+      </c>
+      <c r="O14" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="P14" s="283"/>
+      <c r="Q14" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="R14" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="S14" s="283"/>
+      <c r="T14" s="200"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="146">
+        <v>13</v>
+      </c>
+      <c r="B15" s="177" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="283"/>
+      <c r="E15" s="193"/>
+      <c r="F15" s="192" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="200"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="193" t="s">
+        <v>108</v>
+      </c>
+      <c r="L15" s="177" t="s">
+        <v>103</v>
+      </c>
+      <c r="M15" s="283"/>
+      <c r="N15" s="192" t="s">
+        <v>246</v>
+      </c>
+      <c r="O15" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P15" s="283"/>
+      <c r="Q15" s="283"/>
+      <c r="R15" s="154" t="s">
+        <v>116</v>
+      </c>
+      <c r="S15" s="181" t="s">
+        <v>117</v>
+      </c>
+      <c r="T15" s="200"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="146">
+        <v>14</v>
+      </c>
+      <c r="B16" s="139"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="193"/>
+      <c r="E16" s="193"/>
+      <c r="F16" s="192" t="s">
+        <v>359</v>
+      </c>
+      <c r="G16" s="200"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="193"/>
+      <c r="J16" s="139" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" s="191" t="s">
+        <v>310</v>
+      </c>
+      <c r="L16" s="177" t="s">
+        <v>109</v>
+      </c>
+      <c r="M16" s="139">
+        <v>6</v>
+      </c>
+      <c r="N16" s="192" t="s">
+        <v>276</v>
+      </c>
+      <c r="O16" s="192" t="s">
+        <v>118</v>
+      </c>
+      <c r="P16" s="283"/>
+      <c r="Q16" s="182"/>
+      <c r="R16" s="192" t="s">
+        <v>119</v>
+      </c>
+      <c r="S16" s="283"/>
+      <c r="T16" s="200"/>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A17" s="146">
+        <v>15</v>
+      </c>
+      <c r="B17" s="139">
+        <v>1</v>
+      </c>
+      <c r="C17" s="283"/>
+      <c r="D17" s="193"/>
+      <c r="E17" s="193"/>
+      <c r="F17" s="192" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="200"/>
+      <c r="H17" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
+      <c r="L17" s="283"/>
+      <c r="M17" s="183"/>
+      <c r="N17" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="O17" s="191" t="s">
+        <v>311</v>
+      </c>
+      <c r="P17" s="283"/>
+      <c r="Q17" s="193" t="s">
+        <v>357</v>
+      </c>
+      <c r="R17" s="193" t="s">
+        <v>123</v>
+      </c>
+      <c r="S17" s="283"/>
+      <c r="T17" s="200"/>
+    </row>
+    <row r="18" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="146">
+        <v>16</v>
+      </c>
+      <c r="B18" s="192" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="193"/>
+      <c r="D18" s="193"/>
+      <c r="E18" s="193"/>
+      <c r="F18" s="191" t="s">
+        <v>312</v>
+      </c>
+      <c r="G18" s="179"/>
+      <c r="H18" s="154" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="154" t="s">
+        <v>121</v>
+      </c>
+      <c r="J18" s="283"/>
+      <c r="K18" s="283"/>
+      <c r="L18" s="283"/>
+      <c r="M18" s="183"/>
+      <c r="N18" s="191" t="s">
+        <v>313</v>
+      </c>
+      <c r="O18" s="247" t="s">
+        <v>314</v>
+      </c>
+      <c r="P18" s="283"/>
+      <c r="Q18" s="193" t="s">
+        <v>127</v>
+      </c>
+      <c r="R18" s="193" t="s">
+        <v>352</v>
+      </c>
+      <c r="S18" s="283"/>
+      <c r="T18" s="200"/>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A19" s="146">
+        <v>17</v>
+      </c>
+      <c r="B19" s="192" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="193"/>
+      <c r="D19" s="193"/>
+      <c r="E19" s="193"/>
+      <c r="F19" s="192" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="200"/>
+      <c r="H19" s="192" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="283"/>
+      <c r="J19" s="283"/>
+      <c r="K19" s="283"/>
+      <c r="L19" s="154" t="s">
+        <v>126</v>
+      </c>
+      <c r="M19" s="283"/>
+      <c r="N19" s="191" t="s">
+        <v>315</v>
+      </c>
+      <c r="O19" s="283"/>
+      <c r="P19" s="184"/>
+      <c r="Q19" s="193" t="s">
+        <v>358</v>
+      </c>
+      <c r="R19" s="283"/>
+      <c r="S19" s="192"/>
+      <c r="T19" s="200"/>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A20" s="146">
+        <v>18</v>
+      </c>
+      <c r="B20" s="192" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="193"/>
+      <c r="D20" s="193"/>
+      <c r="E20" s="283"/>
+      <c r="F20" s="192" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="200"/>
+      <c r="H20" s="192" t="s">
+        <v>134</v>
+      </c>
+      <c r="I20" s="283"/>
+      <c r="J20" s="283"/>
+      <c r="K20" s="283"/>
+      <c r="L20" s="191" t="s">
+        <v>316</v>
+      </c>
+      <c r="M20" s="283"/>
+      <c r="N20" s="191" t="s">
+        <v>317</v>
+      </c>
+      <c r="O20" s="283"/>
+      <c r="P20" s="184"/>
+      <c r="Q20" s="181" t="s">
+        <v>135</v>
+      </c>
+      <c r="R20" s="283"/>
+      <c r="S20" s="283"/>
+      <c r="T20" s="195"/>
+    </row>
+    <row r="21" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="146">
+        <v>19</v>
+      </c>
+      <c r="B21" s="192" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="193"/>
+      <c r="D21" s="193"/>
+      <c r="E21" s="193"/>
+      <c r="G21" s="181" t="s">
+        <v>136</v>
+      </c>
+      <c r="H21" s="193"/>
+      <c r="I21" s="283"/>
+      <c r="J21" s="283"/>
+      <c r="K21" s="283"/>
+      <c r="L21" s="191" t="s">
+        <v>318</v>
+      </c>
+      <c r="M21" s="283"/>
+      <c r="O21" s="283"/>
+      <c r="P21" s="184"/>
+      <c r="Q21" s="274"/>
+      <c r="R21" s="282">
+        <v>3</v>
+      </c>
+      <c r="S21" s="283"/>
+      <c r="T21" s="195"/>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A22" s="146">
+        <v>20</v>
+      </c>
+      <c r="B22" s="283"/>
+      <c r="C22" s="193"/>
+      <c r="D22" s="192"/>
+      <c r="E22" s="193"/>
+      <c r="F22" s="192"/>
+      <c r="G22" s="283"/>
+      <c r="H22" s="283"/>
+      <c r="I22" s="283"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="283"/>
+      <c r="L22" s="192" t="s">
+        <v>284</v>
+      </c>
+      <c r="M22" s="283"/>
+      <c r="N22" s="192"/>
+      <c r="O22" s="283"/>
+      <c r="P22" s="283"/>
+      <c r="Q22" s="154" t="s">
+        <v>139</v>
+      </c>
+      <c r="R22" s="154" t="s">
+        <v>140</v>
+      </c>
+      <c r="S22" s="154" t="s">
+        <v>141</v>
+      </c>
+      <c r="T22" s="195"/>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A23" s="146">
+        <v>21</v>
+      </c>
+      <c r="B23" s="181" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="193"/>
+      <c r="D23" s="192"/>
+      <c r="E23" s="193"/>
+      <c r="F23" s="193"/>
+      <c r="G23" s="283"/>
+      <c r="H23" s="139">
+        <v>2</v>
+      </c>
+      <c r="I23" s="283"/>
+      <c r="J23" s="283"/>
+      <c r="K23" s="283"/>
+      <c r="L23" s="192" t="s">
+        <v>285</v>
+      </c>
+      <c r="M23" s="283"/>
+      <c r="N23" s="192"/>
+      <c r="O23" s="283"/>
+      <c r="P23" s="283"/>
+      <c r="Q23" s="191" t="s">
+        <v>145</v>
+      </c>
+      <c r="R23" s="193" t="s">
+        <v>146</v>
+      </c>
+      <c r="S23" s="283"/>
+      <c r="T23" s="200"/>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A24" s="146">
+        <v>22</v>
+      </c>
+      <c r="B24" s="192" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="193"/>
+      <c r="D24" s="192"/>
+      <c r="E24" s="193"/>
+      <c r="F24" s="283"/>
+      <c r="G24" s="283"/>
+      <c r="H24" s="154" t="s">
+        <v>147</v>
+      </c>
+      <c r="I24" s="283"/>
+      <c r="J24" s="283"/>
+      <c r="K24" s="193"/>
+      <c r="L24" s="193" t="s">
+        <v>148</v>
+      </c>
+      <c r="M24" s="283"/>
+      <c r="N24" s="192"/>
+      <c r="O24" s="283"/>
+      <c r="P24" s="283"/>
+      <c r="Q24" s="191" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="193" t="s">
+        <v>256</v>
+      </c>
+      <c r="S24" s="283"/>
+      <c r="T24" s="200"/>
+    </row>
+    <row r="25" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="146">
+        <v>23</v>
+      </c>
+      <c r="B25" s="139">
+        <v>1</v>
+      </c>
+      <c r="C25" s="193"/>
+      <c r="D25" s="193"/>
+      <c r="E25" s="193"/>
+      <c r="F25" s="193" t="s">
+        <v>150</v>
+      </c>
+      <c r="G25" s="283"/>
+      <c r="H25" s="192" t="s">
+        <v>151</v>
+      </c>
+      <c r="I25" s="283"/>
+      <c r="J25" s="274"/>
+      <c r="K25" s="283"/>
+      <c r="L25" s="192" t="s">
+        <v>143</v>
+      </c>
+      <c r="M25" s="283"/>
+      <c r="N25" s="192"/>
+      <c r="O25" s="283"/>
+      <c r="P25" s="283"/>
+      <c r="Q25" s="191" t="s">
+        <v>153</v>
+      </c>
+      <c r="R25" s="283"/>
+      <c r="S25" s="283"/>
+      <c r="T25" s="200"/>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A26" s="146">
+        <v>24</v>
+      </c>
+      <c r="B26" s="283"/>
+      <c r="C26" s="192"/>
+      <c r="D26" s="192"/>
+      <c r="E26" s="193"/>
+      <c r="F26" s="193" t="s">
+        <v>154</v>
+      </c>
+      <c r="G26" s="283"/>
+      <c r="H26" s="192"/>
+      <c r="I26" s="283"/>
+      <c r="J26" s="283"/>
+      <c r="K26" s="283"/>
+      <c r="M26" s="283"/>
+      <c r="N26" s="192"/>
+      <c r="O26" s="283"/>
+      <c r="Q26" s="191" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="200"/>
+    </row>
+    <row r="27" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="146">
+        <v>25</v>
+      </c>
+      <c r="B27" s="283"/>
+      <c r="C27" s="192"/>
+      <c r="D27" s="192"/>
+      <c r="E27" s="193"/>
+      <c r="F27" s="283"/>
+      <c r="G27" s="283"/>
+      <c r="H27" s="139">
+        <v>1</v>
+      </c>
+      <c r="I27" s="283"/>
+      <c r="J27" s="192"/>
+      <c r="K27" s="283"/>
+      <c r="L27" s="139"/>
+      <c r="M27" s="183"/>
+      <c r="N27" s="139" t="s">
+        <v>155</v>
+      </c>
+      <c r="O27" s="283"/>
+      <c r="P27" s="274"/>
+      <c r="Q27" s="193" t="s">
+        <v>354</v>
+      </c>
+      <c r="R27" s="139">
+        <v>1</v>
+      </c>
+      <c r="S27" s="186"/>
+      <c r="T27" s="200"/>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A28" s="146">
+        <v>26</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="283"/>
+      <c r="D28" s="192"/>
+      <c r="E28" s="283"/>
+      <c r="F28" s="283"/>
+      <c r="G28" s="283"/>
+      <c r="H28" s="283"/>
+      <c r="I28" s="283"/>
+      <c r="J28" s="283"/>
+      <c r="K28" s="283"/>
+      <c r="L28" s="282" t="s">
+        <v>225</v>
+      </c>
+      <c r="M28" s="283"/>
+      <c r="N28" s="181" t="s">
+        <v>110</v>
+      </c>
+      <c r="O28" s="283"/>
+      <c r="P28" s="283"/>
+      <c r="R28" s="196"/>
+      <c r="S28" s="283"/>
+      <c r="T28" s="200"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A29" s="146">
+        <v>27</v>
+      </c>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="283"/>
+      <c r="G29" s="283"/>
+      <c r="H29" s="283"/>
+      <c r="I29" s="283"/>
+      <c r="J29" s="192"/>
+      <c r="K29" s="139"/>
+      <c r="L29" s="283"/>
+      <c r="M29" s="283"/>
+      <c r="N29" s="193" t="s">
+        <v>158</v>
+      </c>
+      <c r="O29" s="283"/>
+      <c r="P29" s="192"/>
+      <c r="Q29" s="139"/>
+      <c r="R29" s="283"/>
+      <c r="S29" s="283"/>
+      <c r="T29" s="200"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A30" s="146">
+        <v>28</v>
+      </c>
+      <c r="B30" s="283"/>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="283"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="193"/>
+      <c r="I30" s="283"/>
+      <c r="J30" s="192"/>
+      <c r="K30" s="139"/>
+      <c r="L30" s="283"/>
+      <c r="M30" s="283"/>
+      <c r="N30" s="193" t="s">
+        <v>159</v>
+      </c>
+      <c r="O30" s="283"/>
+      <c r="P30" s="283"/>
+      <c r="Q30" s="139"/>
+      <c r="R30" s="283"/>
+      <c r="S30" s="192"/>
+      <c r="T30" s="200"/>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A31" s="146">
+        <v>29</v>
+      </c>
+      <c r="B31" s="283"/>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="283"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="283"/>
+      <c r="I31" s="283"/>
+      <c r="J31" s="192"/>
+      <c r="K31" s="283"/>
+      <c r="L31" s="193" t="s">
+        <v>157</v>
+      </c>
+      <c r="M31" s="283"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="283"/>
+      <c r="P31" s="283"/>
+      <c r="Q31" s="139" t="s">
+        <v>160</v>
+      </c>
+      <c r="R31" s="283"/>
+      <c r="S31" s="283"/>
+      <c r="T31" s="200"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A32" s="146">
+        <v>30</v>
+      </c>
+      <c r="B32" s="200"/>
+      <c r="C32" s="139" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="139" t="s">
+        <v>163</v>
+      </c>
+      <c r="H32" s="200"/>
+      <c r="I32" s="200"/>
+      <c r="J32" s="192"/>
+      <c r="K32" s="217" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="139"/>
+      <c r="M32" s="200"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="200"/>
+      <c r="P32" s="200"/>
+      <c r="Q32" s="177"/>
+      <c r="R32" s="200"/>
+      <c r="S32" s="200"/>
+      <c r="T32" s="200"/>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A33" s="146"/>
+      <c r="B33" s="161" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="161" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" s="162"/>
+      <c r="E33" s="161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="161"/>
+      <c r="G33" s="162"/>
+      <c r="H33" s="163"/>
+      <c r="I33" s="164"/>
+      <c r="J33" s="165"/>
+      <c r="K33" s="166"/>
+      <c r="L33" s="167" t="s">
+        <v>167</v>
+      </c>
+      <c r="M33" s="163"/>
+      <c r="N33" s="165"/>
+      <c r="O33" s="163"/>
+      <c r="P33" s="163"/>
+      <c r="Q33" s="168"/>
+      <c r="R33" s="163"/>
+      <c r="S33" s="169" t="s">
+        <v>168</v>
+      </c>
+      <c r="T33" s="170"/>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A34" s="146">
+        <v>1</v>
+      </c>
+      <c r="B34" s="200"/>
+      <c r="C34" s="193" t="s">
+        <v>169</v>
+      </c>
+      <c r="D34" s="200"/>
+      <c r="E34" s="200"/>
+      <c r="F34" s="193"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="200"/>
+      <c r="I34" s="200"/>
+      <c r="J34" s="192"/>
+      <c r="K34" s="200"/>
+      <c r="L34" s="193" t="s">
+        <v>170</v>
+      </c>
+      <c r="M34" s="200"/>
+      <c r="N34" s="192"/>
+      <c r="O34" s="200"/>
+      <c r="P34" s="200"/>
+      <c r="Q34" s="197"/>
+      <c r="R34" s="200"/>
+      <c r="S34" s="193" t="s">
+        <v>171</v>
+      </c>
+      <c r="T34" s="200"/>
+    </row>
+    <row r="35" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="146">
+        <v>2</v>
+      </c>
+      <c r="B35" s="148"/>
+      <c r="C35" s="148"/>
+      <c r="D35" s="148"/>
+      <c r="E35" s="148"/>
+      <c r="F35" s="189"/>
+      <c r="G35" s="160"/>
+      <c r="H35" s="148"/>
+      <c r="I35" s="151"/>
+      <c r="J35" s="189"/>
+      <c r="K35" s="179"/>
+      <c r="L35" s="222"/>
+      <c r="M35" s="148"/>
+      <c r="N35" s="156"/>
+      <c r="O35" s="148"/>
+      <c r="P35" s="148"/>
+      <c r="Q35" s="171"/>
+      <c r="R35" s="148"/>
+      <c r="S35" s="193" t="s">
+        <v>172</v>
+      </c>
+      <c r="T35" s="144"/>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A36" s="146">
+        <v>3</v>
+      </c>
+      <c r="B36" s="148"/>
+      <c r="C36" s="148"/>
+      <c r="D36" s="148"/>
+      <c r="E36" s="157"/>
+      <c r="F36" s="157"/>
+      <c r="G36" s="160"/>
+      <c r="H36" s="148"/>
+      <c r="I36" s="151"/>
+      <c r="J36" s="156"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="148">
+        <v>9</v>
+      </c>
+      <c r="M36" s="148"/>
+      <c r="N36" s="156"/>
+      <c r="O36" s="148"/>
+      <c r="P36" s="148"/>
+      <c r="Q36" s="171"/>
+      <c r="R36" s="148"/>
+      <c r="S36" s="200"/>
+      <c r="T36" s="144"/>
+    </row>
+    <row r="37" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="272">
+        <v>4</v>
+      </c>
+      <c r="B37" s="273" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="177" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="221"/>
+      <c r="E37" s="274"/>
+      <c r="F37" s="275"/>
+      <c r="G37" s="187"/>
+      <c r="H37" s="221"/>
+      <c r="I37" s="221"/>
+      <c r="J37" s="192"/>
+      <c r="K37" s="221"/>
+      <c r="L37" s="193" t="s">
+        <v>175</v>
+      </c>
+      <c r="M37" s="221"/>
+      <c r="N37" s="192"/>
+      <c r="O37" s="221"/>
+      <c r="P37" s="221"/>
+      <c r="Q37" s="197"/>
+      <c r="R37" s="276"/>
+      <c r="S37" s="194"/>
+      <c r="T37" s="277"/>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A38" s="146">
+        <v>5</v>
+      </c>
+      <c r="B38" s="148"/>
+      <c r="C38" s="150"/>
+      <c r="D38" s="148"/>
+      <c r="E38" s="189"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="148"/>
+      <c r="I38" s="151"/>
+      <c r="J38" s="156"/>
+      <c r="K38" s="142"/>
+      <c r="L38" s="156"/>
+      <c r="M38" s="148"/>
+      <c r="N38" s="156"/>
+      <c r="O38" s="148"/>
+      <c r="P38" s="148"/>
+      <c r="Q38" s="171"/>
+      <c r="R38" s="148"/>
+      <c r="S38" s="148">
+        <v>4</v>
+      </c>
+      <c r="T38" s="144"/>
+    </row>
+    <row r="40" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="223"/>
+      <c r="B40" s="224"/>
+      <c r="C40" s="225"/>
+      <c r="D40" s="225"/>
+      <c r="E40" s="225"/>
+      <c r="F40" s="225"/>
+      <c r="G40" s="225"/>
+      <c r="H40" s="226"/>
+      <c r="I40" s="226"/>
+      <c r="J40" s="227"/>
+      <c r="K40" s="226"/>
+      <c r="L40" s="225"/>
+      <c r="M40" s="228"/>
+      <c r="N40" s="225"/>
+      <c r="O40" s="229"/>
+      <c r="P40" s="225"/>
+      <c r="Q40" s="230"/>
+      <c r="R40" s="225"/>
+      <c r="S40" s="225"/>
+      <c r="T40" s="231"/>
+    </row>
+    <row r="41" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="223"/>
+      <c r="B41" s="140" t="s">
+        <v>177</v>
+      </c>
+      <c r="C41" s="204"/>
+      <c r="D41" s="200"/>
+      <c r="E41" s="204"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="230"/>
+      <c r="H41" s="230"/>
+      <c r="I41" s="230"/>
+      <c r="J41" s="232"/>
+      <c r="K41" s="232"/>
+      <c r="L41" s="312" t="s">
+        <v>176</v>
+      </c>
+      <c r="M41" s="312"/>
+      <c r="N41" s="312"/>
+      <c r="O41" s="312"/>
+      <c r="P41" s="312"/>
+      <c r="Q41" s="313"/>
+    </row>
+    <row r="42" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="223"/>
+      <c r="B42" s="152" t="s">
+        <v>179</v>
+      </c>
+      <c r="C42" s="174">
+        <v>87019533922</v>
+      </c>
+      <c r="D42" s="152" t="s">
+        <v>180</v>
+      </c>
+      <c r="E42" s="202"/>
+      <c r="F42" s="225"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="229"/>
+      <c r="I42" s="225"/>
+      <c r="J42" s="227"/>
+      <c r="K42" s="233"/>
+      <c r="L42" s="150"/>
+      <c r="M42" s="150"/>
+      <c r="N42" s="146" t="s">
+        <v>182</v>
+      </c>
+      <c r="O42" s="146" t="s">
+        <v>183</v>
+      </c>
+      <c r="P42" s="146" t="s">
+        <v>184</v>
+      </c>
+      <c r="Q42" s="200" t="s">
+        <v>185</v>
+      </c>
+      <c r="R42" s="151"/>
+      <c r="S42" s="234"/>
+      <c r="T42" s="231"/>
+    </row>
+    <row r="43" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="223"/>
+      <c r="B43" s="152"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="202"/>
+      <c r="F43" s="225"/>
+      <c r="G43" s="225"/>
+      <c r="H43" s="229"/>
+      <c r="I43" s="225"/>
+      <c r="J43" s="233"/>
+      <c r="K43" s="233"/>
+      <c r="L43" s="152" t="s">
+        <v>178</v>
+      </c>
+      <c r="M43" s="152" t="s">
+        <v>181</v>
+      </c>
+      <c r="N43" s="152">
+        <v>120</v>
+      </c>
+      <c r="O43" s="152">
+        <v>120</v>
+      </c>
+      <c r="P43" s="153"/>
+      <c r="Q43" s="200"/>
+      <c r="R43" s="205"/>
+      <c r="S43" s="235"/>
+      <c r="T43" s="231"/>
+    </row>
+    <row r="44" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="223"/>
+      <c r="B44" s="152" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="152">
+        <v>87018884483</v>
+      </c>
+      <c r="D44" s="152" t="s">
+        <v>189</v>
+      </c>
+      <c r="E44" s="206" t="s">
+        <v>190</v>
+      </c>
+      <c r="F44" s="225"/>
+      <c r="G44" s="225"/>
+      <c r="H44" s="229"/>
+      <c r="I44" s="225"/>
+      <c r="J44" s="233"/>
+      <c r="K44" s="233"/>
+      <c r="L44" s="152"/>
+      <c r="M44" s="152" t="s">
+        <v>187</v>
+      </c>
+      <c r="N44" s="152">
+        <v>28</v>
+      </c>
+      <c r="O44" s="152">
+        <v>28</v>
+      </c>
+      <c r="P44" s="153"/>
+      <c r="Q44" s="200"/>
+      <c r="R44" s="146"/>
+      <c r="S44" s="236"/>
+      <c r="T44" s="229"/>
+    </row>
+    <row r="45" spans="1:20" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="237"/>
+      <c r="B45" s="218" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="218">
+        <v>87019534037</v>
+      </c>
+      <c r="D45" s="218" t="s">
+        <v>191</v>
+      </c>
+      <c r="E45" s="204" t="s">
+        <v>192</v>
+      </c>
+      <c r="F45" s="230"/>
+      <c r="G45" s="230"/>
+      <c r="H45" s="230"/>
+      <c r="I45" s="230"/>
+      <c r="J45" s="238"/>
+      <c r="K45" s="239"/>
+      <c r="L45" s="219" t="s">
+        <v>186</v>
+      </c>
+  